--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/28/2026, 1:52:56 PM</t>
+    <t>7/30/2026, 10:11:49 AM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>128.79 seconds</t>
+    <t>98.77 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -86,7 +86,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-28T08:20:52.756Z</t>
+    <t>2026-07-30T04:40:26.541Z</t>
   </si>
   <si>
     <t/>
@@ -101,7 +101,7 @@
     <t>Validate Form Validation for Invalid Credentials</t>
   </si>
   <si>
-    <t>2026-07-28T08:21:23.403Z</t>
+    <t>2026-07-30T04:40:37.036Z</t>
   </si>
   <si>
     <t>Invalid credentials input handled gracefully by authentication state.</t>
@@ -113,7 +113,7 @@
     <t>Validate User Login with Valid Credentials</t>
   </si>
   <si>
-    <t>2026-07-28T08:21:53.911Z</t>
+    <t>2026-07-30T04:40:47.450Z</t>
   </si>
   <si>
     <t>User login payload submitted and processed by Supabase auth.</t>
@@ -128,7 +128,7 @@
     <t>Navigate to Session History Tab</t>
   </si>
   <si>
-    <t>2026-07-28T08:22:03.976Z</t>
+    <t>2026-07-30T04:40:57.485Z</t>
   </si>
   <si>
     <t>Switched to Session History tab successfully.</t>
@@ -140,7 +140,7 @@
     <t>Navigate to User Profile Screen</t>
   </si>
   <si>
-    <t>2026-07-28T08:22:14.059Z</t>
+    <t>2026-07-30T04:41:07.579Z</t>
   </si>
   <si>
     <t>Switched to User Profile tab successfully.</t>
@@ -155,7 +155,7 @@
     <t>Open Camera Session Recording Screen</t>
   </si>
   <si>
-    <t>2026-07-28T08:22:24.104Z</t>
+    <t>2026-07-30T04:41:17.625Z</t>
   </si>
   <si>
     <t>Camera viewport opened with media permission handling.</t>
@@ -167,7 +167,7 @@
     <t>Record Video &amp; Submit for AI Posture Analysis</t>
   </si>
   <si>
-    <t>2026-07-28T08:22:56.369Z</t>
+    <t>2026-07-30T04:41:49.844Z</t>
   </si>
   <si>
     <t>Video recorded and payload sent to FastAPI /analyze endpoint.</t>
@@ -741,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>5184</v>
+        <v>15466</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -767,7 +767,7 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>30646</v>
+        <v>10494</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -793,7 +793,7 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>30508</v>
+        <v>10414</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -819,7 +819,7 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>10064</v>
+        <v>10034</v>
       </c>
       <c r="F5" t="s">
         <v>38</v>
@@ -845,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>10083</v>
+        <v>10094</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -871,7 +871,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>10044</v>
+        <v>10045</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
@@ -897,7 +897,7 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>32264</v>
+        <v>32218</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>

--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="390">
   <si>
     <t>ConfidAI Web E2E Selenium Test Analysis Report</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/30/2026, 10:11:49 AM</t>
+    <t>7/30/2026, 10:47:58 AM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -41,13 +41,13 @@
     <t>Pass Rate Percentage</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>98.89%</t>
   </si>
   <si>
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>98.77 seconds</t>
+    <t>146.66 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -59,6 +59,9 @@
     <t>Test Description</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -74,110 +77,1118 @@
     <t>Notes / Context</t>
   </si>
   <si>
-    <t>Authentication E2E Suite</t>
+    <t>Authentication &amp; Onboarding E2E Suite</t>
   </si>
   <si>
     <t>TC-AUTH-001</t>
   </si>
   <si>
-    <t>Verify Web App Loaded on Live Firebase Hosting</t>
+    <t>Verify ConfidAI Web Landing Page Load</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-30T04:40:26.541Z</t>
+    <t>2026-07-30T05:15:58.768Z</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Web application loaded successfully at https://confidai-b469a.web.app</t>
+    <t>Successfully rendered at https://confidai-b469a.web.app</t>
   </si>
   <si>
     <t>TC-AUTH-002</t>
   </si>
   <si>
-    <t>Validate Form Validation for Invalid Credentials</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:40:37.036Z</t>
-  </si>
-  <si>
-    <t>Invalid credentials input handled gracefully by authentication state.</t>
+    <t>Validate empty email input error response</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:15:58.874Z</t>
+  </si>
+  <si>
+    <t>Empty email prompt handled</t>
   </si>
   <si>
     <t>TC-AUTH-003</t>
   </si>
   <si>
-    <t>Validate User Login with Valid Credentials</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:40:47.450Z</t>
-  </si>
-  <si>
-    <t>User login payload submitted and processed by Supabase auth.</t>
-  </si>
-  <si>
-    <t>Navigation &amp; Tabs E2E Suite</t>
+    <t>Validate email without @ symbol format check</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:09.182Z</t>
+  </si>
+  <si>
+    <t>Invalid email format caught</t>
+  </si>
+  <si>
+    <t>TC-AUTH-004</t>
+  </si>
+  <si>
+    <t>Validate email without TLD format check</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:19.374Z</t>
+  </si>
+  <si>
+    <t>Missing TLD handled</t>
+  </si>
+  <si>
+    <t>TC-AUTH-005</t>
+  </si>
+  <si>
+    <t>Validate email with special characters in local part</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:29.628Z</t>
+  </si>
+  <si>
+    <t>Tag sub-addressing accepted</t>
+  </si>
+  <si>
+    <t>TC-AUTH-006</t>
+  </si>
+  <si>
+    <t>Validate short password error response (&lt;6 chars)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:39.792Z</t>
+  </si>
+  <si>
+    <t>Min length password check passed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-007</t>
+  </si>
+  <si>
+    <t>Validate empty password field submission</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:39.892Z</t>
+  </si>
+  <si>
+    <t>Empty password check passed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-008</t>
+  </si>
+  <si>
+    <t>Validate password visibility toggle icon interaction</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:40.007Z</t>
+  </si>
+  <si>
+    <t>Password obscure state updated</t>
+  </si>
+  <si>
+    <t>TC-AUTH-009</t>
+  </si>
+  <si>
+    <t>Validate Login / Register tab toggle switch</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:40.120Z</t>
+  </si>
+  <si>
+    <t>Switched to Register mode UI</t>
+  </si>
+  <si>
+    <t>TC-AUTH-010</t>
+  </si>
+  <si>
+    <t>Validate Register mode Full Name input field</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:40.232Z</t>
+  </si>
+  <si>
+    <t>Full Name text input received</t>
+  </si>
+  <si>
+    <t>TC-AUTH-011</t>
+  </si>
+  <si>
+    <t>Validate Register mode Phone Number input field</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:16:40.355Z</t>
+  </si>
+  <si>
+    <t>Phone Number text input received</t>
+  </si>
+  <si>
+    <t>TC-AUTH-012</t>
+  </si>
+  <si>
+    <t>Validate valid credentials login submission payload</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:00.732Z</t>
+  </si>
+  <si>
+    <t>Auth payload sent to Supabase</t>
+  </si>
+  <si>
+    <t>TC-AUTH-013</t>
+  </si>
+  <si>
+    <t>Validate forgot password link navigation trigger</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:00.850Z</t>
+  </si>
+  <si>
+    <t>Forgot password route triggered</t>
+  </si>
+  <si>
+    <t>TC-AUTH-014</t>
+  </si>
+  <si>
+    <t>Validate reset password email input submission</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:00.953Z</t>
+  </si>
+  <si>
+    <t>Password recovery email dispatched</t>
+  </si>
+  <si>
+    <t>TC-AUTH-015</t>
+  </si>
+  <si>
+    <t>Validate OTP verification screen load &amp; 6-digit pin boxes</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.055Z</t>
+  </si>
+  <si>
+    <t>OTP input boxes rendered</t>
+  </si>
+  <si>
+    <t>TC-AUTH-016</t>
+  </si>
+  <si>
+    <t>Validate OTP submission with incomplete digits</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.175Z</t>
+  </si>
+  <si>
+    <t>Incomplete OTP prevented</t>
+  </si>
+  <si>
+    <t>TC-AUTH-017</t>
+  </si>
+  <si>
+    <t>Validate OTP submission with valid 6-digit code</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.291Z</t>
+  </si>
+  <si>
+    <t>OTP verification confirmed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-018</t>
+  </si>
+  <si>
+    <t>Validate Onboarding screen slide 1 rendering</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.405Z</t>
+  </si>
+  <si>
+    <t>Slide 1 hero image &amp; title visible</t>
+  </si>
+  <si>
+    <t>TC-AUTH-019</t>
+  </si>
+  <si>
+    <t>Validate Onboarding screen slide 2 navigation swipe</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.523Z</t>
+  </si>
+  <si>
+    <t>Slide 2 posture tips displayed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-020</t>
+  </si>
+  <si>
+    <t>Validate Onboarding screen slide 3 navigation swipe</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.640Z</t>
+  </si>
+  <si>
+    <t>Slide 3 AI feature summary displayed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-021</t>
+  </si>
+  <si>
+    <t>Validate Onboarding Skip button action</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.745Z</t>
+  </si>
+  <si>
+    <t>Skipped onboarding to main screen</t>
+  </si>
+  <si>
+    <t>TC-AUTH-022</t>
+  </si>
+  <si>
+    <t>Validate Onboarding Get Started button action</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.854Z</t>
+  </si>
+  <si>
+    <t>Completed onboarding flow</t>
+  </si>
+  <si>
+    <t>TC-AUTH-023</t>
+  </si>
+  <si>
+    <t>Validate persistent login session token restoration</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:01.954Z</t>
+  </si>
+  <si>
+    <t>SharedPreferences session restored</t>
+  </si>
+  <si>
+    <t>TC-AUTH-024</t>
+  </si>
+  <si>
+    <t>Validate auth error banner dismiss button</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.062Z</t>
+  </si>
+  <si>
+    <t>Error snackbar dismissed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-025</t>
+  </si>
+  <si>
+    <t>Validate whitespace trimming on email submission</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.171Z</t>
+  </si>
+  <si>
+    <t>Whitespace trimmed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-026</t>
+  </si>
+  <si>
+    <t>Validate registration password confirmation match</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.276Z</t>
+  </si>
+  <si>
+    <t>Passwords match verified</t>
+  </si>
+  <si>
+    <t>TC-AUTH-027</t>
+  </si>
+  <si>
+    <t>Validate terms of service checkbox toggle</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.388Z</t>
+  </si>
+  <si>
+    <t>TOS checkbox toggled</t>
+  </si>
+  <si>
+    <t>TC-AUTH-028</t>
+  </si>
+  <si>
+    <t>Validate privacy policy external link modal</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.503Z</t>
+  </si>
+  <si>
+    <t>Privacy policy displayed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-029</t>
+  </si>
+  <si>
+    <t>Validate logout button clearing local session state</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.606Z</t>
+  </si>
+  <si>
+    <t>Session storage cleared</t>
+  </si>
+  <si>
+    <t>TC-AUTH-030</t>
+  </si>
+  <si>
+    <t>Validate redirect unauthenticated user to Login screen</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.706Z</t>
+  </si>
+  <si>
+    <t>Guarded route redirected to Login</t>
+  </si>
+  <si>
+    <t>Navigation, Drawer &amp; Theme E2E Suite</t>
   </si>
   <si>
     <t>TC-NAV-001</t>
   </si>
   <si>
-    <t>Navigate to Session History Tab</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:40:57.485Z</t>
-  </si>
-  <si>
-    <t>Switched to Session History tab successfully.</t>
+    <t>Verify AppBar Title ConfidAI on Main Screen</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.789Z</t>
+  </si>
+  <si>
+    <t>AppBar title ConfidAI visible</t>
   </si>
   <si>
     <t>TC-NAV-002</t>
   </si>
   <si>
-    <t>Navigate to User Profile Screen</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:41:07.579Z</t>
-  </si>
-  <si>
-    <t>Switched to User Profile tab successfully.</t>
-  </si>
-  <si>
-    <t>AI Body Language Analysis E2E Suite</t>
+    <t>Verify Drawer Burger Icon opening navigation drawer</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.879Z</t>
+  </si>
+  <si>
+    <t>Navigation drawer opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-003</t>
+  </si>
+  <si>
+    <t>Verify Drawer User Avatar rendering</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:02.970Z</t>
+  </si>
+  <si>
+    <t>User Avatar circle visible in drawer header</t>
+  </si>
+  <si>
+    <t>TC-NAV-004</t>
+  </si>
+  <si>
+    <t>Verify Drawer User Name header label</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:03.053Z</t>
+  </si>
+  <si>
+    <t>User Name header rendered</t>
+  </si>
+  <si>
+    <t>TC-NAV-005</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Home menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:03.144Z</t>
+  </si>
+  <si>
+    <t>Home tab route active</t>
+  </si>
+  <si>
+    <t>TC-NAV-006</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: History menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:13.246Z</t>
+  </si>
+  <si>
+    <t>Session History screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-007</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Profile menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.286Z</t>
+  </si>
+  <si>
+    <t>Profile screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-008</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Settings menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.377Z</t>
+  </si>
+  <si>
+    <t>Settings screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-009</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Notifications menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.470Z</t>
+  </si>
+  <si>
+    <t>Notifications screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-010</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Progress Report menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.554Z</t>
+  </si>
+  <si>
+    <t>Progress Report screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-011</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Help &amp; Support menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.647Z</t>
+  </si>
+  <si>
+    <t>Help &amp; Support screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-012</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: About App menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.729Z</t>
+  </si>
+  <si>
+    <t>About App screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-013</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Tips Library menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.811Z</t>
+  </si>
+  <si>
+    <t>Tips Library screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-014</t>
+  </si>
+  <si>
+    <t>Verify Drawer item: Achievements menu item click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.904Z</t>
+  </si>
+  <si>
+    <t>Achievements screen opened</t>
+  </si>
+  <si>
+    <t>TC-NAV-015</t>
+  </si>
+  <si>
+    <t>Verify Settings screen: Blue Accent Color swatch selection</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:23.987Z</t>
+  </si>
+  <si>
+    <t>Theme accent set to Ocean Blue</t>
+  </si>
+  <si>
+    <t>TC-NAV-016</t>
+  </si>
+  <si>
+    <t>Verify Settings screen: Orange Accent Color swatch selection</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.072Z</t>
+  </si>
+  <si>
+    <t>Theme accent set to Sunset Orange</t>
+  </si>
+  <si>
+    <t>TC-NAV-017</t>
+  </si>
+  <si>
+    <t>Verify Settings screen: Green Accent Color swatch selection</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.153Z</t>
+  </si>
+  <si>
+    <t>Theme accent set to Forest Green</t>
+  </si>
+  <si>
+    <t>TC-NAV-018</t>
+  </si>
+  <si>
+    <t>Verify Settings screen: Dark Mode Switch toggle ON</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.240Z</t>
+  </si>
+  <si>
+    <t>Dark mode theme activated</t>
+  </si>
+  <si>
+    <t>TC-NAV-019</t>
+  </si>
+  <si>
+    <t>Verify Settings screen: Dark Mode Switch toggle OFF</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.322Z</t>
+  </si>
+  <si>
+    <t>Light mode theme activated</t>
+  </si>
+  <si>
+    <t>TC-NAV-020</t>
+  </si>
+  <si>
+    <t>Verify Edit Profile screen load &amp; form text controllers</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.409Z</t>
+  </si>
+  <si>
+    <t>Profile name &amp; bio input fields editable</t>
+  </si>
+  <si>
+    <t>TC-NAV-021</t>
+  </si>
+  <si>
+    <t>Verify Edit Profile save changes button trigger</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.504Z</t>
+  </si>
+  <si>
+    <t>Profile changes saved to SharedPreferences</t>
+  </si>
+  <si>
+    <t>TC-NAV-022</t>
+  </si>
+  <si>
+    <t>Verify Notifications screen recent notification list items</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.587Z</t>
+  </si>
+  <si>
+    <t>5 notification card items rendered</t>
+  </si>
+  <si>
+    <t>TC-NAV-023</t>
+  </si>
+  <si>
+    <t>Verify Progress Report screen 28-day streak calendar grid</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.674Z</t>
+  </si>
+  <si>
+    <t>Streak calendar 28 day circles rendered</t>
+  </si>
+  <si>
+    <t>TC-NAV-024</t>
+  </si>
+  <si>
+    <t>Verify Achievements screen unlocked badge icons</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.756Z</t>
+  </si>
+  <si>
+    <t>Achievement badge list displayed</t>
+  </si>
+  <si>
+    <t>TC-NAV-025</t>
+  </si>
+  <si>
+    <t>Verify Tips Library card expansion details</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.839Z</t>
+  </si>
+  <si>
+    <t>Body language tip detail card expanded</t>
+  </si>
+  <si>
+    <t>TC-NAV-026</t>
+  </si>
+  <si>
+    <t>Verify Help &amp; Support FAQ accordion expansion</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:24.921Z</t>
+  </si>
+  <si>
+    <t>FAQ answer text expanded</t>
+  </si>
+  <si>
+    <t>TC-NAV-027</t>
+  </si>
+  <si>
+    <t>Verify About App version string &amp; tech stack overview</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:25.002Z</t>
+  </si>
+  <si>
+    <t>App version 1.0.0 &amp; Flutter framework credited</t>
+  </si>
+  <si>
+    <t>TC-NAV-028</t>
+  </si>
+  <si>
+    <t>Verify Bottom Navigation Bar Home tab icon click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:25.085Z</t>
+  </si>
+  <si>
+    <t>Switched to Home tab</t>
+  </si>
+  <si>
+    <t>TC-NAV-029</t>
+  </si>
+  <si>
+    <t>Verify Bottom Navigation Bar History tab icon click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:35.116Z</t>
+  </si>
+  <si>
+    <t>Switched to History tab</t>
+  </si>
+  <si>
+    <t>TC-NAV-030</t>
+  </si>
+  <si>
+    <t>Verify Bottom Navigation Bar Profile tab icon click</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:45.196Z</t>
+  </si>
+  <si>
+    <t>Switched to Profile tab</t>
+  </si>
+  <si>
+    <t>AI Body Language Camera Analysis E2E Suite</t>
   </si>
   <si>
     <t>TC-AI-001</t>
   </si>
   <si>
-    <t>Open Camera Session Recording Screen</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:41:17.625Z</t>
-  </si>
-  <si>
-    <t>Camera viewport opened with media permission handling.</t>
+    <t>Verify Start Practice Session button on Home Screen</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.236Z</t>
+  </si>
+  <si>
+    <t>Start Practice Session button active</t>
   </si>
   <si>
     <t>TC-AI-002</t>
   </si>
   <si>
-    <t>Record Video &amp; Submit for AI Posture Analysis</t>
-  </si>
-  <si>
-    <t>2026-07-30T04:41:49.844Z</t>
-  </si>
-  <si>
-    <t>Video recorded and payload sent to FastAPI /analyze endpoint.</t>
+    <t>Verify Camera permission dialog auto-grant via fake UI flags</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.370Z</t>
+  </si>
+  <si>
+    <t>Fake media device flags granted video stream</t>
+  </si>
+  <si>
+    <t>TC-AI-003</t>
+  </si>
+  <si>
+    <t>Verify Y4M real sample video stream feed injection (--use-file-for-fake-video-capture)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.494Z</t>
+  </si>
+  <si>
+    <t>sample_video.y4m video stream feeding HTML5 video element</t>
+  </si>
+  <si>
+    <t>TC-AI-004</t>
+  </si>
+  <si>
+    <t>Verify Camera preview widget initialization &amp; aspect ratio container</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.629Z</t>
+  </si>
+  <si>
+    <t>Camera view container initialized</t>
+  </si>
+  <si>
+    <t>TC-AI-005</t>
+  </si>
+  <si>
+    <t>Verify Live recording duration timer start (00:00 count up)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.753Z</t>
+  </si>
+  <si>
+    <t>Timer counter incrementing</t>
+  </si>
+  <si>
+    <t>TC-AI-006</t>
+  </si>
+  <si>
+    <t>Verify Floating Record / Pause control button rendering</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:55.890Z</t>
+  </si>
+  <si>
+    <t>Floating record button visible</t>
+  </si>
+  <si>
+    <t>TC-AI-007</t>
+  </si>
+  <si>
+    <t>Verify Live Posture Score indicator widget on overlay</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.023Z</t>
+  </si>
+  <si>
+    <t>Live posture score overlay active</t>
+  </si>
+  <si>
+    <t>TC-AI-008</t>
+  </si>
+  <si>
+    <t>Verify Live Head Stability gauge on camera view overlay</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.149Z</t>
+  </si>
+  <si>
+    <t>Head stability gauge active</t>
+  </si>
+  <si>
+    <t>TC-AI-009</t>
+  </si>
+  <si>
+    <t>Verify Live Gesture detection feedback indicator</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.283Z</t>
+  </si>
+  <si>
+    <t>Gesture detection indicator active</t>
+  </si>
+  <si>
+    <t>TC-AI-010</t>
+  </si>
+  <si>
+    <t>Verify Stop Session button action &amp; session finalization</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.284Z</t>
+  </si>
+  <si>
+    <t>cameraPage.clickRecord is not a function</t>
+  </si>
+  <si>
+    <t>TC-AI-011</t>
+  </si>
+  <si>
+    <t>Verify AI Analysis pipeline payload dispatch to Render backend</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.418Z</t>
+  </si>
+  <si>
+    <t>Video payload sent to AI backend service</t>
+  </si>
+  <si>
+    <t>TC-AI-012</t>
+  </si>
+  <si>
+    <t>Verify Results Screen transition after analysis completion</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.552Z</t>
+  </si>
+  <si>
+    <t>Navigated to Results Screen</t>
+  </si>
+  <si>
+    <t>TC-AI-013</t>
+  </si>
+  <si>
+    <t>Verify Overall Confidence Score gauge rendering (0-100%)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.684Z</t>
+  </si>
+  <si>
+    <t>Overall score gauge displayed</t>
+  </si>
+  <si>
+    <t>TC-AI-014</t>
+  </si>
+  <si>
+    <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.820Z</t>
+  </si>
+  <si>
+    <t>Posture sub-score breakdown visible</t>
+  </si>
+  <si>
+    <t>TC-AI-015</t>
+  </si>
+  <si>
+    <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:56.945Z</t>
+  </si>
+  <si>
+    <t>Head stability sub-score breakdown visible</t>
+  </si>
+  <si>
+    <t>TC-AI-016</t>
+  </si>
+  <si>
+    <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.079Z</t>
+  </si>
+  <si>
+    <t>Gesture sub-score breakdown visible</t>
+  </si>
+  <si>
+    <t>TC-AI-017</t>
+  </si>
+  <si>
+    <t>Verify Key Improvement Recommendations list</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.204Z</t>
+  </si>
+  <si>
+    <t>AI feedback recommendations list populated</t>
+  </si>
+  <si>
+    <t>TC-AI-018</t>
+  </si>
+  <si>
+    <t>Verify Save Session to History SharedPreferences database</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.334Z</t>
+  </si>
+  <si>
+    <t>Session JSON record committed to SharedPreferences</t>
+  </si>
+  <si>
+    <t>TC-AI-019</t>
+  </si>
+  <si>
+    <t>Verify Export Session Report CSV button click action</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.460Z</t>
+  </si>
+  <si>
+    <t>CSV file export triggered via Share API</t>
+  </si>
+  <si>
+    <t>TC-AI-020</t>
+  </si>
+  <si>
+    <t>Verify Export Session Summary PDF document generation</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.586Z</t>
+  </si>
+  <si>
+    <t>PDF document compiled via printing package</t>
+  </si>
+  <si>
+    <t>TC-AI-021</t>
+  </si>
+  <si>
+    <t>Verify Session History log list updated with new session item</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.715Z</t>
+  </si>
+  <si>
+    <t>History list contains newly completed session</t>
+  </si>
+  <si>
+    <t>TC-AI-022</t>
+  </si>
+  <si>
+    <t>Verify Session History item score pill color coding (Green/Orange)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.842Z</t>
+  </si>
+  <si>
+    <t>Score pill color matches performance tier</t>
+  </si>
+  <si>
+    <t>TC-AI-023</t>
+  </si>
+  <si>
+    <t>Verify Session History Compare Last 2 Sessions modal trigger</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:57.969Z</t>
+  </si>
+  <si>
+    <t>Compare modal bottom sheet opened</t>
+  </si>
+  <si>
+    <t>TC-AI-024</t>
+  </si>
+  <si>
+    <t>Verify Session Comparison metric deltas (+/- % diff calculations)</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.091Z</t>
+  </si>
+  <si>
+    <t>Posture/head/gesture diff metrics accurate</t>
+  </si>
+  <si>
+    <t>TC-AI-025</t>
+  </si>
+  <si>
+    <t>Verify Clear Session History confirmation dialog</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.222Z</t>
+  </si>
+  <si>
+    <t>Clear history dialog prompted</t>
+  </si>
+  <si>
+    <t>TC-AI-026</t>
+  </si>
+  <si>
+    <t>Verify Cancel Camera Session return to Home screen</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.354Z</t>
+  </si>
+  <si>
+    <t>Session cancelled cleanly</t>
+  </si>
+  <si>
+    <t>TC-AI-027</t>
+  </si>
+  <si>
+    <t>Verify Retry Analysis button action on backend failure</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.502Z</t>
+  </si>
+  <si>
+    <t>Retry analysis request dispatched</t>
+  </si>
+  <si>
+    <t>TC-AI-028</t>
+  </si>
+  <si>
+    <t>Verify Practice Reminder notification trigger logic</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.625Z</t>
+  </si>
+  <si>
+    <t>Weekly practice reminder scheduled</t>
+  </si>
+  <si>
+    <t>TC-AI-029</t>
+  </si>
+  <si>
+    <t>Verify Streak counter increment after session completion</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.755Z</t>
+  </si>
+  <si>
+    <t>Streak count updated in calendar</t>
+  </si>
+  <si>
+    <t>TC-AI-030</t>
+  </si>
+  <si>
+    <t>Verify Achievement unlock detection after 3 completed sessions</t>
+  </si>
+  <si>
+    <t>2026-07-30T05:17:58.876Z</t>
+  </si>
+  <si>
+    <t>3-session achievement unlocked</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -201,6 +1212,10 @@
     </font>
     <font>
       <b/>
+      <color rgb="C0392B"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -208,8 +1223,12 @@
       <b/>
       <color rgb="155724"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="721C24"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +1250,11 @@
         <fgColor rgb="D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -244,7 +1268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,10 +1277,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -642,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,15 +1678,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>0</v>
+      <c r="B8" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -688,225 +1716,2657 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>15746</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>15466</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>226</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>10428</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>10312</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>10374</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>10283</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
-        <v>10494</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>235</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>233</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>232</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>243</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13">
+        <v>20497</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14">
+        <v>238</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15">
+        <v>223</v>
+      </c>
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16">
+        <v>222</v>
+      </c>
+      <c r="G16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
-        <v>10414</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
-        <v>10034</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>10094</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>10045</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>32218</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
+      <c r="E17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17">
+        <v>240</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18">
+        <v>236</v>
+      </c>
+      <c r="G18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>234</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>238</v>
+      </c>
+      <c r="G20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21">
+        <v>237</v>
+      </c>
+      <c r="G21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22">
+        <v>224</v>
+      </c>
+      <c r="G22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>229</v>
+      </c>
+      <c r="G23" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24">
+        <v>220</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25">
+        <v>228</v>
+      </c>
+      <c r="G25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>229</v>
+      </c>
+      <c r="G26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27">
+        <v>224</v>
+      </c>
+      <c r="G27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <v>231</v>
+      </c>
+      <c r="G28" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>234</v>
+      </c>
+      <c r="G29" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>223</v>
+      </c>
+      <c r="G30" t="s">
+        <v>141</v>
+      </c>
+      <c r="H30" t="s">
+        <v>27</v>
+      </c>
+      <c r="I30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31">
+        <v>220</v>
+      </c>
+      <c r="G31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>181</v>
+      </c>
+      <c r="G32" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33">
+        <v>190</v>
+      </c>
+      <c r="G33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34">
+        <v>191</v>
+      </c>
+      <c r="G34" t="s">
+        <v>158</v>
+      </c>
+      <c r="H34" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35">
+        <v>182</v>
+      </c>
+      <c r="G35" t="s">
+        <v>162</v>
+      </c>
+      <c r="H35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36">
+        <v>191</v>
+      </c>
+      <c r="G36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37">
+        <v>10202</v>
+      </c>
+      <c r="G37" t="s">
+        <v>170</v>
+      </c>
+      <c r="H37" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38">
+        <v>10140</v>
+      </c>
+      <c r="G38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39">
+        <v>191</v>
+      </c>
+      <c r="G39" t="s">
+        <v>178</v>
+      </c>
+      <c r="H39" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" t="s">
+        <v>181</v>
+      </c>
+      <c r="D40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40">
+        <v>193</v>
+      </c>
+      <c r="G40" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41">
+        <v>184</v>
+      </c>
+      <c r="G41" t="s">
+        <v>186</v>
+      </c>
+      <c r="H41" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42">
+        <v>192</v>
+      </c>
+      <c r="G42" t="s">
+        <v>190</v>
+      </c>
+      <c r="H42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43">
+        <v>181</v>
+      </c>
+      <c r="G43" t="s">
+        <v>194</v>
+      </c>
+      <c r="H43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>182</v>
+      </c>
+      <c r="G44" t="s">
+        <v>198</v>
+      </c>
+      <c r="H44" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45">
+        <v>193</v>
+      </c>
+      <c r="G45" t="s">
+        <v>202</v>
+      </c>
+      <c r="H45" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>205</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46">
+        <v>183</v>
+      </c>
+      <c r="G46" t="s">
+        <v>206</v>
+      </c>
+      <c r="H46" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>208</v>
+      </c>
+      <c r="C47" t="s">
+        <v>209</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47">
+        <v>185</v>
+      </c>
+      <c r="G47" t="s">
+        <v>210</v>
+      </c>
+      <c r="H47" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" t="s">
+        <v>213</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48">
+        <v>181</v>
+      </c>
+      <c r="G48" t="s">
+        <v>214</v>
+      </c>
+      <c r="H48" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49">
+        <v>186</v>
+      </c>
+      <c r="G49" t="s">
+        <v>218</v>
+      </c>
+      <c r="H49" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50">
+        <v>182</v>
+      </c>
+      <c r="G50" t="s">
+        <v>222</v>
+      </c>
+      <c r="H50" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51">
+        <v>186</v>
+      </c>
+      <c r="G51" t="s">
+        <v>226</v>
+      </c>
+      <c r="H51" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>147</v>
+      </c>
+      <c r="B52" t="s">
+        <v>228</v>
+      </c>
+      <c r="C52" t="s">
+        <v>229</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52">
+        <v>194</v>
+      </c>
+      <c r="G52" t="s">
+        <v>230</v>
+      </c>
+      <c r="H52" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" t="s">
+        <v>233</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53">
+        <v>183</v>
+      </c>
+      <c r="G53" t="s">
+        <v>234</v>
+      </c>
+      <c r="H53" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" t="s">
+        <v>236</v>
+      </c>
+      <c r="C54" t="s">
+        <v>237</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54">
+        <v>186</v>
+      </c>
+      <c r="G54" t="s">
+        <v>238</v>
+      </c>
+      <c r="H54" t="s">
+        <v>27</v>
+      </c>
+      <c r="I54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>147</v>
+      </c>
+      <c r="B55" t="s">
+        <v>240</v>
+      </c>
+      <c r="C55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55">
+        <v>182</v>
+      </c>
+      <c r="G55" t="s">
+        <v>242</v>
+      </c>
+      <c r="H55" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" t="s">
+        <v>245</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56">
+        <v>183</v>
+      </c>
+      <c r="G56" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" t="s">
+        <v>27</v>
+      </c>
+      <c r="I56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C57" t="s">
+        <v>249</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57">
+        <v>182</v>
+      </c>
+      <c r="G57" t="s">
+        <v>250</v>
+      </c>
+      <c r="H57" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" t="s">
+        <v>252</v>
+      </c>
+      <c r="C58" t="s">
+        <v>253</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58">
+        <v>181</v>
+      </c>
+      <c r="G58" t="s">
+        <v>254</v>
+      </c>
+      <c r="H58" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" t="s">
+        <v>256</v>
+      </c>
+      <c r="C59" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59">
+        <v>182</v>
+      </c>
+      <c r="G59" t="s">
+        <v>258</v>
+      </c>
+      <c r="H59" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>260</v>
+      </c>
+      <c r="C60" t="s">
+        <v>261</v>
+      </c>
+      <c r="D60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60">
+        <v>10131</v>
+      </c>
+      <c r="G60" t="s">
+        <v>262</v>
+      </c>
+      <c r="H60" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" t="s">
+        <v>264</v>
+      </c>
+      <c r="C61" t="s">
+        <v>265</v>
+      </c>
+      <c r="D61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61">
+        <v>10180</v>
+      </c>
+      <c r="G61" t="s">
+        <v>266</v>
+      </c>
+      <c r="H61" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>268</v>
+      </c>
+      <c r="B62" t="s">
+        <v>269</v>
+      </c>
+      <c r="C62" t="s">
+        <v>270</v>
+      </c>
+      <c r="D62" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62">
+        <v>10188</v>
+      </c>
+      <c r="G62" t="s">
+        <v>271</v>
+      </c>
+      <c r="H62" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" t="s">
+        <v>273</v>
+      </c>
+      <c r="C63" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63">
+        <v>284</v>
+      </c>
+      <c r="G63" t="s">
+        <v>275</v>
+      </c>
+      <c r="H63" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>268</v>
+      </c>
+      <c r="B64" t="s">
+        <v>277</v>
+      </c>
+      <c r="C64" t="s">
+        <v>278</v>
+      </c>
+      <c r="D64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64">
+        <v>274</v>
+      </c>
+      <c r="G64" t="s">
+        <v>279</v>
+      </c>
+      <c r="H64" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" t="s">
+        <v>281</v>
+      </c>
+      <c r="C65" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65">
+        <v>285</v>
+      </c>
+      <c r="G65" t="s">
+        <v>283</v>
+      </c>
+      <c r="H65" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>268</v>
+      </c>
+      <c r="B66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C66" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66">
+        <v>273</v>
+      </c>
+      <c r="G66" t="s">
+        <v>287</v>
+      </c>
+      <c r="H66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" t="s">
+        <v>289</v>
+      </c>
+      <c r="C67" t="s">
+        <v>290</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67">
+        <v>287</v>
+      </c>
+      <c r="G67" t="s">
+        <v>291</v>
+      </c>
+      <c r="H67" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C68" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68">
+        <v>282</v>
+      </c>
+      <c r="G68" t="s">
+        <v>295</v>
+      </c>
+      <c r="H68" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>268</v>
+      </c>
+      <c r="B69" t="s">
+        <v>297</v>
+      </c>
+      <c r="C69" t="s">
+        <v>298</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69">
+        <v>275</v>
+      </c>
+      <c r="G69" t="s">
+        <v>299</v>
+      </c>
+      <c r="H69" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>268</v>
+      </c>
+      <c r="B70" t="s">
+        <v>301</v>
+      </c>
+      <c r="C70" t="s">
+        <v>302</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70">
+        <v>284</v>
+      </c>
+      <c r="G70" t="s">
+        <v>303</v>
+      </c>
+      <c r="H70" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" t="s">
+        <v>305</v>
+      </c>
+      <c r="C71" t="s">
+        <v>306</v>
+      </c>
+      <c r="D71" t="s">
+        <v>64</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>308</v>
+      </c>
+      <c r="H71" t="s">
+        <v>309</v>
+      </c>
+      <c r="I71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" t="s">
+        <v>310</v>
+      </c>
+      <c r="C72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D72" t="s">
+        <v>64</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72">
+        <v>284</v>
+      </c>
+      <c r="G72" t="s">
+        <v>312</v>
+      </c>
+      <c r="H72" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>268</v>
+      </c>
+      <c r="B73" t="s">
+        <v>314</v>
+      </c>
+      <c r="C73" t="s">
+        <v>315</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73">
+        <v>284</v>
+      </c>
+      <c r="G73" t="s">
+        <v>316</v>
+      </c>
+      <c r="H73" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" t="s">
+        <v>318</v>
+      </c>
+      <c r="C74" t="s">
+        <v>319</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74">
+        <v>281</v>
+      </c>
+      <c r="G74" t="s">
+        <v>320</v>
+      </c>
+      <c r="H74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>268</v>
+      </c>
+      <c r="B75" t="s">
+        <v>322</v>
+      </c>
+      <c r="C75" t="s">
+        <v>323</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75">
+        <v>286</v>
+      </c>
+      <c r="G75" t="s">
+        <v>324</v>
+      </c>
+      <c r="H75" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>268</v>
+      </c>
+      <c r="B76" t="s">
+        <v>326</v>
+      </c>
+      <c r="C76" t="s">
+        <v>327</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76">
+        <v>275</v>
+      </c>
+      <c r="G76" t="s">
+        <v>328</v>
+      </c>
+      <c r="H76" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" t="s">
+        <v>330</v>
+      </c>
+      <c r="C77" t="s">
+        <v>331</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77">
+        <v>284</v>
+      </c>
+      <c r="G77" t="s">
+        <v>332</v>
+      </c>
+      <c r="H77" t="s">
+        <v>27</v>
+      </c>
+      <c r="I77" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>268</v>
+      </c>
+      <c r="B78" t="s">
+        <v>334</v>
+      </c>
+      <c r="C78" t="s">
+        <v>335</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78">
+        <v>275</v>
+      </c>
+      <c r="G78" t="s">
+        <v>336</v>
+      </c>
+      <c r="H78" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>268</v>
+      </c>
+      <c r="B79" t="s">
+        <v>338</v>
+      </c>
+      <c r="C79" t="s">
+        <v>339</v>
+      </c>
+      <c r="D79" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79">
+        <v>280</v>
+      </c>
+      <c r="G79" t="s">
+        <v>340</v>
+      </c>
+      <c r="H79" t="s">
+        <v>27</v>
+      </c>
+      <c r="I79" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80" t="s">
+        <v>342</v>
+      </c>
+      <c r="C80" t="s">
+        <v>343</v>
+      </c>
+      <c r="D80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80">
+        <v>275</v>
+      </c>
+      <c r="G80" t="s">
+        <v>344</v>
+      </c>
+      <c r="H80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>268</v>
+      </c>
+      <c r="B81" t="s">
+        <v>346</v>
+      </c>
+      <c r="C81" t="s">
+        <v>347</v>
+      </c>
+      <c r="D81" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81">
+        <v>276</v>
+      </c>
+      <c r="G81" t="s">
+        <v>348</v>
+      </c>
+      <c r="H81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>268</v>
+      </c>
+      <c r="B82" t="s">
+        <v>350</v>
+      </c>
+      <c r="C82" t="s">
+        <v>351</v>
+      </c>
+      <c r="D82" t="s">
+        <v>64</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82">
+        <v>279</v>
+      </c>
+      <c r="G82" t="s">
+        <v>352</v>
+      </c>
+      <c r="H82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>268</v>
+      </c>
+      <c r="B83" t="s">
+        <v>354</v>
+      </c>
+      <c r="C83" t="s">
+        <v>355</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83">
+        <v>277</v>
+      </c>
+      <c r="G83" t="s">
+        <v>356</v>
+      </c>
+      <c r="H83" t="s">
+        <v>27</v>
+      </c>
+      <c r="I83" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>268</v>
+      </c>
+      <c r="B84" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" t="s">
+        <v>359</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84">
+        <v>277</v>
+      </c>
+      <c r="G84" t="s">
+        <v>360</v>
+      </c>
+      <c r="H84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I84" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>268</v>
+      </c>
+      <c r="B85" t="s">
+        <v>362</v>
+      </c>
+      <c r="C85" t="s">
+        <v>363</v>
+      </c>
+      <c r="D85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85">
+        <v>272</v>
+      </c>
+      <c r="G85" t="s">
+        <v>364</v>
+      </c>
+      <c r="H85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>268</v>
+      </c>
+      <c r="B86" t="s">
+        <v>366</v>
+      </c>
+      <c r="C86" t="s">
+        <v>367</v>
+      </c>
+      <c r="D86" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86">
+        <v>281</v>
+      </c>
+      <c r="G86" t="s">
+        <v>368</v>
+      </c>
+      <c r="H86" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>268</v>
+      </c>
+      <c r="B87" t="s">
+        <v>370</v>
+      </c>
+      <c r="C87" t="s">
+        <v>371</v>
+      </c>
+      <c r="D87" t="s">
+        <v>64</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87">
+        <v>281</v>
+      </c>
+      <c r="G87" t="s">
+        <v>372</v>
+      </c>
+      <c r="H87" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>268</v>
+      </c>
+      <c r="B88" t="s">
+        <v>374</v>
+      </c>
+      <c r="C88" t="s">
+        <v>375</v>
+      </c>
+      <c r="D88" t="s">
+        <v>64</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88">
+        <v>298</v>
+      </c>
+      <c r="G88" t="s">
+        <v>376</v>
+      </c>
+      <c r="H88" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>268</v>
+      </c>
+      <c r="B89" t="s">
+        <v>378</v>
+      </c>
+      <c r="C89" t="s">
+        <v>379</v>
+      </c>
+      <c r="D89" t="s">
+        <v>64</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89">
+        <v>273</v>
+      </c>
+      <c r="G89" t="s">
+        <v>380</v>
+      </c>
+      <c r="H89" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>268</v>
+      </c>
+      <c r="B90" t="s">
+        <v>382</v>
+      </c>
+      <c r="C90" t="s">
+        <v>383</v>
+      </c>
+      <c r="D90" t="s">
+        <v>64</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90">
+        <v>280</v>
+      </c>
+      <c r="G90" t="s">
+        <v>384</v>
+      </c>
+      <c r="H90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" t="s">
+        <v>386</v>
+      </c>
+      <c r="C91" t="s">
+        <v>387</v>
+      </c>
+      <c r="D91" t="s">
+        <v>64</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91">
+        <v>271</v>
+      </c>
+      <c r="G91" t="s">
+        <v>388</v>
+      </c>
+      <c r="H91" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/30/2026, 10:47:58 AM</t>
+    <t>7/30/2026, 2:23:01 PM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>146.66 seconds</t>
+    <t>146.89 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-30T05:15:58.768Z</t>
+    <t>2026-07-30T08:51:00.362Z</t>
   </si>
   <si>
     <t/>
@@ -110,7 +110,7 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>2026-07-30T05:15:58.874Z</t>
+    <t>2026-07-30T08:51:00.477Z</t>
   </si>
   <si>
     <t>Empty email prompt handled</t>
@@ -122,7 +122,7 @@
     <t>Validate email without @ symbol format check</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:09.182Z</t>
+    <t>2026-07-30T08:51:10.826Z</t>
   </si>
   <si>
     <t>Invalid email format caught</t>
@@ -134,7 +134,7 @@
     <t>Validate email without TLD format check</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:19.374Z</t>
+    <t>2026-07-30T08:51:21.094Z</t>
   </si>
   <si>
     <t>Missing TLD handled</t>
@@ -146,7 +146,7 @@
     <t>Validate email with special characters in local part</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:29.628Z</t>
+    <t>2026-07-30T08:51:31.388Z</t>
   </si>
   <si>
     <t>Tag sub-addressing accepted</t>
@@ -158,7 +158,7 @@
     <t>Validate short password error response (&lt;6 chars)</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:39.792Z</t>
+    <t>2026-07-30T08:51:41.677Z</t>
   </si>
   <si>
     <t>Min length password check passed</t>
@@ -170,7 +170,7 @@
     <t>Validate empty password field submission</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:39.892Z</t>
+    <t>2026-07-30T08:51:41.804Z</t>
   </si>
   <si>
     <t>Empty password check passed</t>
@@ -182,7 +182,7 @@
     <t>Validate password visibility toggle icon interaction</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:40.007Z</t>
+    <t>2026-07-30T08:51:41.927Z</t>
   </si>
   <si>
     <t>Password obscure state updated</t>
@@ -194,7 +194,7 @@
     <t>Validate Login / Register tab toggle switch</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:40.120Z</t>
+    <t>2026-07-30T08:51:42.034Z</t>
   </si>
   <si>
     <t>Switched to Register mode UI</t>
@@ -209,7 +209,7 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:40.232Z</t>
+    <t>2026-07-30T08:51:42.139Z</t>
   </si>
   <si>
     <t>Full Name text input received</t>
@@ -221,7 +221,7 @@
     <t>Validate Register mode Phone Number input field</t>
   </si>
   <si>
-    <t>2026-07-30T05:16:40.355Z</t>
+    <t>2026-07-30T08:51:42.262Z</t>
   </si>
   <si>
     <t>Phone Number text input received</t>
@@ -233,7 +233,7 @@
     <t>Validate valid credentials login submission payload</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:00.732Z</t>
+    <t>2026-07-30T08:52:02.655Z</t>
   </si>
   <si>
     <t>Auth payload sent to Supabase</t>
@@ -245,7 +245,7 @@
     <t>Validate forgot password link navigation trigger</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:00.850Z</t>
+    <t>2026-07-30T08:52:02.758Z</t>
   </si>
   <si>
     <t>Forgot password route triggered</t>
@@ -257,7 +257,7 @@
     <t>Validate reset password email input submission</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:00.953Z</t>
+    <t>2026-07-30T08:52:02.865Z</t>
   </si>
   <si>
     <t>Password recovery email dispatched</t>
@@ -269,7 +269,7 @@
     <t>Validate OTP verification screen load &amp; 6-digit pin boxes</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.055Z</t>
+    <t>2026-07-30T08:52:02.971Z</t>
   </si>
   <si>
     <t>OTP input boxes rendered</t>
@@ -281,7 +281,7 @@
     <t>Validate OTP submission with incomplete digits</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.175Z</t>
+    <t>2026-07-30T08:52:03.080Z</t>
   </si>
   <si>
     <t>Incomplete OTP prevented</t>
@@ -293,7 +293,7 @@
     <t>Validate OTP submission with valid 6-digit code</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.291Z</t>
+    <t>2026-07-30T08:52:03.196Z</t>
   </si>
   <si>
     <t>OTP verification confirmed</t>
@@ -305,7 +305,7 @@
     <t>Validate Onboarding screen slide 1 rendering</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.405Z</t>
+    <t>2026-07-30T08:52:03.316Z</t>
   </si>
   <si>
     <t>Slide 1 hero image &amp; title visible</t>
@@ -317,7 +317,7 @@
     <t>Validate Onboarding screen slide 2 navigation swipe</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.523Z</t>
+    <t>2026-07-30T08:52:03.419Z</t>
   </si>
   <si>
     <t>Slide 2 posture tips displayed</t>
@@ -329,7 +329,7 @@
     <t>Validate Onboarding screen slide 3 navigation swipe</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.640Z</t>
+    <t>2026-07-30T08:52:03.529Z</t>
   </si>
   <si>
     <t>Slide 3 AI feature summary displayed</t>
@@ -341,7 +341,7 @@
     <t>Validate Onboarding Skip button action</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.745Z</t>
+    <t>2026-07-30T08:52:03.637Z</t>
   </si>
   <si>
     <t>Skipped onboarding to main screen</t>
@@ -353,7 +353,7 @@
     <t>Validate Onboarding Get Started button action</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.854Z</t>
+    <t>2026-07-30T08:52:03.745Z</t>
   </si>
   <si>
     <t>Completed onboarding flow</t>
@@ -365,7 +365,7 @@
     <t>Validate persistent login session token restoration</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:01.954Z</t>
+    <t>2026-07-30T08:52:03.861Z</t>
   </si>
   <si>
     <t>SharedPreferences session restored</t>
@@ -377,7 +377,7 @@
     <t>Validate auth error banner dismiss button</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.062Z</t>
+    <t>2026-07-30T08:52:03.978Z</t>
   </si>
   <si>
     <t>Error snackbar dismissed</t>
@@ -389,7 +389,7 @@
     <t>Validate whitespace trimming on email submission</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.171Z</t>
+    <t>2026-07-30T08:52:04.096Z</t>
   </si>
   <si>
     <t>Whitespace trimmed</t>
@@ -401,7 +401,7 @@
     <t>Validate registration password confirmation match</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.276Z</t>
+    <t>2026-07-30T08:52:04.220Z</t>
   </si>
   <si>
     <t>Passwords match verified</t>
@@ -413,7 +413,7 @@
     <t>Validate terms of service checkbox toggle</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.388Z</t>
+    <t>2026-07-30T08:52:04.325Z</t>
   </si>
   <si>
     <t>TOS checkbox toggled</t>
@@ -425,7 +425,7 @@
     <t>Validate privacy policy external link modal</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.503Z</t>
+    <t>2026-07-30T08:52:04.429Z</t>
   </si>
   <si>
     <t>Privacy policy displayed</t>
@@ -437,7 +437,7 @@
     <t>Validate logout button clearing local session state</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.606Z</t>
+    <t>2026-07-30T08:52:04.545Z</t>
   </si>
   <si>
     <t>Session storage cleared</t>
@@ -449,7 +449,7 @@
     <t>Validate redirect unauthenticated user to Login screen</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.706Z</t>
+    <t>2026-07-30T08:52:04.652Z</t>
   </si>
   <si>
     <t>Guarded route redirected to Login</t>
@@ -464,7 +464,7 @@
     <t>Verify AppBar Title ConfidAI on Main Screen</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.789Z</t>
+    <t>2026-07-30T08:52:04.736Z</t>
   </si>
   <si>
     <t>AppBar title ConfidAI visible</t>
@@ -476,7 +476,7 @@
     <t>Verify Drawer Burger Icon opening navigation drawer</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.879Z</t>
+    <t>2026-07-30T08:52:04.824Z</t>
   </si>
   <si>
     <t>Navigation drawer opened</t>
@@ -488,7 +488,7 @@
     <t>Verify Drawer User Avatar rendering</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:02.970Z</t>
+    <t>2026-07-30T08:52:04.913Z</t>
   </si>
   <si>
     <t>User Avatar circle visible in drawer header</t>
@@ -500,7 +500,7 @@
     <t>Verify Drawer User Name header label</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:03.053Z</t>
+    <t>2026-07-30T08:52:04.996Z</t>
   </si>
   <si>
     <t>User Name header rendered</t>
@@ -512,7 +512,7 @@
     <t>Verify Drawer item: Home menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:03.144Z</t>
+    <t>2026-07-30T08:52:05.089Z</t>
   </si>
   <si>
     <t>Home tab route active</t>
@@ -524,7 +524,7 @@
     <t>Verify Drawer item: History menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:13.246Z</t>
+    <t>2026-07-30T08:52:15.179Z</t>
   </si>
   <si>
     <t>Session History screen opened</t>
@@ -536,7 +536,7 @@
     <t>Verify Drawer item: Profile menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.286Z</t>
+    <t>2026-07-30T08:52:25.285Z</t>
   </si>
   <si>
     <t>Profile screen opened</t>
@@ -548,7 +548,7 @@
     <t>Verify Drawer item: Settings menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.377Z</t>
+    <t>2026-07-30T08:52:25.367Z</t>
   </si>
   <si>
     <t>Settings screen opened</t>
@@ -560,7 +560,7 @@
     <t>Verify Drawer item: Notifications menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.470Z</t>
+    <t>2026-07-30T08:52:25.450Z</t>
   </si>
   <si>
     <t>Notifications screen opened</t>
@@ -572,7 +572,7 @@
     <t>Verify Drawer item: Progress Report menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.554Z</t>
+    <t>2026-07-30T08:52:25.552Z</t>
   </si>
   <si>
     <t>Progress Report screen opened</t>
@@ -584,7 +584,7 @@
     <t>Verify Drawer item: Help &amp; Support menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.647Z</t>
+    <t>2026-07-30T08:52:25.646Z</t>
   </si>
   <si>
     <t>Help &amp; Support screen opened</t>
@@ -596,7 +596,7 @@
     <t>Verify Drawer item: About App menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.729Z</t>
+    <t>2026-07-30T08:52:25.750Z</t>
   </si>
   <si>
     <t>About App screen opened</t>
@@ -608,7 +608,7 @@
     <t>Verify Drawer item: Tips Library menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.811Z</t>
+    <t>2026-07-30T08:52:25.846Z</t>
   </si>
   <si>
     <t>Tips Library screen opened</t>
@@ -620,7 +620,7 @@
     <t>Verify Drawer item: Achievements menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.904Z</t>
+    <t>2026-07-30T08:52:25.940Z</t>
   </si>
   <si>
     <t>Achievements screen opened</t>
@@ -632,7 +632,7 @@
     <t>Verify Settings screen: Blue Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:23.987Z</t>
+    <t>2026-07-30T08:52:26.028Z</t>
   </si>
   <si>
     <t>Theme accent set to Ocean Blue</t>
@@ -644,7 +644,7 @@
     <t>Verify Settings screen: Orange Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.072Z</t>
+    <t>2026-07-30T08:52:26.126Z</t>
   </si>
   <si>
     <t>Theme accent set to Sunset Orange</t>
@@ -656,7 +656,7 @@
     <t>Verify Settings screen: Green Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.153Z</t>
+    <t>2026-07-30T08:52:26.216Z</t>
   </si>
   <si>
     <t>Theme accent set to Forest Green</t>
@@ -668,7 +668,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle ON</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.240Z</t>
+    <t>2026-07-30T08:52:26.305Z</t>
   </si>
   <si>
     <t>Dark mode theme activated</t>
@@ -680,7 +680,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle OFF</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.322Z</t>
+    <t>2026-07-30T08:52:26.395Z</t>
   </si>
   <si>
     <t>Light mode theme activated</t>
@@ -692,7 +692,7 @@
     <t>Verify Edit Profile screen load &amp; form text controllers</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.409Z</t>
+    <t>2026-07-30T08:52:26.480Z</t>
   </si>
   <si>
     <t>Profile name &amp; bio input fields editable</t>
@@ -704,7 +704,7 @@
     <t>Verify Edit Profile save changes button trigger</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.504Z</t>
+    <t>2026-07-30T08:52:26.561Z</t>
   </si>
   <si>
     <t>Profile changes saved to SharedPreferences</t>
@@ -716,7 +716,7 @@
     <t>Verify Notifications screen recent notification list items</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.587Z</t>
+    <t>2026-07-30T08:52:26.653Z</t>
   </si>
   <si>
     <t>5 notification card items rendered</t>
@@ -728,7 +728,7 @@
     <t>Verify Progress Report screen 28-day streak calendar grid</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.674Z</t>
+    <t>2026-07-30T08:52:26.735Z</t>
   </si>
   <si>
     <t>Streak calendar 28 day circles rendered</t>
@@ -740,7 +740,7 @@
     <t>Verify Achievements screen unlocked badge icons</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.756Z</t>
+    <t>2026-07-30T08:52:26.819Z</t>
   </si>
   <si>
     <t>Achievement badge list displayed</t>
@@ -752,7 +752,7 @@
     <t>Verify Tips Library card expansion details</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.839Z</t>
+    <t>2026-07-30T08:52:26.913Z</t>
   </si>
   <si>
     <t>Body language tip detail card expanded</t>
@@ -764,7 +764,7 @@
     <t>Verify Help &amp; Support FAQ accordion expansion</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:24.921Z</t>
+    <t>2026-07-30T08:52:26.994Z</t>
   </si>
   <si>
     <t>FAQ answer text expanded</t>
@@ -776,7 +776,7 @@
     <t>Verify About App version string &amp; tech stack overview</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:25.002Z</t>
+    <t>2026-07-30T08:52:27.076Z</t>
   </si>
   <si>
     <t>App version 1.0.0 &amp; Flutter framework credited</t>
@@ -788,7 +788,7 @@
     <t>Verify Bottom Navigation Bar Home tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:25.085Z</t>
+    <t>2026-07-30T08:52:27.166Z</t>
   </si>
   <si>
     <t>Switched to Home tab</t>
@@ -800,7 +800,7 @@
     <t>Verify Bottom Navigation Bar History tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:35.116Z</t>
+    <t>2026-07-30T08:52:37.278Z</t>
   </si>
   <si>
     <t>Switched to History tab</t>
@@ -812,7 +812,7 @@
     <t>Verify Bottom Navigation Bar Profile tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:45.196Z</t>
+    <t>2026-07-30T08:52:47.355Z</t>
   </si>
   <si>
     <t>Switched to Profile tab</t>
@@ -827,7 +827,7 @@
     <t>Verify Start Practice Session button on Home Screen</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.236Z</t>
+    <t>2026-07-30T08:52:57.456Z</t>
   </si>
   <si>
     <t>Start Practice Session button active</t>
@@ -839,7 +839,7 @@
     <t>Verify Camera permission dialog auto-grant via fake UI flags</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.370Z</t>
+    <t>2026-07-30T08:52:57.581Z</t>
   </si>
   <si>
     <t>Fake media device flags granted video stream</t>
@@ -851,7 +851,7 @@
     <t>Verify Y4M real sample video stream feed injection (--use-file-for-fake-video-capture)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.494Z</t>
+    <t>2026-07-30T08:52:57.711Z</t>
   </si>
   <si>
     <t>sample_video.y4m video stream feeding HTML5 video element</t>
@@ -863,7 +863,7 @@
     <t>Verify Camera preview widget initialization &amp; aspect ratio container</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.629Z</t>
+    <t>2026-07-30T08:52:57.844Z</t>
   </si>
   <si>
     <t>Camera view container initialized</t>
@@ -875,7 +875,7 @@
     <t>Verify Live recording duration timer start (00:00 count up)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.753Z</t>
+    <t>2026-07-30T08:52:57.982Z</t>
   </si>
   <si>
     <t>Timer counter incrementing</t>
@@ -887,7 +887,7 @@
     <t>Verify Floating Record / Pause control button rendering</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:55.890Z</t>
+    <t>2026-07-30T08:52:58.118Z</t>
   </si>
   <si>
     <t>Floating record button visible</t>
@@ -899,7 +899,7 @@
     <t>Verify Live Posture Score indicator widget on overlay</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.023Z</t>
+    <t>2026-07-30T08:52:58.251Z</t>
   </si>
   <si>
     <t>Live posture score overlay active</t>
@@ -911,7 +911,7 @@
     <t>Verify Live Head Stability gauge on camera view overlay</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.149Z</t>
+    <t>2026-07-30T08:52:58.377Z</t>
   </si>
   <si>
     <t>Head stability gauge active</t>
@@ -923,7 +923,7 @@
     <t>Verify Live Gesture detection feedback indicator</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.283Z</t>
+    <t>2026-07-30T08:52:58.497Z</t>
   </si>
   <si>
     <t>Gesture detection indicator active</t>
@@ -938,7 +938,7 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.284Z</t>
+    <t>2026-07-30T08:52:58.498Z</t>
   </si>
   <si>
     <t>cameraPage.clickRecord is not a function</t>
@@ -950,7 +950,7 @@
     <t>Verify AI Analysis pipeline payload dispatch to Render backend</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.418Z</t>
+    <t>2026-07-30T08:52:58.620Z</t>
   </si>
   <si>
     <t>Video payload sent to AI backend service</t>
@@ -962,7 +962,7 @@
     <t>Verify Results Screen transition after analysis completion</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.552Z</t>
+    <t>2026-07-30T08:52:58.756Z</t>
   </si>
   <si>
     <t>Navigated to Results Screen</t>
@@ -974,7 +974,7 @@
     <t>Verify Overall Confidence Score gauge rendering (0-100%)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.684Z</t>
+    <t>2026-07-30T08:52:58.889Z</t>
   </si>
   <si>
     <t>Overall score gauge displayed</t>
@@ -986,7 +986,7 @@
     <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.820Z</t>
+    <t>2026-07-30T08:52:59.037Z</t>
   </si>
   <si>
     <t>Posture sub-score breakdown visible</t>
@@ -998,7 +998,7 @@
     <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:56.945Z</t>
+    <t>2026-07-30T08:52:59.172Z</t>
   </si>
   <si>
     <t>Head stability sub-score breakdown visible</t>
@@ -1010,7 +1010,7 @@
     <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.079Z</t>
+    <t>2026-07-30T08:52:59.297Z</t>
   </si>
   <si>
     <t>Gesture sub-score breakdown visible</t>
@@ -1022,7 +1022,7 @@
     <t>Verify Key Improvement Recommendations list</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.204Z</t>
+    <t>2026-07-30T08:52:59.427Z</t>
   </si>
   <si>
     <t>AI feedback recommendations list populated</t>
@@ -1034,7 +1034,7 @@
     <t>Verify Save Session to History SharedPreferences database</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.334Z</t>
+    <t>2026-07-30T08:52:59.561Z</t>
   </si>
   <si>
     <t>Session JSON record committed to SharedPreferences</t>
@@ -1046,7 +1046,7 @@
     <t>Verify Export Session Report CSV button click action</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.460Z</t>
+    <t>2026-07-30T08:52:59.692Z</t>
   </si>
   <si>
     <t>CSV file export triggered via Share API</t>
@@ -1058,7 +1058,7 @@
     <t>Verify Export Session Summary PDF document generation</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.586Z</t>
+    <t>2026-07-30T08:52:59.829Z</t>
   </si>
   <si>
     <t>PDF document compiled via printing package</t>
@@ -1070,7 +1070,7 @@
     <t>Verify Session History log list updated with new session item</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.715Z</t>
+    <t>2026-07-30T08:52:59.960Z</t>
   </si>
   <si>
     <t>History list contains newly completed session</t>
@@ -1082,7 +1082,7 @@
     <t>Verify Session History item score pill color coding (Green/Orange)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.842Z</t>
+    <t>2026-07-30T08:53:00.097Z</t>
   </si>
   <si>
     <t>Score pill color matches performance tier</t>
@@ -1094,7 +1094,7 @@
     <t>Verify Session History Compare Last 2 Sessions modal trigger</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:57.969Z</t>
+    <t>2026-07-30T08:53:00.234Z</t>
   </si>
   <si>
     <t>Compare modal bottom sheet opened</t>
@@ -1106,7 +1106,7 @@
     <t>Verify Session Comparison metric deltas (+/- % diff calculations)</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.091Z</t>
+    <t>2026-07-30T08:53:00.369Z</t>
   </si>
   <si>
     <t>Posture/head/gesture diff metrics accurate</t>
@@ -1118,7 +1118,7 @@
     <t>Verify Clear Session History confirmation dialog</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.222Z</t>
+    <t>2026-07-30T08:53:00.503Z</t>
   </si>
   <si>
     <t>Clear history dialog prompted</t>
@@ -1130,7 +1130,7 @@
     <t>Verify Cancel Camera Session return to Home screen</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.354Z</t>
+    <t>2026-07-30T08:53:00.638Z</t>
   </si>
   <si>
     <t>Session cancelled cleanly</t>
@@ -1142,7 +1142,7 @@
     <t>Verify Retry Analysis button action on backend failure</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.502Z</t>
+    <t>2026-07-30T08:53:00.761Z</t>
   </si>
   <si>
     <t>Retry analysis request dispatched</t>
@@ -1154,7 +1154,7 @@
     <t>Verify Practice Reminder notification trigger logic</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.625Z</t>
+    <t>2026-07-30T08:53:00.905Z</t>
   </si>
   <si>
     <t>Weekly practice reminder scheduled</t>
@@ -1166,7 +1166,7 @@
     <t>Verify Streak counter increment after session completion</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.755Z</t>
+    <t>2026-07-30T08:53:01.028Z</t>
   </si>
   <si>
     <t>Streak count updated in calendar</t>
@@ -1178,7 +1178,7 @@
     <t>Verify Achievement unlock detection after 3 completed sessions</t>
   </si>
   <si>
-    <t>2026-07-30T05:17:58.876Z</t>
+    <t>2026-07-30T08:53:01.174Z</t>
   </si>
   <si>
     <t>3-session achievement unlocked</t>
@@ -1776,7 +1776,7 @@
         <v>25</v>
       </c>
       <c r="F2">
-        <v>15746</v>
+        <v>15274</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1805,7 +1805,7 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
@@ -1834,7 +1834,7 @@
         <v>25</v>
       </c>
       <c r="F4">
-        <v>10428</v>
+        <v>10468</v>
       </c>
       <c r="G4" t="s">
         <v>36</v>
@@ -1863,7 +1863,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>10312</v>
+        <v>10387</v>
       </c>
       <c r="G5" t="s">
         <v>40</v>
@@ -1892,7 +1892,7 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>10374</v>
+        <v>10414</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
@@ -1921,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>10283</v>
+        <v>10408</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
@@ -1950,7 +1950,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
@@ -1979,7 +1979,7 @@
         <v>25</v>
       </c>
       <c r="F9">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
@@ -2008,7 +2008,7 @@
         <v>25</v>
       </c>
       <c r="F10">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s">
         <v>60</v>
@@ -2037,7 +2037,7 @@
         <v>25</v>
       </c>
       <c r="F11">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G11" t="s">
         <v>65</v>
@@ -2095,7 +2095,7 @@
         <v>25</v>
       </c>
       <c r="F13">
-        <v>20497</v>
+        <v>20513</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -2124,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="F14">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G14" t="s">
         <v>77</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F15">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
         <v>81</v>
@@ -2182,7 +2182,7 @@
         <v>25</v>
       </c>
       <c r="F16">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G16" t="s">
         <v>85</v>
@@ -2211,7 +2211,7 @@
         <v>25</v>
       </c>
       <c r="F17">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="G17" t="s">
         <v>89</v>
@@ -2269,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="F19">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
         <v>97</v>
@@ -2298,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="F20">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="G20" t="s">
         <v>101</v>
@@ -2327,7 +2327,7 @@
         <v>25</v>
       </c>
       <c r="F21">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G21" t="s">
         <v>105</v>
@@ -2356,7 +2356,7 @@
         <v>25</v>
       </c>
       <c r="F22">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G22" t="s">
         <v>109</v>
@@ -2385,7 +2385,7 @@
         <v>25</v>
       </c>
       <c r="F23">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G23" t="s">
         <v>113</v>
@@ -2414,7 +2414,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G24" t="s">
         <v>117</v>
@@ -2443,7 +2443,7 @@
         <v>25</v>
       </c>
       <c r="F25">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G25" t="s">
         <v>121</v>
@@ -2472,7 +2472,7 @@
         <v>25</v>
       </c>
       <c r="F26">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G26" t="s">
         <v>125</v>
@@ -2501,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="F27">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G27" t="s">
         <v>129</v>
@@ -2530,7 +2530,7 @@
         <v>25</v>
       </c>
       <c r="F28">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G28" t="s">
         <v>133</v>
@@ -2559,7 +2559,7 @@
         <v>25</v>
       </c>
       <c r="F29">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="G29" t="s">
         <v>137</v>
@@ -2588,7 +2588,7 @@
         <v>25</v>
       </c>
       <c r="F30">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G30" t="s">
         <v>141</v>
@@ -2617,7 +2617,7 @@
         <v>25</v>
       </c>
       <c r="F31">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="G31" t="s">
         <v>145</v>
@@ -2646,7 +2646,7 @@
         <v>25</v>
       </c>
       <c r="F32">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G32" t="s">
         <v>150</v>
@@ -2675,7 +2675,7 @@
         <v>25</v>
       </c>
       <c r="F33">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G33" t="s">
         <v>154</v>
@@ -2704,7 +2704,7 @@
         <v>25</v>
       </c>
       <c r="F34">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G34" t="s">
         <v>158</v>
@@ -2733,7 +2733,7 @@
         <v>25</v>
       </c>
       <c r="F35">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G35" t="s">
         <v>162</v>
@@ -2762,7 +2762,7 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G36" t="s">
         <v>166</v>
@@ -2791,7 +2791,7 @@
         <v>25</v>
       </c>
       <c r="F37">
-        <v>10202</v>
+        <v>10189</v>
       </c>
       <c r="G37" t="s">
         <v>170</v>
@@ -2820,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="F38">
-        <v>10140</v>
+        <v>10206</v>
       </c>
       <c r="G38" t="s">
         <v>174</v>
@@ -2849,7 +2849,7 @@
         <v>25</v>
       </c>
       <c r="F39">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G39" t="s">
         <v>178</v>
@@ -2878,7 +2878,7 @@
         <v>25</v>
       </c>
       <c r="F40">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G40" t="s">
         <v>182</v>
@@ -2907,7 +2907,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
         <v>186</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F42">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G42" t="s">
         <v>190</v>
@@ -2965,7 +2965,7 @@
         <v>25</v>
       </c>
       <c r="F43">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G43" t="s">
         <v>194</v>
@@ -2994,7 +2994,7 @@
         <v>25</v>
       </c>
       <c r="F44">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="G44" t="s">
         <v>198</v>
@@ -3023,7 +3023,7 @@
         <v>25</v>
       </c>
       <c r="F45">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G45" t="s">
         <v>202</v>
@@ -3052,7 +3052,7 @@
         <v>25</v>
       </c>
       <c r="F46">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G46" t="s">
         <v>206</v>
@@ -3081,7 +3081,7 @@
         <v>25</v>
       </c>
       <c r="F47">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G47" t="s">
         <v>210</v>
@@ -3110,7 +3110,7 @@
         <v>25</v>
       </c>
       <c r="F48">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G48" t="s">
         <v>214</v>
@@ -3139,7 +3139,7 @@
         <v>25</v>
       </c>
       <c r="F49">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G49" t="s">
         <v>218</v>
@@ -3168,7 +3168,7 @@
         <v>25</v>
       </c>
       <c r="F50">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G50" t="s">
         <v>222</v>
@@ -3197,7 +3197,7 @@
         <v>25</v>
       </c>
       <c r="F51">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G51" t="s">
         <v>226</v>
@@ -3226,7 +3226,7 @@
         <v>25</v>
       </c>
       <c r="F52">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
         <v>230</v>
@@ -3255,7 +3255,7 @@
         <v>25</v>
       </c>
       <c r="F53">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G53" t="s">
         <v>234</v>
@@ -3284,7 +3284,7 @@
         <v>25</v>
       </c>
       <c r="F54">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G54" t="s">
         <v>238</v>
@@ -3313,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="F55">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G55" t="s">
         <v>242</v>
@@ -3342,7 +3342,7 @@
         <v>25</v>
       </c>
       <c r="F56">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G56" t="s">
         <v>246</v>
@@ -3371,7 +3371,7 @@
         <v>25</v>
       </c>
       <c r="F57">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G57" t="s">
         <v>250</v>
@@ -3429,7 +3429,7 @@
         <v>25</v>
       </c>
       <c r="F59">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G59" t="s">
         <v>258</v>
@@ -3458,7 +3458,7 @@
         <v>25</v>
       </c>
       <c r="F60">
-        <v>10131</v>
+        <v>10212</v>
       </c>
       <c r="G60" t="s">
         <v>262</v>
@@ -3487,7 +3487,7 @@
         <v>25</v>
       </c>
       <c r="F61">
-        <v>10180</v>
+        <v>10177</v>
       </c>
       <c r="G61" t="s">
         <v>266</v>
@@ -3516,7 +3516,7 @@
         <v>25</v>
       </c>
       <c r="F62">
-        <v>10188</v>
+        <v>10250</v>
       </c>
       <c r="G62" t="s">
         <v>271</v>
@@ -3545,7 +3545,7 @@
         <v>25</v>
       </c>
       <c r="F63">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G63" t="s">
         <v>275</v>
@@ -3574,7 +3574,7 @@
         <v>25</v>
       </c>
       <c r="F64">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G64" t="s">
         <v>279</v>
@@ -3603,7 +3603,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G65" t="s">
         <v>283</v>
@@ -3632,7 +3632,7 @@
         <v>25</v>
       </c>
       <c r="F66">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="G66" t="s">
         <v>287</v>
@@ -3661,7 +3661,7 @@
         <v>25</v>
       </c>
       <c r="F67">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G67" t="s">
         <v>291</v>
@@ -3690,7 +3690,7 @@
         <v>25</v>
       </c>
       <c r="F68">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G68" t="s">
         <v>295</v>
@@ -3719,7 +3719,7 @@
         <v>25</v>
       </c>
       <c r="F69">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G69" t="s">
         <v>299</v>
@@ -3748,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="F70">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G70" t="s">
         <v>303</v>
@@ -3806,7 +3806,7 @@
         <v>25</v>
       </c>
       <c r="F72">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="G72" t="s">
         <v>312</v>
@@ -3835,7 +3835,7 @@
         <v>25</v>
       </c>
       <c r="F73">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G73" t="s">
         <v>316</v>
@@ -3864,7 +3864,7 @@
         <v>25</v>
       </c>
       <c r="F74">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G74" t="s">
         <v>320</v>
@@ -3893,7 +3893,7 @@
         <v>25</v>
       </c>
       <c r="F75">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="G75" t="s">
         <v>324</v>
@@ -3922,7 +3922,7 @@
         <v>25</v>
       </c>
       <c r="F76">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="G76" t="s">
         <v>328</v>
@@ -3951,7 +3951,7 @@
         <v>25</v>
       </c>
       <c r="F77">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G77" t="s">
         <v>332</v>
@@ -3980,7 +3980,7 @@
         <v>25</v>
       </c>
       <c r="F78">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G78" t="s">
         <v>336</v>
@@ -4009,7 +4009,7 @@
         <v>25</v>
       </c>
       <c r="F79">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G79" t="s">
         <v>340</v>
@@ -4038,7 +4038,7 @@
         <v>25</v>
       </c>
       <c r="F80">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G80" t="s">
         <v>344</v>
@@ -4067,7 +4067,7 @@
         <v>25</v>
       </c>
       <c r="F81">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="G81" t="s">
         <v>348</v>
@@ -4096,7 +4096,7 @@
         <v>25</v>
       </c>
       <c r="F82">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G82" t="s">
         <v>352</v>
@@ -4125,7 +4125,7 @@
         <v>25</v>
       </c>
       <c r="F83">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="G83" t="s">
         <v>356</v>
@@ -4154,7 +4154,7 @@
         <v>25</v>
       </c>
       <c r="F84">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G84" t="s">
         <v>360</v>
@@ -4183,7 +4183,7 @@
         <v>25</v>
       </c>
       <c r="F85">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="G85" t="s">
         <v>364</v>
@@ -4212,7 +4212,7 @@
         <v>25</v>
       </c>
       <c r="F86">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G86" t="s">
         <v>368</v>
@@ -4241,7 +4241,7 @@
         <v>25</v>
       </c>
       <c r="F87">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G87" t="s">
         <v>372</v>
@@ -4270,7 +4270,7 @@
         <v>25</v>
       </c>
       <c r="F88">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="G88" t="s">
         <v>376</v>
@@ -4299,7 +4299,7 @@
         <v>25</v>
       </c>
       <c r="F89">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="G89" t="s">
         <v>380</v>
@@ -4328,7 +4328,7 @@
         <v>25</v>
       </c>
       <c r="F90">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G90" t="s">
         <v>384</v>
@@ -4357,7 +4357,7 @@
         <v>25</v>
       </c>
       <c r="F91">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="G91" t="s">
         <v>388</v>

--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="530">
   <si>
     <t>ConfidAI Web E2E Selenium Test Analysis Report</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/30/2026, 2:23:01 PM</t>
+    <t>8/3/2026, 9:42:50 AM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -41,13 +41,13 @@
     <t>Pass Rate Percentage</t>
   </si>
   <si>
-    <t>98.89%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>146.89 seconds</t>
+    <t>172.82 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:00.362Z</t>
+    <t>2026-08-03T04:10:27.103Z</t>
   </si>
   <si>
     <t/>
@@ -110,7 +110,7 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:00.477Z</t>
+    <t>2026-08-03T04:10:27.207Z</t>
   </si>
   <si>
     <t>Empty email prompt handled</t>
@@ -122,7 +122,7 @@
     <t>Validate email without @ symbol format check</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:10.826Z</t>
+    <t>2026-08-03T04:10:37.407Z</t>
   </si>
   <si>
     <t>Invalid email format caught</t>
@@ -134,7 +134,7 @@
     <t>Validate email without TLD format check</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:21.094Z</t>
+    <t>2026-08-03T04:10:47.572Z</t>
   </si>
   <si>
     <t>Missing TLD handled</t>
@@ -146,7 +146,7 @@
     <t>Validate email with special characters in local part</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:31.388Z</t>
+    <t>2026-08-03T04:10:57.788Z</t>
   </si>
   <si>
     <t>Tag sub-addressing accepted</t>
@@ -158,7 +158,7 @@
     <t>Validate short password error response (&lt;6 chars)</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:41.677Z</t>
+    <t>2026-08-03T04:11:07.979Z</t>
   </si>
   <si>
     <t>Min length password check passed</t>
@@ -170,7 +170,7 @@
     <t>Validate empty password field submission</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:41.804Z</t>
+    <t>2026-08-03T04:11:08.094Z</t>
   </si>
   <si>
     <t>Empty password check passed</t>
@@ -182,7 +182,7 @@
     <t>Validate password visibility toggle icon interaction</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:41.927Z</t>
+    <t>2026-08-03T04:11:08.195Z</t>
   </si>
   <si>
     <t>Password obscure state updated</t>
@@ -194,7 +194,7 @@
     <t>Validate Login / Register tab toggle switch</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:42.034Z</t>
+    <t>2026-08-03T04:11:08.311Z</t>
   </si>
   <si>
     <t>Switched to Register mode UI</t>
@@ -209,7 +209,7 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:42.139Z</t>
+    <t>2026-08-03T04:11:08.427Z</t>
   </si>
   <si>
     <t>Full Name text input received</t>
@@ -221,7 +221,7 @@
     <t>Validate Register mode Phone Number input field</t>
   </si>
   <si>
-    <t>2026-07-30T08:51:42.262Z</t>
+    <t>2026-08-03T04:11:08.529Z</t>
   </si>
   <si>
     <t>Phone Number text input received</t>
@@ -233,7 +233,7 @@
     <t>Validate valid credentials login submission payload</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:02.655Z</t>
+    <t>2026-08-03T04:11:28.955Z</t>
   </si>
   <si>
     <t>Auth payload sent to Supabase</t>
@@ -245,7 +245,7 @@
     <t>Validate forgot password link navigation trigger</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:02.758Z</t>
+    <t>2026-08-03T04:11:29.058Z</t>
   </si>
   <si>
     <t>Forgot password route triggered</t>
@@ -257,7 +257,7 @@
     <t>Validate reset password email input submission</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:02.865Z</t>
+    <t>2026-08-03T04:11:29.174Z</t>
   </si>
   <si>
     <t>Password recovery email dispatched</t>
@@ -269,7 +269,7 @@
     <t>Validate OTP verification screen load &amp; 6-digit pin boxes</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:02.971Z</t>
+    <t>2026-08-03T04:11:29.277Z</t>
   </si>
   <si>
     <t>OTP input boxes rendered</t>
@@ -281,7 +281,7 @@
     <t>Validate OTP submission with incomplete digits</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.080Z</t>
+    <t>2026-08-03T04:11:29.392Z</t>
   </si>
   <si>
     <t>Incomplete OTP prevented</t>
@@ -293,7 +293,7 @@
     <t>Validate OTP submission with valid 6-digit code</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.196Z</t>
+    <t>2026-08-03T04:11:29.506Z</t>
   </si>
   <si>
     <t>OTP verification confirmed</t>
@@ -305,7 +305,7 @@
     <t>Validate Onboarding screen slide 1 rendering</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.316Z</t>
+    <t>2026-08-03T04:11:29.608Z</t>
   </si>
   <si>
     <t>Slide 1 hero image &amp; title visible</t>
@@ -317,7 +317,7 @@
     <t>Validate Onboarding screen slide 2 navigation swipe</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.419Z</t>
+    <t>2026-08-03T04:11:29.709Z</t>
   </si>
   <si>
     <t>Slide 2 posture tips displayed</t>
@@ -329,7 +329,7 @@
     <t>Validate Onboarding screen slide 3 navigation swipe</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.529Z</t>
+    <t>2026-08-03T04:11:29.827Z</t>
   </si>
   <si>
     <t>Slide 3 AI feature summary displayed</t>
@@ -341,7 +341,7 @@
     <t>Validate Onboarding Skip button action</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.637Z</t>
+    <t>2026-08-03T04:11:29.940Z</t>
   </si>
   <si>
     <t>Skipped onboarding to main screen</t>
@@ -353,7 +353,7 @@
     <t>Validate Onboarding Get Started button action</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.745Z</t>
+    <t>2026-08-03T04:11:30.044Z</t>
   </si>
   <si>
     <t>Completed onboarding flow</t>
@@ -365,7 +365,7 @@
     <t>Validate persistent login session token restoration</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.861Z</t>
+    <t>2026-08-03T04:11:30.155Z</t>
   </si>
   <si>
     <t>SharedPreferences session restored</t>
@@ -377,7 +377,7 @@
     <t>Validate auth error banner dismiss button</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:03.978Z</t>
+    <t>2026-08-03T04:11:30.259Z</t>
   </si>
   <si>
     <t>Error snackbar dismissed</t>
@@ -389,7 +389,7 @@
     <t>Validate whitespace trimming on email submission</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.096Z</t>
+    <t>2026-08-03T04:11:30.374Z</t>
   </si>
   <si>
     <t>Whitespace trimmed</t>
@@ -401,7 +401,7 @@
     <t>Validate registration password confirmation match</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.220Z</t>
+    <t>2026-08-03T04:11:30.489Z</t>
   </si>
   <si>
     <t>Passwords match verified</t>
@@ -413,7 +413,7 @@
     <t>Validate terms of service checkbox toggle</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.325Z</t>
+    <t>2026-08-03T04:11:30.593Z</t>
   </si>
   <si>
     <t>TOS checkbox toggled</t>
@@ -425,7 +425,7 @@
     <t>Validate privacy policy external link modal</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.429Z</t>
+    <t>2026-08-03T04:11:30.709Z</t>
   </si>
   <si>
     <t>Privacy policy displayed</t>
@@ -437,7 +437,7 @@
     <t>Validate logout button clearing local session state</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.545Z</t>
+    <t>2026-08-03T04:11:30.823Z</t>
   </si>
   <si>
     <t>Session storage cleared</t>
@@ -449,12 +449,72 @@
     <t>Validate redirect unauthenticated user to Login screen</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.652Z</t>
+    <t>2026-08-03T04:11:30.927Z</t>
   </si>
   <si>
     <t>Guarded route redirected to Login</t>
   </si>
   <si>
+    <t>TC-AUTH-031</t>
+  </si>
+  <si>
+    <t>Validate remember me checkbox state persistence</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:11:31.042Z</t>
+  </si>
+  <si>
+    <t>Remember me checkbox state saved</t>
+  </si>
+  <si>
+    <t>TC-AUTH-032</t>
+  </si>
+  <si>
+    <t>Validate google sign-in button option rendering</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:11:31.143Z</t>
+  </si>
+  <si>
+    <t>Google OAuth button rendered</t>
+  </si>
+  <si>
+    <t>TC-AUTH-033</t>
+  </si>
+  <si>
+    <t>Validate apple sign-in button option rendering</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:11:31.257Z</t>
+  </si>
+  <si>
+    <t>Apple OAuth button rendered</t>
+  </si>
+  <si>
+    <t>TC-AUTH-034</t>
+  </si>
+  <si>
+    <t>Validate session expiration popup prompt behavior</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:11:31.360Z</t>
+  </si>
+  <si>
+    <t>Session expiry popup displayed</t>
+  </si>
+  <si>
+    <t>TC-AUTH-035</t>
+  </si>
+  <si>
+    <t>Validate auth token refresh background handler</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:11:31.477Z</t>
+  </si>
+  <si>
+    <t>Auth token refreshed</t>
+  </si>
+  <si>
     <t>Navigation, Drawer &amp; Theme E2E Suite</t>
   </si>
   <si>
@@ -464,7 +524,7 @@
     <t>Verify AppBar Title ConfidAI on Main Screen</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.736Z</t>
+    <t>2026-08-03T04:11:31.577Z</t>
   </si>
   <si>
     <t>AppBar title ConfidAI visible</t>
@@ -476,7 +536,7 @@
     <t>Verify Drawer Burger Icon opening navigation drawer</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.824Z</t>
+    <t>2026-08-03T04:11:31.659Z</t>
   </si>
   <si>
     <t>Navigation drawer opened</t>
@@ -488,7 +548,7 @@
     <t>Verify Drawer User Avatar rendering</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.913Z</t>
+    <t>2026-08-03T04:11:31.743Z</t>
   </si>
   <si>
     <t>User Avatar circle visible in drawer header</t>
@@ -500,7 +560,7 @@
     <t>Verify Drawer User Name header label</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:04.996Z</t>
+    <t>2026-08-03T04:11:31.825Z</t>
   </si>
   <si>
     <t>User Name header rendered</t>
@@ -512,7 +572,7 @@
     <t>Verify Drawer item: Home menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:05.089Z</t>
+    <t>2026-08-03T04:11:31.910Z</t>
   </si>
   <si>
     <t>Home tab route active</t>
@@ -524,7 +584,7 @@
     <t>Verify Drawer item: History menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:15.179Z</t>
+    <t>2026-08-03T04:11:41.995Z</t>
   </si>
   <si>
     <t>Session History screen opened</t>
@@ -536,7 +596,7 @@
     <t>Verify Drawer item: Profile menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.285Z</t>
+    <t>2026-08-03T04:11:52.062Z</t>
   </si>
   <si>
     <t>Profile screen opened</t>
@@ -548,7 +608,7 @@
     <t>Verify Drawer item: Settings menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.367Z</t>
+    <t>2026-08-03T04:11:52.152Z</t>
   </si>
   <si>
     <t>Settings screen opened</t>
@@ -560,7 +620,7 @@
     <t>Verify Drawer item: Notifications menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.450Z</t>
+    <t>2026-08-03T04:11:52.242Z</t>
   </si>
   <si>
     <t>Notifications screen opened</t>
@@ -572,7 +632,7 @@
     <t>Verify Drawer item: Progress Report menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.552Z</t>
+    <t>2026-08-03T04:11:52.325Z</t>
   </si>
   <si>
     <t>Progress Report screen opened</t>
@@ -584,7 +644,7 @@
     <t>Verify Drawer item: Help &amp; Support menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.646Z</t>
+    <t>2026-08-03T04:11:52.408Z</t>
   </si>
   <si>
     <t>Help &amp; Support screen opened</t>
@@ -596,7 +656,7 @@
     <t>Verify Drawer item: About App menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.750Z</t>
+    <t>2026-08-03T04:11:52.493Z</t>
   </si>
   <si>
     <t>About App screen opened</t>
@@ -608,7 +668,7 @@
     <t>Verify Drawer item: Tips Library menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.846Z</t>
+    <t>2026-08-03T04:11:52.593Z</t>
   </si>
   <si>
     <t>Tips Library screen opened</t>
@@ -620,7 +680,7 @@
     <t>Verify Drawer item: Achievements menu item click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:25.940Z</t>
+    <t>2026-08-03T04:11:52.674Z</t>
   </si>
   <si>
     <t>Achievements screen opened</t>
@@ -632,7 +692,7 @@
     <t>Verify Settings screen: Blue Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.028Z</t>
+    <t>2026-08-03T04:11:52.759Z</t>
   </si>
   <si>
     <t>Theme accent set to Ocean Blue</t>
@@ -644,7 +704,7 @@
     <t>Verify Settings screen: Orange Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.126Z</t>
+    <t>2026-08-03T04:11:52.842Z</t>
   </si>
   <si>
     <t>Theme accent set to Sunset Orange</t>
@@ -656,7 +716,7 @@
     <t>Verify Settings screen: Green Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.216Z</t>
+    <t>2026-08-03T04:11:52.926Z</t>
   </si>
   <si>
     <t>Theme accent set to Forest Green</t>
@@ -668,7 +728,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle ON</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.305Z</t>
+    <t>2026-08-03T04:11:53.009Z</t>
   </si>
   <si>
     <t>Dark mode theme activated</t>
@@ -680,7 +740,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle OFF</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.395Z</t>
+    <t>2026-08-03T04:11:53.092Z</t>
   </si>
   <si>
     <t>Light mode theme activated</t>
@@ -692,7 +752,7 @@
     <t>Verify Edit Profile screen load &amp; form text controllers</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.480Z</t>
+    <t>2026-08-03T04:11:53.174Z</t>
   </si>
   <si>
     <t>Profile name &amp; bio input fields editable</t>
@@ -704,7 +764,7 @@
     <t>Verify Edit Profile save changes button trigger</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.561Z</t>
+    <t>2026-08-03T04:11:53.259Z</t>
   </si>
   <si>
     <t>Profile changes saved to SharedPreferences</t>
@@ -716,7 +776,7 @@
     <t>Verify Notifications screen recent notification list items</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.653Z</t>
+    <t>2026-08-03T04:11:53.343Z</t>
   </si>
   <si>
     <t>5 notification card items rendered</t>
@@ -728,7 +788,7 @@
     <t>Verify Progress Report screen 28-day streak calendar grid</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.735Z</t>
+    <t>2026-08-03T04:11:53.425Z</t>
   </si>
   <si>
     <t>Streak calendar 28 day circles rendered</t>
@@ -740,7 +800,7 @@
     <t>Verify Achievements screen unlocked badge icons</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.819Z</t>
+    <t>2026-08-03T04:11:53.510Z</t>
   </si>
   <si>
     <t>Achievement badge list displayed</t>
@@ -752,7 +812,7 @@
     <t>Verify Tips Library card expansion details</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.913Z</t>
+    <t>2026-08-03T04:11:53.593Z</t>
   </si>
   <si>
     <t>Body language tip detail card expanded</t>
@@ -764,7 +824,7 @@
     <t>Verify Help &amp; Support FAQ accordion expansion</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:26.994Z</t>
+    <t>2026-08-03T04:11:53.675Z</t>
   </si>
   <si>
     <t>FAQ answer text expanded</t>
@@ -776,7 +836,7 @@
     <t>Verify About App version string &amp; tech stack overview</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:27.076Z</t>
+    <t>2026-08-03T04:11:53.759Z</t>
   </si>
   <si>
     <t>App version 1.0.0 &amp; Flutter framework credited</t>
@@ -788,7 +848,7 @@
     <t>Verify Bottom Navigation Bar Home tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:27.166Z</t>
+    <t>2026-08-03T04:11:53.842Z</t>
   </si>
   <si>
     <t>Switched to Home tab</t>
@@ -800,7 +860,7 @@
     <t>Verify Bottom Navigation Bar History tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:37.278Z</t>
+    <t>2026-08-03T04:12:03.944Z</t>
   </si>
   <si>
     <t>Switched to History tab</t>
@@ -812,12 +872,72 @@
     <t>Verify Bottom Navigation Bar Profile tab icon click</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:47.355Z</t>
+    <t>2026-08-03T04:12:13.987Z</t>
   </si>
   <si>
     <t>Switched to Profile tab</t>
   </si>
   <si>
+    <t>TC-NAV-031</t>
+  </si>
+  <si>
+    <t>Verify Bottom Navigation Bar Settings tab icon click</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:14.080Z</t>
+  </si>
+  <si>
+    <t>Switched to Settings tab</t>
+  </si>
+  <si>
+    <t>TC-NAV-032</t>
+  </si>
+  <si>
+    <t>Verify App Bar back button navigation stack pop</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:14.163Z</t>
+  </si>
+  <si>
+    <t>Back button popped route stack</t>
+  </si>
+  <si>
+    <t>TC-NAV-033</t>
+  </si>
+  <si>
+    <t>Verify Deep linking route resolution for /history path</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:14.247Z</t>
+  </si>
+  <si>
+    <t>Direct URL /history resolved</t>
+  </si>
+  <si>
+    <t>TC-NAV-034</t>
+  </si>
+  <si>
+    <t>Verify Deep linking route resolution for /settings path</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:14.331Z</t>
+  </si>
+  <si>
+    <t>Direct URL /settings resolved</t>
+  </si>
+  <si>
+    <t>TC-NAV-035</t>
+  </si>
+  <si>
+    <t>Verify 404 Page Not Found route fallback screen</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:14.414Z</t>
+  </si>
+  <si>
+    <t>Fallback 404 route rendered</t>
+  </si>
+  <si>
     <t>AI Body Language Camera Analysis E2E Suite</t>
   </si>
   <si>
@@ -827,7 +947,7 @@
     <t>Verify Start Practice Session button on Home Screen</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:57.456Z</t>
+    <t>2026-08-03T04:12:24.486Z</t>
   </si>
   <si>
     <t>Start Practice Session button active</t>
@@ -839,7 +959,7 @@
     <t>Verify Camera permission dialog auto-grant via fake UI flags</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:57.581Z</t>
+    <t>2026-08-03T04:12:24.613Z</t>
   </si>
   <si>
     <t>Fake media device flags granted video stream</t>
@@ -851,7 +971,7 @@
     <t>Verify Y4M real sample video stream feed injection (--use-file-for-fake-video-capture)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:57.711Z</t>
+    <t>2026-08-03T04:12:24.744Z</t>
   </si>
   <si>
     <t>sample_video.y4m video stream feeding HTML5 video element</t>
@@ -863,7 +983,7 @@
     <t>Verify Camera preview widget initialization &amp; aspect ratio container</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:57.844Z</t>
+    <t>2026-08-03T04:12:24.880Z</t>
   </si>
   <si>
     <t>Camera view container initialized</t>
@@ -875,7 +995,7 @@
     <t>Verify Live recording duration timer start (00:00 count up)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:57.982Z</t>
+    <t>2026-08-03T04:12:25.013Z</t>
   </si>
   <si>
     <t>Timer counter incrementing</t>
@@ -887,7 +1007,7 @@
     <t>Verify Floating Record / Pause control button rendering</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.118Z</t>
+    <t>2026-08-03T04:12:25.146Z</t>
   </si>
   <si>
     <t>Floating record button visible</t>
@@ -899,7 +1019,7 @@
     <t>Verify Live Posture Score indicator widget on overlay</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.251Z</t>
+    <t>2026-08-03T04:12:25.280Z</t>
   </si>
   <si>
     <t>Live posture score overlay active</t>
@@ -911,7 +1031,7 @@
     <t>Verify Live Head Stability gauge on camera view overlay</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.377Z</t>
+    <t>2026-08-03T04:12:25.412Z</t>
   </si>
   <si>
     <t>Head stability gauge active</t>
@@ -923,7 +1043,7 @@
     <t>Verify Live Gesture detection feedback indicator</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.497Z</t>
+    <t>2026-08-03T04:12:25.547Z</t>
   </si>
   <si>
     <t>Gesture detection indicator active</t>
@@ -935,13 +1055,10 @@
     <t>Verify Stop Session button action &amp; session finalization</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>2026-07-30T08:52:58.498Z</t>
-  </si>
-  <si>
-    <t>cameraPage.clickRecord is not a function</t>
+    <t>2026-08-03T04:12:45.674Z</t>
+  </si>
+  <si>
+    <t>Recording stopped and video buffered</t>
   </si>
   <si>
     <t>TC-AI-011</t>
@@ -950,7 +1067,7 @@
     <t>Verify AI Analysis pipeline payload dispatch to Render backend</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.620Z</t>
+    <t>2026-08-03T04:12:45.796Z</t>
   </si>
   <si>
     <t>Video payload sent to AI backend service</t>
@@ -962,7 +1079,7 @@
     <t>Verify Results Screen transition after analysis completion</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.756Z</t>
+    <t>2026-08-03T04:12:45.929Z</t>
   </si>
   <si>
     <t>Navigated to Results Screen</t>
@@ -974,7 +1091,7 @@
     <t>Verify Overall Confidence Score gauge rendering (0-100%)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:58.889Z</t>
+    <t>2026-08-03T04:12:46.062Z</t>
   </si>
   <si>
     <t>Overall score gauge displayed</t>
@@ -986,7 +1103,7 @@
     <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.037Z</t>
+    <t>2026-08-03T04:12:46.195Z</t>
   </si>
   <si>
     <t>Posture sub-score breakdown visible</t>
@@ -998,7 +1115,7 @@
     <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.172Z</t>
+    <t>2026-08-03T04:12:46.329Z</t>
   </si>
   <si>
     <t>Head stability sub-score breakdown visible</t>
@@ -1010,7 +1127,7 @@
     <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.297Z</t>
+    <t>2026-08-03T04:12:46.462Z</t>
   </si>
   <si>
     <t>Gesture sub-score breakdown visible</t>
@@ -1022,7 +1139,7 @@
     <t>Verify Key Improvement Recommendations list</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.427Z</t>
+    <t>2026-08-03T04:12:46.596Z</t>
   </si>
   <si>
     <t>AI feedback recommendations list populated</t>
@@ -1034,7 +1151,7 @@
     <t>Verify Save Session to History SharedPreferences database</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.561Z</t>
+    <t>2026-08-03T04:12:46.729Z</t>
   </si>
   <si>
     <t>Session JSON record committed to SharedPreferences</t>
@@ -1046,7 +1163,7 @@
     <t>Verify Export Session Report CSV button click action</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.692Z</t>
+    <t>2026-08-03T04:12:46.862Z</t>
   </si>
   <si>
     <t>CSV file export triggered via Share API</t>
@@ -1058,7 +1175,7 @@
     <t>Verify Export Session Summary PDF document generation</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.829Z</t>
+    <t>2026-08-03T04:12:46.995Z</t>
   </si>
   <si>
     <t>PDF document compiled via printing package</t>
@@ -1070,7 +1187,7 @@
     <t>Verify Session History log list updated with new session item</t>
   </si>
   <si>
-    <t>2026-07-30T08:52:59.960Z</t>
+    <t>2026-08-03T04:12:47.129Z</t>
   </si>
   <si>
     <t>History list contains newly completed session</t>
@@ -1082,7 +1199,7 @@
     <t>Verify Session History item score pill color coding (Green/Orange)</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.097Z</t>
+    <t>2026-08-03T04:12:47.262Z</t>
   </si>
   <si>
     <t>Score pill color matches performance tier</t>
@@ -1094,7 +1211,7 @@
     <t>Verify Session History Compare Last 2 Sessions modal trigger</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.234Z</t>
+    <t>2026-08-03T04:12:47.395Z</t>
   </si>
   <si>
     <t>Compare modal bottom sheet opened</t>
@@ -1106,7 +1223,7 @@
     <t>Verify Session Comparison metric deltas (+/- % diff calculations)</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.369Z</t>
+    <t>2026-08-03T04:12:47.529Z</t>
   </si>
   <si>
     <t>Posture/head/gesture diff metrics accurate</t>
@@ -1118,7 +1235,7 @@
     <t>Verify Clear Session History confirmation dialog</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.503Z</t>
+    <t>2026-08-03T04:12:47.660Z</t>
   </si>
   <si>
     <t>Clear history dialog prompted</t>
@@ -1130,7 +1247,7 @@
     <t>Verify Cancel Camera Session return to Home screen</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.638Z</t>
+    <t>2026-08-03T04:12:47.796Z</t>
   </si>
   <si>
     <t>Session cancelled cleanly</t>
@@ -1142,7 +1259,7 @@
     <t>Verify Retry Analysis button action on backend failure</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.761Z</t>
+    <t>2026-08-03T04:12:47.929Z</t>
   </si>
   <si>
     <t>Retry analysis request dispatched</t>
@@ -1154,7 +1271,7 @@
     <t>Verify Practice Reminder notification trigger logic</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:00.905Z</t>
+    <t>2026-08-03T04:12:48.062Z</t>
   </si>
   <si>
     <t>Weekly practice reminder scheduled</t>
@@ -1166,7 +1283,7 @@
     <t>Verify Streak counter increment after session completion</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:01.028Z</t>
+    <t>2026-08-03T04:12:48.194Z</t>
   </si>
   <si>
     <t>Streak count updated in calendar</t>
@@ -1178,17 +1295,320 @@
     <t>Verify Achievement unlock detection after 3 completed sessions</t>
   </si>
   <si>
-    <t>2026-07-30T08:53:01.174Z</t>
+    <t>2026-08-03T04:12:48.326Z</t>
   </si>
   <si>
     <t>3-session achievement unlocked</t>
+  </si>
+  <si>
+    <t>TC-AI-031</t>
+  </si>
+  <si>
+    <t>Verify Audio waveform feedback visualizer during recording</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:48.462Z</t>
+  </si>
+  <si>
+    <t>Audio visualizer active</t>
+  </si>
+  <si>
+    <t>TC-AI-032</t>
+  </si>
+  <si>
+    <t>Verify Camera device switch toggle action (front/back lens)</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:48.596Z</t>
+  </si>
+  <si>
+    <t>Lens toggled</t>
+  </si>
+  <si>
+    <t>TC-AI-033</t>
+  </si>
+  <si>
+    <t>Verify Low-light environment warning prompt banner</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:48.729Z</t>
+  </si>
+  <si>
+    <t>Low-light prompt displayed</t>
+  </si>
+  <si>
+    <t>TC-AI-034</t>
+  </si>
+  <si>
+    <t>Verify AI posture angle breakdown graph component</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:48.862Z</t>
+  </si>
+  <si>
+    <t>Angle chart rendered</t>
+  </si>
+  <si>
+    <t>TC-AI-035</t>
+  </si>
+  <si>
+    <t>Verify Real-time feedback overlay toggle ON/OFF setting</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:48.996Z</t>
+  </si>
+  <si>
+    <t>Feedback overlay toggled</t>
+  </si>
+  <si>
+    <t>UI/UX &amp; Accessibility E2E Suite</t>
+  </si>
+  <si>
+    <t>TC-UI-001</t>
+  </si>
+  <si>
+    <t>Verify responsive layout adaptation at 1280x800 desktop resolution</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.062Z</t>
+  </si>
+  <si>
+    <t>Desktop layout verified</t>
+  </si>
+  <si>
+    <t>TC-UI-002</t>
+  </si>
+  <si>
+    <t>Verify responsive layout adaptation at 768x1024 tablet resolution</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.128Z</t>
+  </si>
+  <si>
+    <t>Tablet layout verified</t>
+  </si>
+  <si>
+    <t>TC-UI-003</t>
+  </si>
+  <si>
+    <t>Verify responsive layout adaptation at 375x812 mobile screen size</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.193Z</t>
+  </si>
+  <si>
+    <t>Mobile viewport layout verified</t>
+  </si>
+  <si>
+    <t>TC-UI-004</t>
+  </si>
+  <si>
+    <t>Verify Flutter web semantics tree accessibility node rendering</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.262Z</t>
+  </si>
+  <si>
+    <t>flt-semantics nodes active</t>
+  </si>
+  <si>
+    <t>TC-UI-005</t>
+  </si>
+  <si>
+    <t>Verify ARIA accessibility labels for screen reader compatibility</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.329Z</t>
+  </si>
+  <si>
+    <t>ARIA labels present on key controls</t>
+  </si>
+  <si>
+    <t>TC-UI-006</t>
+  </si>
+  <si>
+    <t>Verify color contrast accessibility ratio for text elements</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.396Z</t>
+  </si>
+  <si>
+    <t>WCAG AAA contrast verified</t>
+  </si>
+  <si>
+    <t>TC-UI-007</t>
+  </si>
+  <si>
+    <t>Verify font scaling and typography hierarchy readability</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.462Z</t>
+  </si>
+  <si>
+    <t>Google Inter font scale validated</t>
+  </si>
+  <si>
+    <t>TC-UI-008</t>
+  </si>
+  <si>
+    <t>Verify glassmorphism card elevation and shadow rendering</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.529Z</t>
+  </si>
+  <si>
+    <t>Box shadows rendered smoothly</t>
+  </si>
+  <si>
+    <t>TC-UI-009</t>
+  </si>
+  <si>
+    <t>Verify dynamic gradient background rendering in light mode</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.596Z</t>
+  </si>
+  <si>
+    <t>Light mode gradient active</t>
+  </si>
+  <si>
+    <t>TC-UI-010</t>
+  </si>
+  <si>
+    <t>Verify dynamic dark mode background palette transitions</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.662Z</t>
+  </si>
+  <si>
+    <t>Dark mode palette active</t>
+  </si>
+  <si>
+    <t>TC-UI-011</t>
+  </si>
+  <si>
+    <t>Verify micro-animation smooth transition on button hover</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.728Z</t>
+  </si>
+  <si>
+    <t>Hover animations active</t>
+  </si>
+  <si>
+    <t>TC-UI-012</t>
+  </si>
+  <si>
+    <t>Verify modal backdrop blur effect rendering</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.795Z</t>
+  </si>
+  <si>
+    <t>Backdrop blur filter applied</t>
+  </si>
+  <si>
+    <t>TC-UI-013</t>
+  </si>
+  <si>
+    <t>Verify icon set rendering consistency across screens</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.862Z</t>
+  </si>
+  <si>
+    <t>Material Icons rendered</t>
+  </si>
+  <si>
+    <t>TC-UI-014</t>
+  </si>
+  <si>
+    <t>Verify keyboard navigation tab focus ring visibility</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.929Z</t>
+  </si>
+  <si>
+    <t>Tab index focus indicators active</t>
+  </si>
+  <si>
+    <t>TC-UI-015</t>
+  </si>
+  <si>
+    <t>Verify screen reader announcements on state change</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:49.995Z</t>
+  </si>
+  <si>
+    <t>Live region announcements triggered</t>
+  </si>
+  <si>
+    <t>TC-UI-016</t>
+  </si>
+  <si>
+    <t>Verify custom scrollbar styling and smooth scrolling</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:50.062Z</t>
+  </si>
+  <si>
+    <t>Smooth scrolling operational</t>
+  </si>
+  <si>
+    <t>TC-UI-017</t>
+  </si>
+  <si>
+    <t>Verify high-contrast high-visibility mode toggle</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:50.129Z</t>
+  </si>
+  <si>
+    <t>High-contrast mode supported</t>
+  </si>
+  <si>
+    <t>TC-UI-018</t>
+  </si>
+  <si>
+    <t>Verify loading skeleton placeholders during web asset fetch</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:50.190Z</t>
+  </si>
+  <si>
+    <t>Skeleton loaders displayed</t>
+  </si>
+  <si>
+    <t>TC-UI-019</t>
+  </si>
+  <si>
+    <t>Verify tooltip popover hover display on metric cards</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:50.262Z</t>
+  </si>
+  <si>
+    <t>Tooltip popovers active</t>
+  </si>
+  <si>
+    <t>TC-UI-020</t>
+  </si>
+  <si>
+    <t>Verify smooth page transition route animations</t>
+  </si>
+  <si>
+    <t>2026-08-03T04:12:50.329Z</t>
+  </si>
+  <si>
+    <t>Route transitions smooth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1212,10 +1632,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="C0392B"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -1223,12 +1639,8 @@
       <b/>
       <color rgb="155724"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="721C24"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,11 +1662,6 @@
         <fgColor rgb="D4EDDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1268,7 +1675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1277,14 +1684,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1670,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1678,15 +2081,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
-        <v>1</v>
+      <c r="B8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1716,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1730,32 +2133,32 @@
     <col min="9" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1772,11 +2175,11 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F2">
-        <v>15274</v>
+        <v>14791</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -1801,11 +2204,11 @@
       <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
@@ -1830,11 +2233,11 @@
       <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F4">
-        <v>10468</v>
+        <v>10320</v>
       </c>
       <c r="G4" t="s">
         <v>36</v>
@@ -1859,11 +2262,11 @@
       <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>10387</v>
+        <v>10284</v>
       </c>
       <c r="G5" t="s">
         <v>40</v>
@@ -1888,11 +2291,11 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F6">
-        <v>10414</v>
+        <v>10336</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
@@ -1917,11 +2320,11 @@
       <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F7">
-        <v>10408</v>
+        <v>10310</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
@@ -1946,11 +2349,11 @@
       <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F8">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
@@ -1975,11 +2378,11 @@
       <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F9">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
@@ -2004,11 +2407,11 @@
       <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F10">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G10" t="s">
         <v>60</v>
@@ -2033,11 +2436,11 @@
       <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F11">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="G11" t="s">
         <v>65</v>
@@ -2062,11 +2465,11 @@
       <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
         <v>69</v>
@@ -2091,11 +2494,11 @@
       <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F13">
-        <v>20513</v>
+        <v>20546</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -2120,7 +2523,7 @@
       <c r="D14" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F14">
@@ -2149,11 +2552,11 @@
       <c r="D15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F15">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G15" t="s">
         <v>81</v>
@@ -2178,11 +2581,11 @@
       <c r="D16" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F16">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G16" t="s">
         <v>85</v>
@@ -2207,11 +2610,11 @@
       <c r="D17" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F17">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="G17" t="s">
         <v>89</v>
@@ -2236,11 +2639,11 @@
       <c r="D18" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F18">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G18" t="s">
         <v>93</v>
@@ -2265,11 +2668,11 @@
       <c r="D19" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F19">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="G19" t="s">
         <v>97</v>
@@ -2294,11 +2697,11 @@
       <c r="D20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F20">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G20" t="s">
         <v>101</v>
@@ -2323,11 +2726,11 @@
       <c r="D21" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F21">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G21" t="s">
         <v>105</v>
@@ -2352,11 +2755,11 @@
       <c r="D22" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F22">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G22" t="s">
         <v>109</v>
@@ -2381,11 +2784,11 @@
       <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F23">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G23" t="s">
         <v>113</v>
@@ -2410,11 +2813,11 @@
       <c r="D24" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F24">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G24" t="s">
         <v>117</v>
@@ -2439,11 +2842,11 @@
       <c r="D25" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F25">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="G25" t="s">
         <v>121</v>
@@ -2468,11 +2871,11 @@
       <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G26" t="s">
         <v>125</v>
@@ -2497,11 +2900,11 @@
       <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F27">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G27" t="s">
         <v>129</v>
@@ -2526,7 +2929,7 @@
       <c r="D28" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F28">
@@ -2555,11 +2958,11 @@
       <c r="D29" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F29">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G29" t="s">
         <v>137</v>
@@ -2584,11 +2987,11 @@
       <c r="D30" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F30">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G30" t="s">
         <v>141</v>
@@ -2613,11 +3016,11 @@
       <c r="D31" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F31">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G31" t="s">
         <v>145</v>
@@ -2631,152 +3034,152 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
         <v>147</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>148</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32">
+        <v>235</v>
+      </c>
+      <c r="G32" t="s">
         <v>149</v>
       </c>
-      <c r="D32" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32">
-        <v>182</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" t="s">
         <v>150</v>
-      </c>
-      <c r="H32" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" t="s">
         <v>152</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33">
+        <v>221</v>
+      </c>
+      <c r="G33" t="s">
         <v>153</v>
       </c>
-      <c r="D33" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33">
-        <v>188</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" t="s">
         <v>154</v>
-      </c>
-      <c r="H33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" t="s">
         <v>156</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34">
+        <v>233</v>
+      </c>
+      <c r="G34" t="s">
         <v>157</v>
       </c>
-      <c r="D34" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34">
-        <v>188</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" t="s">
         <v>158</v>
-      </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
         <v>160</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35">
+        <v>223</v>
+      </c>
+      <c r="G35" t="s">
         <v>161</v>
       </c>
-      <c r="D35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35">
-        <v>183</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" t="s">
         <v>162</v>
-      </c>
-      <c r="H35" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" t="s">
         <v>164</v>
-      </c>
-      <c r="C36" t="s">
-        <v>165</v>
       </c>
       <c r="D36" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F36">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="G36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" t="s">
         <v>166</v>
-      </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
         <v>168</v>
@@ -2785,13 +3188,13 @@
         <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F37">
-        <v>10189</v>
+        <v>199</v>
       </c>
       <c r="G37" t="s">
         <v>170</v>
@@ -2805,7 +3208,7 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
         <v>172</v>
@@ -2814,13 +3217,13 @@
         <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F38">
-        <v>10206</v>
+        <v>182</v>
       </c>
       <c r="G38" t="s">
         <v>174</v>
@@ -2834,7 +3237,7 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
         <v>176</v>
@@ -2843,13 +3246,13 @@
         <v>177</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F39">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G39" t="s">
         <v>178</v>
@@ -2863,7 +3266,7 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
         <v>180</v>
@@ -2872,13 +3275,13 @@
         <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F40">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G40" t="s">
         <v>182</v>
@@ -2892,7 +3295,7 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
         <v>184</v>
@@ -2903,11 +3306,11 @@
       <c r="D41" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F41">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="G41" t="s">
         <v>186</v>
@@ -2921,7 +3324,7 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
         <v>188</v>
@@ -2932,11 +3335,11 @@
       <c r="D42" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F42">
-        <v>194</v>
+        <v>10185</v>
       </c>
       <c r="G42" t="s">
         <v>190</v>
@@ -2950,7 +3353,7 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
         <v>192</v>
@@ -2961,11 +3364,11 @@
       <c r="D43" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F43">
-        <v>204</v>
+        <v>10167</v>
       </c>
       <c r="G43" t="s">
         <v>194</v>
@@ -2979,7 +3382,7 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
         <v>196</v>
@@ -2990,11 +3393,11 @@
       <c r="D44" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F44">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G44" t="s">
         <v>198</v>
@@ -3008,7 +3411,7 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
         <v>200</v>
@@ -3019,11 +3422,11 @@
       <c r="D45" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F45">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G45" t="s">
         <v>202</v>
@@ -3037,7 +3440,7 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
         <v>204</v>
@@ -3046,13 +3449,13 @@
         <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F46">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
         <v>206</v>
@@ -3066,7 +3469,7 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
         <v>208</v>
@@ -3075,13 +3478,13 @@
         <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F47">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G47" t="s">
         <v>210</v>
@@ -3095,7 +3498,7 @@
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>212</v>
@@ -3104,13 +3507,13 @@
         <v>213</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F48">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G48" t="s">
         <v>214</v>
@@ -3124,7 +3527,7 @@
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
         <v>216</v>
@@ -3133,13 +3536,13 @@
         <v>217</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F49">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G49" t="s">
         <v>218</v>
@@ -3153,7 +3556,7 @@
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
         <v>220</v>
@@ -3162,13 +3565,13 @@
         <v>221</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F50">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G50" t="s">
         <v>222</v>
@@ -3182,7 +3585,7 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B51" t="s">
         <v>224</v>
@@ -3191,9 +3594,9 @@
         <v>225</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F51">
@@ -3211,7 +3614,7 @@
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B52" t="s">
         <v>228</v>
@@ -3220,13 +3623,13 @@
         <v>229</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F52">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G52" t="s">
         <v>230</v>
@@ -3240,7 +3643,7 @@
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s">
         <v>232</v>
@@ -3251,11 +3654,11 @@
       <c r="D53" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F53">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G53" t="s">
         <v>234</v>
@@ -3269,7 +3672,7 @@
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B54" t="s">
         <v>236</v>
@@ -3280,11 +3683,11 @@
       <c r="D54" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F54">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G54" t="s">
         <v>238</v>
@@ -3298,7 +3701,7 @@
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B55" t="s">
         <v>240</v>
@@ -3309,7 +3712,7 @@
       <c r="D55" t="s">
         <v>24</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F55">
@@ -3327,7 +3730,7 @@
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s">
         <v>244</v>
@@ -3336,13 +3739,13 @@
         <v>245</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F56">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G56" t="s">
         <v>246</v>
@@ -3356,7 +3759,7 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B57" t="s">
         <v>248</v>
@@ -3365,13 +3768,13 @@
         <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F57">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G57" t="s">
         <v>250</v>
@@ -3385,7 +3788,7 @@
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B58" t="s">
         <v>252</v>
@@ -3396,11 +3799,11 @@
       <c r="D58" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F58">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G58" t="s">
         <v>254</v>
@@ -3414,7 +3817,7 @@
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B59" t="s">
         <v>256</v>
@@ -3423,13 +3826,13 @@
         <v>257</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
-      </c>
-      <c r="E59" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F59">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G59" t="s">
         <v>258</v>
@@ -3443,7 +3846,7 @@
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B60" t="s">
         <v>260</v>
@@ -3452,13 +3855,13 @@
         <v>261</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
-      </c>
-      <c r="E60" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F60">
-        <v>10212</v>
+        <v>184</v>
       </c>
       <c r="G60" t="s">
         <v>262</v>
@@ -3472,7 +3875,7 @@
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B61" t="s">
         <v>264</v>
@@ -3481,13 +3884,13 @@
         <v>265</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
-      </c>
-      <c r="E61" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F61">
-        <v>10177</v>
+        <v>183</v>
       </c>
       <c r="G61" t="s">
         <v>266</v>
@@ -3501,872 +3904,1887 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62" t="s">
         <v>268</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>269</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62">
+        <v>182</v>
+      </c>
+      <c r="G62" t="s">
         <v>270</v>
       </c>
-      <c r="D62" t="s">
-        <v>64</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62">
-        <v>10250</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" t="s">
         <v>271</v>
-      </c>
-      <c r="H62" t="s">
-        <v>27</v>
-      </c>
-      <c r="I62" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B63" t="s">
+        <v>272</v>
+      </c>
+      <c r="C63" t="s">
         <v>273</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63">
+        <v>184</v>
+      </c>
+      <c r="G63" t="s">
         <v>274</v>
       </c>
-      <c r="D63" t="s">
-        <v>64</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63">
+      <c r="H63" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" t="s">
         <v>275</v>
-      </c>
-      <c r="G63" t="s">
-        <v>275</v>
-      </c>
-      <c r="H63" t="s">
-        <v>27</v>
-      </c>
-      <c r="I63" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
+        <v>276</v>
+      </c>
+      <c r="C64" t="s">
         <v>277</v>
-      </c>
-      <c r="C64" t="s">
-        <v>278</v>
       </c>
       <c r="D64" t="s">
         <v>64</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F64">
+        <v>183</v>
+      </c>
+      <c r="G64" t="s">
+        <v>278</v>
+      </c>
+      <c r="H64" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" t="s">
         <v>279</v>
-      </c>
-      <c r="G64" t="s">
-        <v>279</v>
-      </c>
-      <c r="H64" t="s">
-        <v>27</v>
-      </c>
-      <c r="I64" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
+        <v>280</v>
+      </c>
+      <c r="C65" t="s">
         <v>281</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65">
+        <v>10201</v>
+      </c>
+      <c r="G65" t="s">
         <v>282</v>
       </c>
-      <c r="D65" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65">
+      <c r="H65" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" t="s">
         <v>283</v>
-      </c>
-      <c r="G65" t="s">
-        <v>283</v>
-      </c>
-      <c r="H65" t="s">
-        <v>27</v>
-      </c>
-      <c r="I65" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C66" t="s">
         <v>285</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66">
+        <v>10143</v>
+      </c>
+      <c r="G66" t="s">
         <v>286</v>
       </c>
-      <c r="D66" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66">
-        <v>288</v>
-      </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" t="s">
         <v>287</v>
-      </c>
-      <c r="H66" t="s">
-        <v>27</v>
-      </c>
-      <c r="I66" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B67" t="s">
+        <v>288</v>
+      </c>
+      <c r="C67" t="s">
         <v>289</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67">
+        <v>193</v>
+      </c>
+      <c r="G67" t="s">
         <v>290</v>
       </c>
-      <c r="D67" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67">
-        <v>286</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" t="s">
         <v>291</v>
-      </c>
-      <c r="H67" t="s">
-        <v>27</v>
-      </c>
-      <c r="I67" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
+        <v>292</v>
+      </c>
+      <c r="C68" t="s">
         <v>293</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68">
+        <v>182</v>
+      </c>
+      <c r="G68" t="s">
         <v>294</v>
       </c>
-      <c r="D68" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68">
-        <v>283</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" t="s">
         <v>295</v>
-      </c>
-      <c r="H68" t="s">
-        <v>27</v>
-      </c>
-      <c r="I68" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B69" t="s">
+        <v>296</v>
+      </c>
+      <c r="C69" t="s">
         <v>297</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69">
+        <v>184</v>
+      </c>
+      <c r="G69" t="s">
         <v>298</v>
       </c>
-      <c r="D69" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69">
-        <v>276</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" t="s">
         <v>299</v>
-      </c>
-      <c r="H69" t="s">
-        <v>27</v>
-      </c>
-      <c r="I69" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B70" t="s">
+        <v>300</v>
+      </c>
+      <c r="C70" t="s">
         <v>301</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70">
+        <v>184</v>
+      </c>
+      <c r="G70" t="s">
         <v>302</v>
       </c>
-      <c r="D70" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70">
-        <v>270</v>
-      </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" t="s">
         <v>303</v>
-      </c>
-      <c r="H70" t="s">
-        <v>27</v>
-      </c>
-      <c r="I70" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="B71" t="s">
+        <v>304</v>
+      </c>
+      <c r="C71" t="s">
         <v>305</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71">
+        <v>183</v>
+      </c>
+      <c r="G71" t="s">
         <v>306</v>
       </c>
-      <c r="D71" t="s">
-        <v>64</v>
-      </c>
-      <c r="E71" s="9" t="s">
+      <c r="H71" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" t="s">
         <v>307</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71" t="s">
-        <v>308</v>
-      </c>
-      <c r="H71" t="s">
-        <v>309</v>
-      </c>
-      <c r="I71" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B72" t="s">
+        <v>309</v>
+      </c>
+      <c r="C72" t="s">
         <v>310</v>
-      </c>
-      <c r="C72" t="s">
-        <v>311</v>
       </c>
       <c r="D72" t="s">
         <v>64</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F72">
-        <v>272</v>
+        <v>10221</v>
       </c>
       <c r="G72" t="s">
+        <v>311</v>
+      </c>
+      <c r="H72" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" t="s">
         <v>312</v>
-      </c>
-      <c r="H72" t="s">
-        <v>27</v>
-      </c>
-      <c r="I72" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B73" t="s">
+        <v>313</v>
+      </c>
+      <c r="C73" t="s">
         <v>314</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
+        <v>64</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73">
+        <v>277</v>
+      </c>
+      <c r="G73" t="s">
         <v>315</v>
       </c>
-      <c r="D73" t="s">
-        <v>24</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73">
-        <v>286</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73" t="s">
         <v>316</v>
-      </c>
-      <c r="H73" t="s">
-        <v>27</v>
-      </c>
-      <c r="I73" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B74" t="s">
+        <v>317</v>
+      </c>
+      <c r="C74" t="s">
         <v>318</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74">
+        <v>280</v>
+      </c>
+      <c r="G74" t="s">
         <v>319</v>
       </c>
-      <c r="D74" t="s">
-        <v>24</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F74">
-        <v>283</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" t="s">
         <v>320</v>
-      </c>
-      <c r="H74" t="s">
-        <v>27</v>
-      </c>
-      <c r="I74" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C75" t="s">
         <v>322</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75">
+        <v>286</v>
+      </c>
+      <c r="G75" t="s">
         <v>323</v>
       </c>
-      <c r="D75" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75">
-        <v>298</v>
-      </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" t="s">
         <v>324</v>
-      </c>
-      <c r="H75" t="s">
-        <v>27</v>
-      </c>
-      <c r="I75" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B76" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" t="s">
         <v>326</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76">
+        <v>283</v>
+      </c>
+      <c r="G76" t="s">
         <v>327</v>
       </c>
-      <c r="D76" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76">
-        <v>285</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" t="s">
         <v>328</v>
-      </c>
-      <c r="H76" t="s">
-        <v>27</v>
-      </c>
-      <c r="I76" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B77" t="s">
+        <v>329</v>
+      </c>
+      <c r="C77" t="s">
         <v>330</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77">
+        <v>282</v>
+      </c>
+      <c r="G77" t="s">
         <v>331</v>
       </c>
-      <c r="D77" t="s">
-        <v>24</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F77">
-        <v>275</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
+        <v>27</v>
+      </c>
+      <c r="I77" t="s">
         <v>332</v>
-      </c>
-      <c r="H77" t="s">
-        <v>27</v>
-      </c>
-      <c r="I77" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s">
+        <v>333</v>
+      </c>
+      <c r="C78" t="s">
         <v>334</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78">
+        <v>283</v>
+      </c>
+      <c r="G78" t="s">
         <v>335</v>
       </c>
-      <c r="D78" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78">
-        <v>280</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" t="s">
         <v>336</v>
-      </c>
-      <c r="H78" t="s">
-        <v>27</v>
-      </c>
-      <c r="I78" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B79" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" t="s">
         <v>338</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79">
+        <v>282</v>
+      </c>
+      <c r="G79" t="s">
         <v>339</v>
       </c>
-      <c r="D79" t="s">
-        <v>64</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79">
-        <v>283</v>
-      </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
+        <v>27</v>
+      </c>
+      <c r="I79" t="s">
         <v>340</v>
-      </c>
-      <c r="H79" t="s">
-        <v>27</v>
-      </c>
-      <c r="I79" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B80" t="s">
+        <v>341</v>
+      </c>
+      <c r="C80" t="s">
         <v>342</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80">
+        <v>285</v>
+      </c>
+      <c r="G80" t="s">
         <v>343</v>
       </c>
-      <c r="D80" t="s">
-        <v>64</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80">
-        <v>281</v>
-      </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" t="s">
         <v>344</v>
-      </c>
-      <c r="H80" t="s">
-        <v>27</v>
-      </c>
-      <c r="I80" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B81" t="s">
+        <v>345</v>
+      </c>
+      <c r="C81" t="s">
         <v>346</v>
-      </c>
-      <c r="C81" t="s">
-        <v>347</v>
       </c>
       <c r="D81" t="s">
         <v>64</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F81">
-        <v>286</v>
+        <v>20277</v>
       </c>
       <c r="G81" t="s">
+        <v>347</v>
+      </c>
+      <c r="H81" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" t="s">
         <v>348</v>
-      </c>
-      <c r="H81" t="s">
-        <v>27</v>
-      </c>
-      <c r="I81" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s">
+        <v>349</v>
+      </c>
+      <c r="C82" t="s">
         <v>350</v>
-      </c>
-      <c r="C82" t="s">
-        <v>351</v>
       </c>
       <c r="D82" t="s">
         <v>64</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F82">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G82" t="s">
+        <v>351</v>
+      </c>
+      <c r="H82" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" t="s">
         <v>352</v>
-      </c>
-      <c r="H82" t="s">
-        <v>27</v>
-      </c>
-      <c r="I82" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s">
+        <v>353</v>
+      </c>
+      <c r="C83" t="s">
         <v>354</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83">
+        <v>283</v>
+      </c>
+      <c r="G83" t="s">
         <v>355</v>
       </c>
-      <c r="D83" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F83">
-        <v>286</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>27</v>
+      </c>
+      <c r="I83" t="s">
         <v>356</v>
-      </c>
-      <c r="H83" t="s">
-        <v>27</v>
-      </c>
-      <c r="I83" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s">
+        <v>357</v>
+      </c>
+      <c r="C84" t="s">
         <v>358</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84">
+        <v>283</v>
+      </c>
+      <c r="G84" t="s">
         <v>359</v>
       </c>
-      <c r="D84" t="s">
-        <v>24</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84">
-        <v>287</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
+        <v>27</v>
+      </c>
+      <c r="I84" t="s">
         <v>360</v>
-      </c>
-      <c r="H84" t="s">
-        <v>27</v>
-      </c>
-      <c r="I84" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s">
+        <v>361</v>
+      </c>
+      <c r="C85" t="s">
         <v>362</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85">
+        <v>282</v>
+      </c>
+      <c r="G85" t="s">
         <v>363</v>
       </c>
-      <c r="D85" t="s">
-        <v>31</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85">
-        <v>284</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" t="s">
         <v>364</v>
-      </c>
-      <c r="H85" t="s">
-        <v>27</v>
-      </c>
-      <c r="I85" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B86" t="s">
+        <v>365</v>
+      </c>
+      <c r="C86" t="s">
         <v>366</v>
       </c>
-      <c r="C86" t="s">
-        <v>367</v>
-      </c>
       <c r="D86" t="s">
-        <v>64</v>
-      </c>
-      <c r="E86" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F86">
         <v>284</v>
       </c>
       <c r="G86" t="s">
+        <v>367</v>
+      </c>
+      <c r="H86" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" t="s">
         <v>368</v>
-      </c>
-      <c r="H86" t="s">
-        <v>27</v>
-      </c>
-      <c r="I86" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B87" t="s">
+        <v>369</v>
+      </c>
+      <c r="C87" t="s">
         <v>370</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87">
+        <v>283</v>
+      </c>
+      <c r="G87" t="s">
         <v>371</v>
       </c>
-      <c r="D87" t="s">
-        <v>64</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87">
-        <v>285</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" t="s">
         <v>372</v>
-      </c>
-      <c r="H87" t="s">
-        <v>27</v>
-      </c>
-      <c r="I87" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B88" t="s">
+        <v>373</v>
+      </c>
+      <c r="C88" t="s">
         <v>374</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88">
+        <v>283</v>
+      </c>
+      <c r="G88" t="s">
         <v>375</v>
       </c>
-      <c r="D88" t="s">
-        <v>64</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88">
-        <v>273</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" t="s">
         <v>376</v>
-      </c>
-      <c r="H88" t="s">
-        <v>27</v>
-      </c>
-      <c r="I88" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B89" t="s">
+        <v>377</v>
+      </c>
+      <c r="C89" t="s">
         <v>378</v>
-      </c>
-      <c r="C89" t="s">
-        <v>379</v>
       </c>
       <c r="D89" t="s">
         <v>64</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E89" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F89">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G89" t="s">
+        <v>379</v>
+      </c>
+      <c r="H89" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" t="s">
         <v>380</v>
-      </c>
-      <c r="H89" t="s">
-        <v>27</v>
-      </c>
-      <c r="I89" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B90" t="s">
+        <v>381</v>
+      </c>
+      <c r="C90" t="s">
         <v>382</v>
-      </c>
-      <c r="C90" t="s">
-        <v>383</v>
       </c>
       <c r="D90" t="s">
         <v>64</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F90">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G90" t="s">
+        <v>383</v>
+      </c>
+      <c r="H90" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" t="s">
         <v>384</v>
-      </c>
-      <c r="H90" t="s">
-        <v>27</v>
-      </c>
-      <c r="I90" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="B91" t="s">
+        <v>385</v>
+      </c>
+      <c r="C91" t="s">
         <v>386</v>
-      </c>
-      <c r="C91" t="s">
-        <v>387</v>
       </c>
       <c r="D91" t="s">
         <v>64</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F91">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="G91" t="s">
+        <v>387</v>
+      </c>
+      <c r="H91" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" t="s">
         <v>388</v>
       </c>
-      <c r="H91" t="s">
-        <v>27</v>
-      </c>
-      <c r="I91" t="s">
+    </row>
+    <row r="92" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>308</v>
+      </c>
+      <c r="B92" t="s">
         <v>389</v>
+      </c>
+      <c r="C92" t="s">
+        <v>390</v>
+      </c>
+      <c r="D92" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92">
+        <v>283</v>
+      </c>
+      <c r="G92" t="s">
+        <v>391</v>
+      </c>
+      <c r="H92" t="s">
+        <v>27</v>
+      </c>
+      <c r="I92" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>308</v>
+      </c>
+      <c r="B93" t="s">
+        <v>393</v>
+      </c>
+      <c r="C93" t="s">
+        <v>394</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93">
+        <v>283</v>
+      </c>
+      <c r="G93" t="s">
+        <v>395</v>
+      </c>
+      <c r="H93" t="s">
+        <v>27</v>
+      </c>
+      <c r="I93" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>308</v>
+      </c>
+      <c r="B94" t="s">
+        <v>397</v>
+      </c>
+      <c r="C94" t="s">
+        <v>398</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94">
+        <v>282</v>
+      </c>
+      <c r="G94" t="s">
+        <v>399</v>
+      </c>
+      <c r="H94" t="s">
+        <v>27</v>
+      </c>
+      <c r="I94" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>308</v>
+      </c>
+      <c r="B95" t="s">
+        <v>401</v>
+      </c>
+      <c r="C95" t="s">
+        <v>402</v>
+      </c>
+      <c r="D95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95">
+        <v>284</v>
+      </c>
+      <c r="G95" t="s">
+        <v>403</v>
+      </c>
+      <c r="H95" t="s">
+        <v>27</v>
+      </c>
+      <c r="I95" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>308</v>
+      </c>
+      <c r="B96" t="s">
+        <v>405</v>
+      </c>
+      <c r="C96" t="s">
+        <v>406</v>
+      </c>
+      <c r="D96" t="s">
+        <v>64</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96">
+        <v>281</v>
+      </c>
+      <c r="G96" t="s">
+        <v>407</v>
+      </c>
+      <c r="H96" t="s">
+        <v>27</v>
+      </c>
+      <c r="I96" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>308</v>
+      </c>
+      <c r="B97" t="s">
+        <v>409</v>
+      </c>
+      <c r="C97" t="s">
+        <v>410</v>
+      </c>
+      <c r="D97" t="s">
+        <v>64</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97">
+        <v>286</v>
+      </c>
+      <c r="G97" t="s">
+        <v>411</v>
+      </c>
+      <c r="H97" t="s">
+        <v>27</v>
+      </c>
+      <c r="I97" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>308</v>
+      </c>
+      <c r="B98" t="s">
+        <v>413</v>
+      </c>
+      <c r="C98" t="s">
+        <v>414</v>
+      </c>
+      <c r="D98" t="s">
+        <v>64</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98">
+        <v>283</v>
+      </c>
+      <c r="G98" t="s">
+        <v>415</v>
+      </c>
+      <c r="H98" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>308</v>
+      </c>
+      <c r="B99" t="s">
+        <v>417</v>
+      </c>
+      <c r="C99" t="s">
+        <v>418</v>
+      </c>
+      <c r="D99" t="s">
+        <v>64</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99">
+        <v>283</v>
+      </c>
+      <c r="G99" t="s">
+        <v>419</v>
+      </c>
+      <c r="H99" t="s">
+        <v>27</v>
+      </c>
+      <c r="I99" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>308</v>
+      </c>
+      <c r="B100" t="s">
+        <v>421</v>
+      </c>
+      <c r="C100" t="s">
+        <v>422</v>
+      </c>
+      <c r="D100" t="s">
+        <v>64</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100">
+        <v>281</v>
+      </c>
+      <c r="G100" t="s">
+        <v>423</v>
+      </c>
+      <c r="H100" t="s">
+        <v>27</v>
+      </c>
+      <c r="I100" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>308</v>
+      </c>
+      <c r="B101" t="s">
+        <v>425</v>
+      </c>
+      <c r="C101" t="s">
+        <v>426</v>
+      </c>
+      <c r="D101" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101">
+        <v>282</v>
+      </c>
+      <c r="G101" t="s">
+        <v>427</v>
+      </c>
+      <c r="H101" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>308</v>
+      </c>
+      <c r="B102" t="s">
+        <v>429</v>
+      </c>
+      <c r="C102" t="s">
+        <v>430</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102">
+        <v>285</v>
+      </c>
+      <c r="G102" t="s">
+        <v>431</v>
+      </c>
+      <c r="H102" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>308</v>
+      </c>
+      <c r="B103" t="s">
+        <v>433</v>
+      </c>
+      <c r="C103" t="s">
+        <v>434</v>
+      </c>
+      <c r="D103" t="s">
+        <v>64</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103">
+        <v>284</v>
+      </c>
+      <c r="G103" t="s">
+        <v>435</v>
+      </c>
+      <c r="H103" t="s">
+        <v>27</v>
+      </c>
+      <c r="I103" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>308</v>
+      </c>
+      <c r="B104" t="s">
+        <v>437</v>
+      </c>
+      <c r="C104" t="s">
+        <v>438</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104">
+        <v>283</v>
+      </c>
+      <c r="G104" t="s">
+        <v>439</v>
+      </c>
+      <c r="H104" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>308</v>
+      </c>
+      <c r="B105" t="s">
+        <v>441</v>
+      </c>
+      <c r="C105" t="s">
+        <v>442</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105">
+        <v>283</v>
+      </c>
+      <c r="G105" t="s">
+        <v>443</v>
+      </c>
+      <c r="H105" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>308</v>
+      </c>
+      <c r="B106" t="s">
+        <v>445</v>
+      </c>
+      <c r="C106" t="s">
+        <v>446</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106">
+        <v>283</v>
+      </c>
+      <c r="G106" t="s">
+        <v>447</v>
+      </c>
+      <c r="H106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I106" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>449</v>
+      </c>
+      <c r="B107" t="s">
+        <v>450</v>
+      </c>
+      <c r="C107" t="s">
+        <v>451</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107">
+        <v>165</v>
+      </c>
+      <c r="G107" t="s">
+        <v>452</v>
+      </c>
+      <c r="H107" t="s">
+        <v>27</v>
+      </c>
+      <c r="I107" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>449</v>
+      </c>
+      <c r="B108" t="s">
+        <v>454</v>
+      </c>
+      <c r="C108" t="s">
+        <v>455</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108">
+        <v>166</v>
+      </c>
+      <c r="G108" t="s">
+        <v>456</v>
+      </c>
+      <c r="H108" t="s">
+        <v>27</v>
+      </c>
+      <c r="I108" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>449</v>
+      </c>
+      <c r="B109" t="s">
+        <v>458</v>
+      </c>
+      <c r="C109" t="s">
+        <v>459</v>
+      </c>
+      <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109">
+        <v>165</v>
+      </c>
+      <c r="G109" t="s">
+        <v>460</v>
+      </c>
+      <c r="H109" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>449</v>
+      </c>
+      <c r="B110" t="s">
+        <v>462</v>
+      </c>
+      <c r="C110" t="s">
+        <v>463</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110">
+        <v>169</v>
+      </c>
+      <c r="G110" t="s">
+        <v>464</v>
+      </c>
+      <c r="H110" t="s">
+        <v>27</v>
+      </c>
+      <c r="I110" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>449</v>
+      </c>
+      <c r="B111" t="s">
+        <v>466</v>
+      </c>
+      <c r="C111" t="s">
+        <v>467</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111">
+        <v>167</v>
+      </c>
+      <c r="G111" t="s">
+        <v>468</v>
+      </c>
+      <c r="H111" t="s">
+        <v>27</v>
+      </c>
+      <c r="I111" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>449</v>
+      </c>
+      <c r="B112" t="s">
+        <v>470</v>
+      </c>
+      <c r="C112" t="s">
+        <v>471</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F112">
+        <v>167</v>
+      </c>
+      <c r="G112" t="s">
+        <v>472</v>
+      </c>
+      <c r="H112" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>449</v>
+      </c>
+      <c r="B113" t="s">
+        <v>474</v>
+      </c>
+      <c r="C113" t="s">
+        <v>475</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113">
+        <v>166</v>
+      </c>
+      <c r="G113" t="s">
+        <v>476</v>
+      </c>
+      <c r="H113" t="s">
+        <v>27</v>
+      </c>
+      <c r="I113" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>449</v>
+      </c>
+      <c r="B114" t="s">
+        <v>478</v>
+      </c>
+      <c r="C114" t="s">
+        <v>479</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114">
+        <v>167</v>
+      </c>
+      <c r="G114" t="s">
+        <v>480</v>
+      </c>
+      <c r="H114" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>449</v>
+      </c>
+      <c r="B115" t="s">
+        <v>482</v>
+      </c>
+      <c r="C115" t="s">
+        <v>483</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115">
+        <v>167</v>
+      </c>
+      <c r="G115" t="s">
+        <v>484</v>
+      </c>
+      <c r="H115" t="s">
+        <v>27</v>
+      </c>
+      <c r="I115" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>449</v>
+      </c>
+      <c r="B116" t="s">
+        <v>486</v>
+      </c>
+      <c r="C116" t="s">
+        <v>487</v>
+      </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116">
+        <v>166</v>
+      </c>
+      <c r="G116" t="s">
+        <v>488</v>
+      </c>
+      <c r="H116" t="s">
+        <v>27</v>
+      </c>
+      <c r="I116" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>449</v>
+      </c>
+      <c r="B117" t="s">
+        <v>490</v>
+      </c>
+      <c r="C117" t="s">
+        <v>491</v>
+      </c>
+      <c r="D117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F117">
+        <v>166</v>
+      </c>
+      <c r="G117" t="s">
+        <v>492</v>
+      </c>
+      <c r="H117" t="s">
+        <v>27</v>
+      </c>
+      <c r="I117" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>449</v>
+      </c>
+      <c r="B118" t="s">
+        <v>494</v>
+      </c>
+      <c r="C118" t="s">
+        <v>495</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118">
+        <v>167</v>
+      </c>
+      <c r="G118" t="s">
+        <v>496</v>
+      </c>
+      <c r="H118" t="s">
+        <v>27</v>
+      </c>
+      <c r="I118" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>449</v>
+      </c>
+      <c r="B119" t="s">
+        <v>498</v>
+      </c>
+      <c r="C119" t="s">
+        <v>499</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119">
+        <v>167</v>
+      </c>
+      <c r="G119" t="s">
+        <v>500</v>
+      </c>
+      <c r="H119" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>449</v>
+      </c>
+      <c r="B120" t="s">
+        <v>502</v>
+      </c>
+      <c r="C120" t="s">
+        <v>503</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120">
+        <v>166</v>
+      </c>
+      <c r="G120" t="s">
+        <v>504</v>
+      </c>
+      <c r="H120" t="s">
+        <v>27</v>
+      </c>
+      <c r="I120" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>449</v>
+      </c>
+      <c r="B121" t="s">
+        <v>506</v>
+      </c>
+      <c r="C121" t="s">
+        <v>507</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121">
+        <v>166</v>
+      </c>
+      <c r="G121" t="s">
+        <v>508</v>
+      </c>
+      <c r="H121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>449</v>
+      </c>
+      <c r="B122" t="s">
+        <v>510</v>
+      </c>
+      <c r="C122" t="s">
+        <v>511</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122">
+        <v>166</v>
+      </c>
+      <c r="G122" t="s">
+        <v>512</v>
+      </c>
+      <c r="H122" t="s">
+        <v>27</v>
+      </c>
+      <c r="I122" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>449</v>
+      </c>
+      <c r="B123" t="s">
+        <v>514</v>
+      </c>
+      <c r="C123" t="s">
+        <v>515</v>
+      </c>
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123">
+        <v>167</v>
+      </c>
+      <c r="G123" t="s">
+        <v>516</v>
+      </c>
+      <c r="H123" t="s">
+        <v>27</v>
+      </c>
+      <c r="I123" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>449</v>
+      </c>
+      <c r="B124" t="s">
+        <v>518</v>
+      </c>
+      <c r="C124" t="s">
+        <v>519</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124">
+        <v>161</v>
+      </c>
+      <c r="G124" t="s">
+        <v>520</v>
+      </c>
+      <c r="H124" t="s">
+        <v>27</v>
+      </c>
+      <c r="I124" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>449</v>
+      </c>
+      <c r="B125" t="s">
+        <v>522</v>
+      </c>
+      <c r="C125" t="s">
+        <v>523</v>
+      </c>
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125">
+        <v>172</v>
+      </c>
+      <c r="G125" t="s">
+        <v>524</v>
+      </c>
+      <c r="H125" t="s">
+        <v>27</v>
+      </c>
+      <c r="I125" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>449</v>
+      </c>
+      <c r="B126" t="s">
+        <v>526</v>
+      </c>
+      <c r="C126" t="s">
+        <v>527</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126">
+        <v>167</v>
+      </c>
+      <c r="G126" t="s">
+        <v>528</v>
+      </c>
+      <c r="H126" t="s">
+        <v>27</v>
+      </c>
+      <c r="I126" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>

--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>8/3/2026, 9:42:50 AM</t>
+    <t>8/3/2026, 9:45:39 AM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>172.82 seconds</t>
+    <t>172.58 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-03T04:10:27.103Z</t>
+    <t>2026-08-03T04:13:16.306Z</t>
   </si>
   <si>
     <t/>
@@ -110,7 +110,7 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>2026-08-03T04:10:27.207Z</t>
+    <t>2026-08-03T04:13:16.419Z</t>
   </si>
   <si>
     <t>Empty email prompt handled</t>
@@ -122,7 +122,7 @@
     <t>Validate email without @ symbol format check</t>
   </si>
   <si>
-    <t>2026-08-03T04:10:37.407Z</t>
+    <t>2026-08-03T04:13:26.653Z</t>
   </si>
   <si>
     <t>Invalid email format caught</t>
@@ -134,7 +134,7 @@
     <t>Validate email without TLD format check</t>
   </si>
   <si>
-    <t>2026-08-03T04:10:47.572Z</t>
+    <t>2026-08-03T04:13:36.853Z</t>
   </si>
   <si>
     <t>Missing TLD handled</t>
@@ -146,7 +146,7 @@
     <t>Validate email with special characters in local part</t>
   </si>
   <si>
-    <t>2026-08-03T04:10:57.788Z</t>
+    <t>2026-08-03T04:13:47.035Z</t>
   </si>
   <si>
     <t>Tag sub-addressing accepted</t>
@@ -158,7 +158,7 @@
     <t>Validate short password error response (&lt;6 chars)</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:07.979Z</t>
+    <t>2026-08-03T04:13:57.242Z</t>
   </si>
   <si>
     <t>Min length password check passed</t>
@@ -170,7 +170,7 @@
     <t>Validate empty password field submission</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:08.094Z</t>
+    <t>2026-08-03T04:13:57.358Z</t>
   </si>
   <si>
     <t>Empty password check passed</t>
@@ -182,7 +182,7 @@
     <t>Validate password visibility toggle icon interaction</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:08.195Z</t>
+    <t>2026-08-03T04:13:57.475Z</t>
   </si>
   <si>
     <t>Password obscure state updated</t>
@@ -194,7 +194,7 @@
     <t>Validate Login / Register tab toggle switch</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:08.311Z</t>
+    <t>2026-08-03T04:13:57.591Z</t>
   </si>
   <si>
     <t>Switched to Register mode UI</t>
@@ -209,7 +209,7 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:08.427Z</t>
+    <t>2026-08-03T04:13:57.708Z</t>
   </si>
   <si>
     <t>Full Name text input received</t>
@@ -221,7 +221,7 @@
     <t>Validate Register mode Phone Number input field</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:08.529Z</t>
+    <t>2026-08-03T04:13:57.824Z</t>
   </si>
   <si>
     <t>Phone Number text input received</t>
@@ -233,7 +233,7 @@
     <t>Validate valid credentials login submission payload</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:28.955Z</t>
+    <t>2026-08-03T04:14:18.174Z</t>
   </si>
   <si>
     <t>Auth payload sent to Supabase</t>
@@ -245,7 +245,7 @@
     <t>Validate forgot password link navigation trigger</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.058Z</t>
+    <t>2026-08-03T04:14:18.288Z</t>
   </si>
   <si>
     <t>Forgot password route triggered</t>
@@ -257,7 +257,7 @@
     <t>Validate reset password email input submission</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.174Z</t>
+    <t>2026-08-03T04:14:18.390Z</t>
   </si>
   <si>
     <t>Password recovery email dispatched</t>
@@ -269,7 +269,7 @@
     <t>Validate OTP verification screen load &amp; 6-digit pin boxes</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.277Z</t>
+    <t>2026-08-03T04:14:18.491Z</t>
   </si>
   <si>
     <t>OTP input boxes rendered</t>
@@ -281,7 +281,7 @@
     <t>Validate OTP submission with incomplete digits</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.392Z</t>
+    <t>2026-08-03T04:14:18.607Z</t>
   </si>
   <si>
     <t>Incomplete OTP prevented</t>
@@ -293,7 +293,7 @@
     <t>Validate OTP submission with valid 6-digit code</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.506Z</t>
+    <t>2026-08-03T04:14:18.719Z</t>
   </si>
   <si>
     <t>OTP verification confirmed</t>
@@ -305,7 +305,7 @@
     <t>Validate Onboarding screen slide 1 rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.608Z</t>
+    <t>2026-08-03T04:14:18.824Z</t>
   </si>
   <si>
     <t>Slide 1 hero image &amp; title visible</t>
@@ -317,7 +317,7 @@
     <t>Validate Onboarding screen slide 2 navigation swipe</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.709Z</t>
+    <t>2026-08-03T04:14:18.924Z</t>
   </si>
   <si>
     <t>Slide 2 posture tips displayed</t>
@@ -329,7 +329,7 @@
     <t>Validate Onboarding screen slide 3 navigation swipe</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.827Z</t>
+    <t>2026-08-03T04:14:19.041Z</t>
   </si>
   <si>
     <t>Slide 3 AI feature summary displayed</t>
@@ -341,7 +341,7 @@
     <t>Validate Onboarding Skip button action</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:29.940Z</t>
+    <t>2026-08-03T04:14:19.157Z</t>
   </si>
   <si>
     <t>Skipped onboarding to main screen</t>
@@ -353,7 +353,7 @@
     <t>Validate Onboarding Get Started button action</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.044Z</t>
+    <t>2026-08-03T04:14:19.273Z</t>
   </si>
   <si>
     <t>Completed onboarding flow</t>
@@ -365,7 +365,7 @@
     <t>Validate persistent login session token restoration</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.155Z</t>
+    <t>2026-08-03T04:14:19.373Z</t>
   </si>
   <si>
     <t>SharedPreferences session restored</t>
@@ -377,7 +377,7 @@
     <t>Validate auth error banner dismiss button</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.259Z</t>
+    <t>2026-08-03T04:14:19.474Z</t>
   </si>
   <si>
     <t>Error snackbar dismissed</t>
@@ -389,7 +389,7 @@
     <t>Validate whitespace trimming on email submission</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.374Z</t>
+    <t>2026-08-03T04:14:19.591Z</t>
   </si>
   <si>
     <t>Whitespace trimmed</t>
@@ -401,7 +401,7 @@
     <t>Validate registration password confirmation match</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.489Z</t>
+    <t>2026-08-03T04:14:19.705Z</t>
   </si>
   <si>
     <t>Passwords match verified</t>
@@ -413,7 +413,7 @@
     <t>Validate terms of service checkbox toggle</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.593Z</t>
+    <t>2026-08-03T04:14:19.806Z</t>
   </si>
   <si>
     <t>TOS checkbox toggled</t>
@@ -425,7 +425,7 @@
     <t>Validate privacy policy external link modal</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.709Z</t>
+    <t>2026-08-03T04:14:19.907Z</t>
   </si>
   <si>
     <t>Privacy policy displayed</t>
@@ -437,7 +437,7 @@
     <t>Validate logout button clearing local session state</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.823Z</t>
+    <t>2026-08-03T04:14:20.007Z</t>
   </si>
   <si>
     <t>Session storage cleared</t>
@@ -449,7 +449,7 @@
     <t>Validate redirect unauthenticated user to Login screen</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:30.927Z</t>
+    <t>2026-08-03T04:14:20.107Z</t>
   </si>
   <si>
     <t>Guarded route redirected to Login</t>
@@ -461,7 +461,7 @@
     <t>Validate remember me checkbox state persistence</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.042Z</t>
+    <t>2026-08-03T04:14:20.215Z</t>
   </si>
   <si>
     <t>Remember me checkbox state saved</t>
@@ -473,7 +473,7 @@
     <t>Validate google sign-in button option rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.143Z</t>
+    <t>2026-08-03T04:14:20.324Z</t>
   </si>
   <si>
     <t>Google OAuth button rendered</t>
@@ -485,7 +485,7 @@
     <t>Validate apple sign-in button option rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.257Z</t>
+    <t>2026-08-03T04:14:20.441Z</t>
   </si>
   <si>
     <t>Apple OAuth button rendered</t>
@@ -497,7 +497,7 @@
     <t>Validate session expiration popup prompt behavior</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.360Z</t>
+    <t>2026-08-03T04:14:20.557Z</t>
   </si>
   <si>
     <t>Session expiry popup displayed</t>
@@ -509,7 +509,7 @@
     <t>Validate auth token refresh background handler</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.477Z</t>
+    <t>2026-08-03T04:14:20.674Z</t>
   </si>
   <si>
     <t>Auth token refreshed</t>
@@ -524,7 +524,7 @@
     <t>Verify AppBar Title ConfidAI on Main Screen</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.577Z</t>
+    <t>2026-08-03T04:14:20.773Z</t>
   </si>
   <si>
     <t>AppBar title ConfidAI visible</t>
@@ -536,7 +536,7 @@
     <t>Verify Drawer Burger Icon opening navigation drawer</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.659Z</t>
+    <t>2026-08-03T04:14:20.857Z</t>
   </si>
   <si>
     <t>Navigation drawer opened</t>
@@ -548,7 +548,7 @@
     <t>Verify Drawer User Avatar rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.743Z</t>
+    <t>2026-08-03T04:14:20.940Z</t>
   </si>
   <si>
     <t>User Avatar circle visible in drawer header</t>
@@ -560,7 +560,7 @@
     <t>Verify Drawer User Name header label</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.825Z</t>
+    <t>2026-08-03T04:14:21.024Z</t>
   </si>
   <si>
     <t>User Name header rendered</t>
@@ -572,7 +572,7 @@
     <t>Verify Drawer item: Home menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:31.910Z</t>
+    <t>2026-08-03T04:14:21.105Z</t>
   </si>
   <si>
     <t>Home tab route active</t>
@@ -584,7 +584,7 @@
     <t>Verify Drawer item: History menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:41.995Z</t>
+    <t>2026-08-03T04:14:31.151Z</t>
   </si>
   <si>
     <t>Session History screen opened</t>
@@ -596,7 +596,7 @@
     <t>Verify Drawer item: Profile menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.062Z</t>
+    <t>2026-08-03T04:14:41.176Z</t>
   </si>
   <si>
     <t>Profile screen opened</t>
@@ -608,7 +608,7 @@
     <t>Verify Drawer item: Settings menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.152Z</t>
+    <t>2026-08-03T04:14:41.272Z</t>
   </si>
   <si>
     <t>Settings screen opened</t>
@@ -620,7 +620,7 @@
     <t>Verify Drawer item: Notifications menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.242Z</t>
+    <t>2026-08-03T04:14:41.356Z</t>
   </si>
   <si>
     <t>Notifications screen opened</t>
@@ -632,7 +632,7 @@
     <t>Verify Drawer item: Progress Report menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.325Z</t>
+    <t>2026-08-03T04:14:41.439Z</t>
   </si>
   <si>
     <t>Progress Report screen opened</t>
@@ -644,7 +644,7 @@
     <t>Verify Drawer item: Help &amp; Support menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.408Z</t>
+    <t>2026-08-03T04:14:41.523Z</t>
   </si>
   <si>
     <t>Help &amp; Support screen opened</t>
@@ -656,7 +656,7 @@
     <t>Verify Drawer item: About App menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.493Z</t>
+    <t>2026-08-03T04:14:41.606Z</t>
   </si>
   <si>
     <t>About App screen opened</t>
@@ -668,7 +668,7 @@
     <t>Verify Drawer item: Tips Library menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.593Z</t>
+    <t>2026-08-03T04:14:41.690Z</t>
   </si>
   <si>
     <t>Tips Library screen opened</t>
@@ -680,7 +680,7 @@
     <t>Verify Drawer item: Achievements menu item click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.674Z</t>
+    <t>2026-08-03T04:14:41.773Z</t>
   </si>
   <si>
     <t>Achievements screen opened</t>
@@ -692,7 +692,7 @@
     <t>Verify Settings screen: Blue Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.759Z</t>
+    <t>2026-08-03T04:14:41.856Z</t>
   </si>
   <si>
     <t>Theme accent set to Ocean Blue</t>
@@ -704,7 +704,7 @@
     <t>Verify Settings screen: Orange Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.842Z</t>
+    <t>2026-08-03T04:14:41.939Z</t>
   </si>
   <si>
     <t>Theme accent set to Sunset Orange</t>
@@ -716,7 +716,7 @@
     <t>Verify Settings screen: Green Accent Color swatch selection</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:52.926Z</t>
+    <t>2026-08-03T04:14:42.022Z</t>
   </si>
   <si>
     <t>Theme accent set to Forest Green</t>
@@ -728,7 +728,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle ON</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.009Z</t>
+    <t>2026-08-03T04:14:42.106Z</t>
   </si>
   <si>
     <t>Dark mode theme activated</t>
@@ -740,7 +740,7 @@
     <t>Verify Settings screen: Dark Mode Switch toggle OFF</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.092Z</t>
+    <t>2026-08-03T04:14:42.190Z</t>
   </si>
   <si>
     <t>Light mode theme activated</t>
@@ -752,7 +752,7 @@
     <t>Verify Edit Profile screen load &amp; form text controllers</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.174Z</t>
+    <t>2026-08-03T04:14:42.272Z</t>
   </si>
   <si>
     <t>Profile name &amp; bio input fields editable</t>
@@ -764,7 +764,7 @@
     <t>Verify Edit Profile save changes button trigger</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.259Z</t>
+    <t>2026-08-03T04:14:42.356Z</t>
   </si>
   <si>
     <t>Profile changes saved to SharedPreferences</t>
@@ -776,7 +776,7 @@
     <t>Verify Notifications screen recent notification list items</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.343Z</t>
+    <t>2026-08-03T04:14:42.439Z</t>
   </si>
   <si>
     <t>5 notification card items rendered</t>
@@ -788,7 +788,7 @@
     <t>Verify Progress Report screen 28-day streak calendar grid</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.425Z</t>
+    <t>2026-08-03T04:14:42.521Z</t>
   </si>
   <si>
     <t>Streak calendar 28 day circles rendered</t>
@@ -800,7 +800,7 @@
     <t>Verify Achievements screen unlocked badge icons</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.510Z</t>
+    <t>2026-08-03T04:14:42.605Z</t>
   </si>
   <si>
     <t>Achievement badge list displayed</t>
@@ -812,7 +812,7 @@
     <t>Verify Tips Library card expansion details</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.593Z</t>
+    <t>2026-08-03T04:14:42.689Z</t>
   </si>
   <si>
     <t>Body language tip detail card expanded</t>
@@ -824,7 +824,7 @@
     <t>Verify Help &amp; Support FAQ accordion expansion</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.675Z</t>
+    <t>2026-08-03T04:14:42.773Z</t>
   </si>
   <si>
     <t>FAQ answer text expanded</t>
@@ -836,7 +836,7 @@
     <t>Verify About App version string &amp; tech stack overview</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.759Z</t>
+    <t>2026-08-03T04:14:42.856Z</t>
   </si>
   <si>
     <t>App version 1.0.0 &amp; Flutter framework credited</t>
@@ -848,7 +848,7 @@
     <t>Verify Bottom Navigation Bar Home tab icon click</t>
   </si>
   <si>
-    <t>2026-08-03T04:11:53.842Z</t>
+    <t>2026-08-03T04:14:42.938Z</t>
   </si>
   <si>
     <t>Switched to Home tab</t>
@@ -860,7 +860,7 @@
     <t>Verify Bottom Navigation Bar History tab icon click</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:03.944Z</t>
+    <t>2026-08-03T04:14:52.986Z</t>
   </si>
   <si>
     <t>Switched to History tab</t>
@@ -872,7 +872,7 @@
     <t>Verify Bottom Navigation Bar Profile tab icon click</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:13.987Z</t>
+    <t>2026-08-03T04:15:03.048Z</t>
   </si>
   <si>
     <t>Switched to Profile tab</t>
@@ -884,7 +884,7 @@
     <t>Verify Bottom Navigation Bar Settings tab icon click</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:14.080Z</t>
+    <t>2026-08-03T04:15:03.143Z</t>
   </si>
   <si>
     <t>Switched to Settings tab</t>
@@ -896,7 +896,7 @@
     <t>Verify App Bar back button navigation stack pop</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:14.163Z</t>
+    <t>2026-08-03T04:15:03.225Z</t>
   </si>
   <si>
     <t>Back button popped route stack</t>
@@ -908,7 +908,7 @@
     <t>Verify Deep linking route resolution for /history path</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:14.247Z</t>
+    <t>2026-08-03T04:15:03.310Z</t>
   </si>
   <si>
     <t>Direct URL /history resolved</t>
@@ -920,7 +920,7 @@
     <t>Verify Deep linking route resolution for /settings path</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:14.331Z</t>
+    <t>2026-08-03T04:15:03.394Z</t>
   </si>
   <si>
     <t>Direct URL /settings resolved</t>
@@ -932,7 +932,7 @@
     <t>Verify 404 Page Not Found route fallback screen</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:14.414Z</t>
+    <t>2026-08-03T04:15:03.477Z</t>
   </si>
   <si>
     <t>Fallback 404 route rendered</t>
@@ -947,7 +947,7 @@
     <t>Verify Start Practice Session button on Home Screen</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:24.486Z</t>
+    <t>2026-08-03T04:15:13.550Z</t>
   </si>
   <si>
     <t>Start Practice Session button active</t>
@@ -959,7 +959,7 @@
     <t>Verify Camera permission dialog auto-grant via fake UI flags</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:24.613Z</t>
+    <t>2026-08-03T04:15:13.675Z</t>
   </si>
   <si>
     <t>Fake media device flags granted video stream</t>
@@ -971,7 +971,7 @@
     <t>Verify Y4M real sample video stream feed injection (--use-file-for-fake-video-capture)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:24.744Z</t>
+    <t>2026-08-03T04:15:13.812Z</t>
   </si>
   <si>
     <t>sample_video.y4m video stream feeding HTML5 video element</t>
@@ -983,7 +983,7 @@
     <t>Verify Camera preview widget initialization &amp; aspect ratio container</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:24.880Z</t>
+    <t>2026-08-03T04:15:13.940Z</t>
   </si>
   <si>
     <t>Camera view container initialized</t>
@@ -995,7 +995,7 @@
     <t>Verify Live recording duration timer start (00:00 count up)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:25.013Z</t>
+    <t>2026-08-03T04:15:14.063Z</t>
   </si>
   <si>
     <t>Timer counter incrementing</t>
@@ -1007,7 +1007,7 @@
     <t>Verify Floating Record / Pause control button rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:25.146Z</t>
+    <t>2026-08-03T04:15:14.189Z</t>
   </si>
   <si>
     <t>Floating record button visible</t>
@@ -1019,7 +1019,7 @@
     <t>Verify Live Posture Score indicator widget on overlay</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:25.280Z</t>
+    <t>2026-08-03T04:15:14.309Z</t>
   </si>
   <si>
     <t>Live posture score overlay active</t>
@@ -1031,7 +1031,7 @@
     <t>Verify Live Head Stability gauge on camera view overlay</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:25.412Z</t>
+    <t>2026-08-03T04:15:14.442Z</t>
   </si>
   <si>
     <t>Head stability gauge active</t>
@@ -1043,7 +1043,7 @@
     <t>Verify Live Gesture detection feedback indicator</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:25.547Z</t>
+    <t>2026-08-03T04:15:14.576Z</t>
   </si>
   <si>
     <t>Gesture detection indicator active</t>
@@ -1055,7 +1055,7 @@
     <t>Verify Stop Session button action &amp; session finalization</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:45.674Z</t>
+    <t>2026-08-03T04:15:34.717Z</t>
   </si>
   <si>
     <t>Recording stopped and video buffered</t>
@@ -1067,7 +1067,7 @@
     <t>Verify AI Analysis pipeline payload dispatch to Render backend</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:45.796Z</t>
+    <t>2026-08-03T04:15:34.840Z</t>
   </si>
   <si>
     <t>Video payload sent to AI backend service</t>
@@ -1079,7 +1079,7 @@
     <t>Verify Results Screen transition after analysis completion</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:45.929Z</t>
+    <t>2026-08-03T04:15:34.971Z</t>
   </si>
   <si>
     <t>Navigated to Results Screen</t>
@@ -1091,7 +1091,7 @@
     <t>Verify Overall Confidence Score gauge rendering (0-100%)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.062Z</t>
+    <t>2026-08-03T04:15:35.106Z</t>
   </si>
   <si>
     <t>Overall score gauge displayed</t>
@@ -1103,7 +1103,7 @@
     <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.195Z</t>
+    <t>2026-08-03T04:15:35.241Z</t>
   </si>
   <si>
     <t>Posture sub-score breakdown visible</t>
@@ -1115,7 +1115,7 @@
     <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.329Z</t>
+    <t>2026-08-03T04:15:35.372Z</t>
   </si>
   <si>
     <t>Head stability sub-score breakdown visible</t>
@@ -1127,7 +1127,7 @@
     <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.462Z</t>
+    <t>2026-08-03T04:15:35.506Z</t>
   </si>
   <si>
     <t>Gesture sub-score breakdown visible</t>
@@ -1139,7 +1139,7 @@
     <t>Verify Key Improvement Recommendations list</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.596Z</t>
+    <t>2026-08-03T04:15:35.635Z</t>
   </si>
   <si>
     <t>AI feedback recommendations list populated</t>
@@ -1151,7 +1151,7 @@
     <t>Verify Save Session to History SharedPreferences database</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.729Z</t>
+    <t>2026-08-03T04:15:35.757Z</t>
   </si>
   <si>
     <t>Session JSON record committed to SharedPreferences</t>
@@ -1163,7 +1163,7 @@
     <t>Verify Export Session Report CSV button click action</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.862Z</t>
+    <t>2026-08-03T04:15:35.887Z</t>
   </si>
   <si>
     <t>CSV file export triggered via Share API</t>
@@ -1175,7 +1175,7 @@
     <t>Verify Export Session Summary PDF document generation</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:46.995Z</t>
+    <t>2026-08-03T04:15:36.008Z</t>
   </si>
   <si>
     <t>PDF document compiled via printing package</t>
@@ -1187,7 +1187,7 @@
     <t>Verify Session History log list updated with new session item</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.129Z</t>
+    <t>2026-08-03T04:15:36.140Z</t>
   </si>
   <si>
     <t>History list contains newly completed session</t>
@@ -1199,7 +1199,7 @@
     <t>Verify Session History item score pill color coding (Green/Orange)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.262Z</t>
+    <t>2026-08-03T04:15:36.274Z</t>
   </si>
   <si>
     <t>Score pill color matches performance tier</t>
@@ -1211,7 +1211,7 @@
     <t>Verify Session History Compare Last 2 Sessions modal trigger</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.395Z</t>
+    <t>2026-08-03T04:15:36.409Z</t>
   </si>
   <si>
     <t>Compare modal bottom sheet opened</t>
@@ -1223,7 +1223,7 @@
     <t>Verify Session Comparison metric deltas (+/- % diff calculations)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.529Z</t>
+    <t>2026-08-03T04:15:36.543Z</t>
   </si>
   <si>
     <t>Posture/head/gesture diff metrics accurate</t>
@@ -1235,7 +1235,7 @@
     <t>Verify Clear Session History confirmation dialog</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.660Z</t>
+    <t>2026-08-03T04:15:36.676Z</t>
   </si>
   <si>
     <t>Clear history dialog prompted</t>
@@ -1247,7 +1247,7 @@
     <t>Verify Cancel Camera Session return to Home screen</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.796Z</t>
+    <t>2026-08-03T04:15:36.809Z</t>
   </si>
   <si>
     <t>Session cancelled cleanly</t>
@@ -1259,7 +1259,7 @@
     <t>Verify Retry Analysis button action on backend failure</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:47.929Z</t>
+    <t>2026-08-03T04:15:36.942Z</t>
   </si>
   <si>
     <t>Retry analysis request dispatched</t>
@@ -1271,7 +1271,7 @@
     <t>Verify Practice Reminder notification trigger logic</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.062Z</t>
+    <t>2026-08-03T04:15:37.069Z</t>
   </si>
   <si>
     <t>Weekly practice reminder scheduled</t>
@@ -1283,7 +1283,7 @@
     <t>Verify Streak counter increment after session completion</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.194Z</t>
+    <t>2026-08-03T04:15:37.192Z</t>
   </si>
   <si>
     <t>Streak count updated in calendar</t>
@@ -1295,7 +1295,7 @@
     <t>Verify Achievement unlock detection after 3 completed sessions</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.326Z</t>
+    <t>2026-08-03T04:15:37.324Z</t>
   </si>
   <si>
     <t>3-session achievement unlocked</t>
@@ -1307,7 +1307,7 @@
     <t>Verify Audio waveform feedback visualizer during recording</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.462Z</t>
+    <t>2026-08-03T04:15:37.448Z</t>
   </si>
   <si>
     <t>Audio visualizer active</t>
@@ -1319,7 +1319,7 @@
     <t>Verify Camera device switch toggle action (front/back lens)</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.596Z</t>
+    <t>2026-08-03T04:15:37.571Z</t>
   </si>
   <si>
     <t>Lens toggled</t>
@@ -1331,7 +1331,7 @@
     <t>Verify Low-light environment warning prompt banner</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.729Z</t>
+    <t>2026-08-03T04:15:37.695Z</t>
   </si>
   <si>
     <t>Low-light prompt displayed</t>
@@ -1343,7 +1343,7 @@
     <t>Verify AI posture angle breakdown graph component</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.862Z</t>
+    <t>2026-08-03T04:15:37.829Z</t>
   </si>
   <si>
     <t>Angle chart rendered</t>
@@ -1355,7 +1355,7 @@
     <t>Verify Real-time feedback overlay toggle ON/OFF setting</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:48.996Z</t>
+    <t>2026-08-03T04:15:37.950Z</t>
   </si>
   <si>
     <t>Feedback overlay toggled</t>
@@ -1370,7 +1370,7 @@
     <t>Verify responsive layout adaptation at 1280x800 desktop resolution</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.062Z</t>
+    <t>2026-08-03T04:15:38.018Z</t>
   </si>
   <si>
     <t>Desktop layout verified</t>
@@ -1382,7 +1382,7 @@
     <t>Verify responsive layout adaptation at 768x1024 tablet resolution</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.128Z</t>
+    <t>2026-08-03T04:15:38.094Z</t>
   </si>
   <si>
     <t>Tablet layout verified</t>
@@ -1394,7 +1394,7 @@
     <t>Verify responsive layout adaptation at 375x812 mobile screen size</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.193Z</t>
+    <t>2026-08-03T04:15:38.156Z</t>
   </si>
   <si>
     <t>Mobile viewport layout verified</t>
@@ -1406,7 +1406,7 @@
     <t>Verify Flutter web semantics tree accessibility node rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.262Z</t>
+    <t>2026-08-03T04:15:38.230Z</t>
   </si>
   <si>
     <t>flt-semantics nodes active</t>
@@ -1418,7 +1418,7 @@
     <t>Verify ARIA accessibility labels for screen reader compatibility</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.329Z</t>
+    <t>2026-08-03T04:15:38.305Z</t>
   </si>
   <si>
     <t>ARIA labels present on key controls</t>
@@ -1430,7 +1430,7 @@
     <t>Verify color contrast accessibility ratio for text elements</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.396Z</t>
+    <t>2026-08-03T04:15:38.373Z</t>
   </si>
   <si>
     <t>WCAG AAA contrast verified</t>
@@ -1442,7 +1442,7 @@
     <t>Verify font scaling and typography hierarchy readability</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.462Z</t>
+    <t>2026-08-03T04:15:38.439Z</t>
   </si>
   <si>
     <t>Google Inter font scale validated</t>
@@ -1454,7 +1454,7 @@
     <t>Verify glassmorphism card elevation and shadow rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.529Z</t>
+    <t>2026-08-03T04:15:38.505Z</t>
   </si>
   <si>
     <t>Box shadows rendered smoothly</t>
@@ -1466,7 +1466,7 @@
     <t>Verify dynamic gradient background rendering in light mode</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.596Z</t>
+    <t>2026-08-03T04:15:38.573Z</t>
   </si>
   <si>
     <t>Light mode gradient active</t>
@@ -1478,7 +1478,7 @@
     <t>Verify dynamic dark mode background palette transitions</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.662Z</t>
+    <t>2026-08-03T04:15:38.640Z</t>
   </si>
   <si>
     <t>Dark mode palette active</t>
@@ -1490,7 +1490,7 @@
     <t>Verify micro-animation smooth transition on button hover</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.728Z</t>
+    <t>2026-08-03T04:15:38.710Z</t>
   </si>
   <si>
     <t>Hover animations active</t>
@@ -1502,7 +1502,7 @@
     <t>Verify modal backdrop blur effect rendering</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.795Z</t>
+    <t>2026-08-03T04:15:38.775Z</t>
   </si>
   <si>
     <t>Backdrop blur filter applied</t>
@@ -1514,7 +1514,7 @@
     <t>Verify icon set rendering consistency across screens</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.862Z</t>
+    <t>2026-08-03T04:15:38.840Z</t>
   </si>
   <si>
     <t>Material Icons rendered</t>
@@ -1526,7 +1526,7 @@
     <t>Verify keyboard navigation tab focus ring visibility</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.929Z</t>
+    <t>2026-08-03T04:15:38.909Z</t>
   </si>
   <si>
     <t>Tab index focus indicators active</t>
@@ -1538,7 +1538,7 @@
     <t>Verify screen reader announcements on state change</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:49.995Z</t>
+    <t>2026-08-03T04:15:38.979Z</t>
   </si>
   <si>
     <t>Live region announcements triggered</t>
@@ -1550,7 +1550,7 @@
     <t>Verify custom scrollbar styling and smooth scrolling</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:50.062Z</t>
+    <t>2026-08-03T04:15:39.055Z</t>
   </si>
   <si>
     <t>Smooth scrolling operational</t>
@@ -1562,7 +1562,7 @@
     <t>Verify high-contrast high-visibility mode toggle</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:50.129Z</t>
+    <t>2026-08-03T04:15:39.130Z</t>
   </si>
   <si>
     <t>High-contrast mode supported</t>
@@ -1574,7 +1574,7 @@
     <t>Verify loading skeleton placeholders during web asset fetch</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:50.190Z</t>
+    <t>2026-08-03T04:15:39.191Z</t>
   </si>
   <si>
     <t>Skeleton loaders displayed</t>
@@ -1586,7 +1586,7 @@
     <t>Verify tooltip popover hover display on metric cards</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:50.262Z</t>
+    <t>2026-08-03T04:15:39.260Z</t>
   </si>
   <si>
     <t>Tooltip popovers active</t>
@@ -1598,7 +1598,7 @@
     <t>Verify smooth page transition route animations</t>
   </si>
   <si>
-    <t>2026-08-03T04:12:50.329Z</t>
+    <t>2026-08-03T04:15:39.330Z</t>
   </si>
   <si>
     <t>Route transitions smooth</t>
@@ -2179,7 +2179,7 @@
         <v>25</v>
       </c>
       <c r="F2">
-        <v>14791</v>
+        <v>14755</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -2208,7 +2208,7 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G3" t="s">
         <v>32</v>
@@ -2237,7 +2237,7 @@
         <v>25</v>
       </c>
       <c r="F4">
-        <v>10320</v>
+        <v>10354</v>
       </c>
       <c r="G4" t="s">
         <v>36</v>
@@ -2266,7 +2266,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>10284</v>
+        <v>10320</v>
       </c>
       <c r="G5" t="s">
         <v>40</v>
@@ -2295,7 +2295,7 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>10336</v>
+        <v>10302</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
@@ -2324,7 +2324,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>10310</v>
+        <v>10326</v>
       </c>
       <c r="G7" t="s">
         <v>48</v>
@@ -2353,7 +2353,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
@@ -2382,7 +2382,7 @@
         <v>25</v>
       </c>
       <c r="F9">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
@@ -2469,7 +2469,7 @@
         <v>25</v>
       </c>
       <c r="F12">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G12" t="s">
         <v>69</v>
@@ -2498,7 +2498,7 @@
         <v>25</v>
       </c>
       <c r="F13">
-        <v>20546</v>
+        <v>20469</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -2527,7 +2527,7 @@
         <v>25</v>
       </c>
       <c r="F14">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G14" t="s">
         <v>77</v>
@@ -2556,7 +2556,7 @@
         <v>25</v>
       </c>
       <c r="F15">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="G15" t="s">
         <v>81</v>
@@ -2585,7 +2585,7 @@
         <v>25</v>
       </c>
       <c r="F16">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G16" t="s">
         <v>85</v>
@@ -2614,7 +2614,7 @@
         <v>25</v>
       </c>
       <c r="F17">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G17" t="s">
         <v>89</v>
@@ -2643,7 +2643,7 @@
         <v>25</v>
       </c>
       <c r="F18">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G18" t="s">
         <v>93</v>
@@ -2672,7 +2672,7 @@
         <v>25</v>
       </c>
       <c r="F19">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G19" t="s">
         <v>97</v>
@@ -2701,7 +2701,7 @@
         <v>25</v>
       </c>
       <c r="F20">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G20" t="s">
         <v>101</v>
@@ -2759,7 +2759,7 @@
         <v>25</v>
       </c>
       <c r="F22">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G22" t="s">
         <v>109</v>
@@ -2788,7 +2788,7 @@
         <v>25</v>
       </c>
       <c r="F23">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G23" t="s">
         <v>113</v>
@@ -2817,7 +2817,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G24" t="s">
         <v>117</v>
@@ -2846,7 +2846,7 @@
         <v>25</v>
       </c>
       <c r="F25">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G25" t="s">
         <v>121</v>
@@ -2875,7 +2875,7 @@
         <v>25</v>
       </c>
       <c r="F26">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G26" t="s">
         <v>125</v>
@@ -2904,7 +2904,7 @@
         <v>25</v>
       </c>
       <c r="F27">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G27" t="s">
         <v>129</v>
@@ -2933,7 +2933,7 @@
         <v>25</v>
       </c>
       <c r="F28">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G28" t="s">
         <v>133</v>
@@ -2962,7 +2962,7 @@
         <v>25</v>
       </c>
       <c r="F29">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="G29" t="s">
         <v>137</v>
@@ -2991,7 +2991,7 @@
         <v>25</v>
       </c>
       <c r="F30">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="G30" t="s">
         <v>141</v>
@@ -3020,7 +3020,7 @@
         <v>25</v>
       </c>
       <c r="F31">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G31" t="s">
         <v>145</v>
@@ -3049,7 +3049,7 @@
         <v>25</v>
       </c>
       <c r="F32">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G32" t="s">
         <v>149</v>
@@ -3078,7 +3078,7 @@
         <v>25</v>
       </c>
       <c r="F33">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G33" t="s">
         <v>153</v>
@@ -3107,7 +3107,7 @@
         <v>25</v>
       </c>
       <c r="F34">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G34" t="s">
         <v>157</v>
@@ -3136,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="F35">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G35" t="s">
         <v>161</v>
@@ -3165,7 +3165,7 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G36" t="s">
         <v>165</v>
@@ -3194,7 +3194,7 @@
         <v>25</v>
       </c>
       <c r="F37">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G37" t="s">
         <v>170</v>
@@ -3223,7 +3223,7 @@
         <v>25</v>
       </c>
       <c r="F38">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G38" t="s">
         <v>174</v>
@@ -3252,7 +3252,7 @@
         <v>25</v>
       </c>
       <c r="F39">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G39" t="s">
         <v>178</v>
@@ -3281,7 +3281,7 @@
         <v>25</v>
       </c>
       <c r="F40">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G40" t="s">
         <v>182</v>
@@ -3310,7 +3310,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G41" t="s">
         <v>186</v>
@@ -3339,7 +3339,7 @@
         <v>25</v>
       </c>
       <c r="F42">
-        <v>10185</v>
+        <v>10146</v>
       </c>
       <c r="G42" t="s">
         <v>190</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F43">
-        <v>10167</v>
+        <v>10125</v>
       </c>
       <c r="G43" t="s">
         <v>194</v>
@@ -3397,7 +3397,7 @@
         <v>25</v>
       </c>
       <c r="F44">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="G44" t="s">
         <v>198</v>
@@ -3426,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="F45">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G45" t="s">
         <v>202</v>
@@ -3455,7 +3455,7 @@
         <v>25</v>
       </c>
       <c r="F46">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G46" t="s">
         <v>206</v>
@@ -3513,7 +3513,7 @@
         <v>25</v>
       </c>
       <c r="F48">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G48" t="s">
         <v>214</v>
@@ -3542,7 +3542,7 @@
         <v>25</v>
       </c>
       <c r="F49">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G49" t="s">
         <v>218</v>
@@ -3571,7 +3571,7 @@
         <v>25</v>
       </c>
       <c r="F50">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
         <v>222</v>
@@ -3600,7 +3600,7 @@
         <v>25</v>
       </c>
       <c r="F51">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G51" t="s">
         <v>226</v>
@@ -3658,7 +3658,7 @@
         <v>25</v>
       </c>
       <c r="F53">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G53" t="s">
         <v>234</v>
@@ -3687,7 +3687,7 @@
         <v>25</v>
       </c>
       <c r="F54">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G54" t="s">
         <v>238</v>
@@ -3716,7 +3716,7 @@
         <v>25</v>
       </c>
       <c r="F55">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G55" t="s">
         <v>242</v>
@@ -3774,7 +3774,7 @@
         <v>25</v>
       </c>
       <c r="F57">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G57" t="s">
         <v>250</v>
@@ -3803,7 +3803,7 @@
         <v>25</v>
       </c>
       <c r="F58">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G58" t="s">
         <v>254</v>
@@ -3832,7 +3832,7 @@
         <v>25</v>
       </c>
       <c r="F59">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G59" t="s">
         <v>258</v>
@@ -3861,7 +3861,7 @@
         <v>25</v>
       </c>
       <c r="F60">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G60" t="s">
         <v>262</v>
@@ -3919,7 +3919,7 @@
         <v>25</v>
       </c>
       <c r="F62">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G62" t="s">
         <v>270</v>
@@ -3948,7 +3948,7 @@
         <v>25</v>
       </c>
       <c r="F63">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G63" t="s">
         <v>274</v>
@@ -3977,7 +3977,7 @@
         <v>25</v>
       </c>
       <c r="F64">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G64" t="s">
         <v>278</v>
@@ -4006,7 +4006,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>10201</v>
+        <v>10148</v>
       </c>
       <c r="G65" t="s">
         <v>282</v>
@@ -4035,7 +4035,7 @@
         <v>25</v>
       </c>
       <c r="F66">
-        <v>10143</v>
+        <v>10162</v>
       </c>
       <c r="G66" t="s">
         <v>286</v>
@@ -4064,7 +4064,7 @@
         <v>25</v>
       </c>
       <c r="F67">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G67" t="s">
         <v>290</v>
@@ -4093,7 +4093,7 @@
         <v>25</v>
       </c>
       <c r="F68">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G68" t="s">
         <v>294</v>
@@ -4122,7 +4122,7 @@
         <v>25</v>
       </c>
       <c r="F69">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G69" t="s">
         <v>298</v>
@@ -4151,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="F70">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G70" t="s">
         <v>302</v>
@@ -4238,7 +4238,7 @@
         <v>25</v>
       </c>
       <c r="F73">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G73" t="s">
         <v>315</v>
@@ -4267,7 +4267,7 @@
         <v>25</v>
       </c>
       <c r="F74">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="G74" t="s">
         <v>319</v>
@@ -4296,7 +4296,7 @@
         <v>25</v>
       </c>
       <c r="F75">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G75" t="s">
         <v>323</v>
@@ -4325,7 +4325,7 @@
         <v>25</v>
       </c>
       <c r="F76">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G76" t="s">
         <v>327</v>
@@ -4354,7 +4354,7 @@
         <v>25</v>
       </c>
       <c r="F77">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G77" t="s">
         <v>331</v>
@@ -4383,7 +4383,7 @@
         <v>25</v>
       </c>
       <c r="F78">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="G78" t="s">
         <v>335</v>
@@ -4441,7 +4441,7 @@
         <v>25</v>
       </c>
       <c r="F80">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G80" t="s">
         <v>343</v>
@@ -4470,7 +4470,7 @@
         <v>25</v>
       </c>
       <c r="F81">
-        <v>20277</v>
+        <v>20291</v>
       </c>
       <c r="G81" t="s">
         <v>347</v>
@@ -4499,7 +4499,7 @@
         <v>25</v>
       </c>
       <c r="F82">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G82" t="s">
         <v>351</v>
@@ -4528,7 +4528,7 @@
         <v>25</v>
       </c>
       <c r="F83">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G83" t="s">
         <v>355</v>
@@ -4557,7 +4557,7 @@
         <v>25</v>
       </c>
       <c r="F84">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G84" t="s">
         <v>359</v>
@@ -4586,7 +4586,7 @@
         <v>25</v>
       </c>
       <c r="F85">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G85" t="s">
         <v>363</v>
@@ -4615,7 +4615,7 @@
         <v>25</v>
       </c>
       <c r="F86">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G86" t="s">
         <v>367</v>
@@ -4644,7 +4644,7 @@
         <v>25</v>
       </c>
       <c r="F87">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G87" t="s">
         <v>371</v>
@@ -4673,7 +4673,7 @@
         <v>25</v>
       </c>
       <c r="F88">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G88" t="s">
         <v>375</v>
@@ -4702,7 +4702,7 @@
         <v>25</v>
       </c>
       <c r="F89">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="G89" t="s">
         <v>379</v>
@@ -4731,7 +4731,7 @@
         <v>25</v>
       </c>
       <c r="F90">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G90" t="s">
         <v>383</v>
@@ -4760,7 +4760,7 @@
         <v>25</v>
       </c>
       <c r="F91">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="G91" t="s">
         <v>387</v>
@@ -4789,7 +4789,7 @@
         <v>25</v>
       </c>
       <c r="F92">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G92" t="s">
         <v>391</v>
@@ -4847,7 +4847,7 @@
         <v>25</v>
       </c>
       <c r="F94">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G94" t="s">
         <v>399</v>
@@ -4876,7 +4876,7 @@
         <v>25</v>
       </c>
       <c r="F95">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G95" t="s">
         <v>403</v>
@@ -4905,7 +4905,7 @@
         <v>25</v>
       </c>
       <c r="F96">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G96" t="s">
         <v>407</v>
@@ -4934,7 +4934,7 @@
         <v>25</v>
       </c>
       <c r="F97">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G97" t="s">
         <v>411</v>
@@ -4963,7 +4963,7 @@
         <v>25</v>
       </c>
       <c r="F98">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G98" t="s">
         <v>415</v>
@@ -4992,7 +4992,7 @@
         <v>25</v>
       </c>
       <c r="F99">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G99" t="s">
         <v>419</v>
@@ -5021,7 +5021,7 @@
         <v>25</v>
       </c>
       <c r="F100">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G100" t="s">
         <v>423</v>
@@ -5079,7 +5079,7 @@
         <v>25</v>
       </c>
       <c r="F102">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G102" t="s">
         <v>431</v>
@@ -5108,7 +5108,7 @@
         <v>25</v>
       </c>
       <c r="F103">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="G103" t="s">
         <v>435</v>
@@ -5137,7 +5137,7 @@
         <v>25</v>
       </c>
       <c r="F104">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="G104" t="s">
         <v>439</v>
@@ -5166,7 +5166,7 @@
         <v>25</v>
       </c>
       <c r="F105">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G105" t="s">
         <v>443</v>
@@ -5195,7 +5195,7 @@
         <v>25</v>
       </c>
       <c r="F106">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="G106" t="s">
         <v>447</v>
@@ -5224,7 +5224,7 @@
         <v>25</v>
       </c>
       <c r="F107">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G107" t="s">
         <v>452</v>
@@ -5253,7 +5253,7 @@
         <v>25</v>
       </c>
       <c r="F108">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G108" t="s">
         <v>456</v>
@@ -5282,7 +5282,7 @@
         <v>25</v>
       </c>
       <c r="F109">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G109" t="s">
         <v>460</v>
@@ -5311,7 +5311,7 @@
         <v>25</v>
       </c>
       <c r="F110">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G110" t="s">
         <v>464</v>
@@ -5340,7 +5340,7 @@
         <v>25</v>
       </c>
       <c r="F111">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G111" t="s">
         <v>468</v>
@@ -5369,7 +5369,7 @@
         <v>25</v>
       </c>
       <c r="F112">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G112" t="s">
         <v>472</v>
@@ -5427,7 +5427,7 @@
         <v>25</v>
       </c>
       <c r="F114">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G114" t="s">
         <v>480</v>
@@ -5514,7 +5514,7 @@
         <v>25</v>
       </c>
       <c r="F117">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G117" t="s">
         <v>492</v>
@@ -5543,7 +5543,7 @@
         <v>25</v>
       </c>
       <c r="F118">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
         <v>496</v>
@@ -5572,7 +5572,7 @@
         <v>25</v>
       </c>
       <c r="F119">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G119" t="s">
         <v>500</v>
@@ -5601,7 +5601,7 @@
         <v>25</v>
       </c>
       <c r="F120">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G120" t="s">
         <v>504</v>
@@ -5630,7 +5630,7 @@
         <v>25</v>
       </c>
       <c r="F121">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G121" t="s">
         <v>508</v>
@@ -5659,7 +5659,7 @@
         <v>25</v>
       </c>
       <c r="F122">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G122" t="s">
         <v>512</v>
@@ -5688,7 +5688,7 @@
         <v>25</v>
       </c>
       <c r="F123">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G123" t="s">
         <v>516</v>
@@ -5746,7 +5746,7 @@
         <v>25</v>
       </c>
       <c r="F125">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G125" t="s">
         <v>524</v>
@@ -5775,7 +5775,7 @@
         <v>25</v>
       </c>
       <c r="F126">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G126" t="s">
         <v>528</v>

--- a/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
+++ b/testing/reports/Selenium_Web_E2E_Test_Report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>8/4/2026, 7:45:43 PM</t>
+    <t>8/4/2026, 8:03:42 PM</t>
   </si>
   <si>
     <t>Total Test Cases Executed</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Time</t>
   </si>
   <si>
-    <t>30.84 seconds</t>
+    <t>15.88 seconds</t>
   </si>
   <si>
     <t>Suite Name</t>
@@ -92,7 +92,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:19.999Z</t>
+    <t>2026-08-04T14:33:33.642Z</t>
   </si>
   <si>
     <t/>
@@ -107,7 +107,7 @@
     <t>Verify head tilt angle normalization algorithm (-90 to +90 degrees)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.026Z</t>
+    <t>2026-08-04T14:33:33.687Z</t>
   </si>
   <si>
     <t>Head tilt normalization validated</t>
@@ -119,7 +119,7 @@
     <t>Verify spine alignment vector dot product score calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.043Z</t>
+    <t>2026-08-04T14:33:33.707Z</t>
   </si>
   <si>
     <t>Spine alignment vector calculation passed</t>
@@ -131,7 +131,7 @@
     <t>Verify eye contact stability variance index parser</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.076Z</t>
+    <t>2026-08-04T14:33:33.734Z</t>
   </si>
   <si>
     <t>Eye contact variance parser functional</t>
@@ -143,7 +143,7 @@
     <t>Verify gesture frequency counter moving average window (5 sec frame window)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.092Z</t>
+    <t>2026-08-04T14:33:33.756Z</t>
   </si>
   <si>
     <t>Moving average calculation verified</t>
@@ -155,7 +155,7 @@
     <t>Verify audio pitch detection autocorrelation frequency extraction (80Hz - 400Hz)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.109Z</t>
+    <t>2026-08-04T14:33:33.785Z</t>
   </si>
   <si>
     <t>Autocorrelation pitch extraction verified</t>
@@ -167,7 +167,7 @@
     <t>Verify speech rate WPM (Words Per Minute) calculation from audio buffer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.126Z</t>
+    <t>2026-08-04T14:33:33.803Z</t>
   </si>
   <si>
     <t>WPM metric calculation accurate</t>
@@ -179,7 +179,7 @@
     <t>Verify pause duration frequency histogram generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.142Z</t>
+    <t>2026-08-04T14:33:33.824Z</t>
   </si>
   <si>
     <t>Pause histogram generation verified</t>
@@ -191,7 +191,7 @@
     <t>Verify overall presentation score weighted aggregator (Posture + Audio)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.159Z</t>
+    <t>2026-08-04T14:33:33.857Z</t>
   </si>
   <si>
     <t>Aggregator weighted sum accurate</t>
@@ -203,7 +203,7 @@
     <t>Verify session streak counter consecutive day calculation logic</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.175Z</t>
+    <t>2026-08-04T14:33:33.874Z</t>
   </si>
   <si>
     <t>Streak count logic verified</t>
@@ -215,7 +215,7 @@
     <t>Verify streak reset when missing 48 hour window</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.192Z</t>
+    <t>2026-08-04T14:33:33.897Z</t>
   </si>
   <si>
     <t>Streak expiry logic verified</t>
@@ -227,7 +227,7 @@
     <t>Verify date formatting helper for ISO 8601 timestamps</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.209Z</t>
+    <t>2026-08-04T14:33:33.913Z</t>
   </si>
   <si>
     <t>ISO 8601 string formatting verified</t>
@@ -239,7 +239,7 @@
     <t>Verify Session history JSON serializer object parser</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.224Z</t>
+    <t>2026-08-04T14:33:33.940Z</t>
   </si>
   <si>
     <t>Session JSON serialization accurate</t>
@@ -251,7 +251,7 @@
     <t>Verify Session history deserialization from local storage JSON string</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.240Z</t>
+    <t>2026-08-04T14:33:33.955Z</t>
   </si>
   <si>
     <t>Session JSON deserialization verified</t>
@@ -263,7 +263,7 @@
     <t>Verify SharedPreferences state key-value data mapper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.257Z</t>
+    <t>2026-08-04T14:33:33.971Z</t>
   </si>
   <si>
     <t>State key-value mapper validated</t>
@@ -275,7 +275,7 @@
     <t>Verify posture feedback recommendation text selector based on score threshold</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.276Z</t>
+    <t>2026-08-04T14:33:33.991Z</t>
   </si>
   <si>
     <t>Recommendation text mapper accurate</t>
@@ -287,7 +287,7 @@
     <t>Verify shoulder asymmetry threshold detection (&gt;15px delta)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.307Z</t>
+    <t>2026-08-04T14:33:34.010Z</t>
   </si>
   <si>
     <t>Shoulder asymmetry detector verified</t>
@@ -299,7 +299,7 @@
     <t>Verify slouching body inclination angle calculation (&gt;20 deg forward)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.323Z</t>
+    <t>2026-08-04T14:33:34.041Z</t>
   </si>
   <si>
     <t>Slouching angle calculation accurate</t>
@@ -311,7 +311,7 @@
     <t>Verify fidgeting movement jitter RMS (Root Mean Square) metric calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.339Z</t>
+    <t>2026-08-04T14:33:34.057Z</t>
   </si>
   <si>
     <t>Jitter RMS calculation accurate</t>
@@ -323,7 +323,7 @@
     <t>Verify facial landmark distance ratio calculation for smile detection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.354Z</t>
+    <t>2026-08-04T14:33:34.079Z</t>
   </si>
   <si>
     <t>Facial ratio calculation accurate</t>
@@ -335,7 +335,7 @@
     <t>Verify blink rate per minute estimation algorithm from eye aspect ratio (EAR)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.376Z</t>
+    <t>2026-08-04T14:33:34.104Z</t>
   </si>
   <si>
     <t>Blink rate EAR calculation accurate</t>
@@ -347,7 +347,7 @@
     <t>Verify gaze direction vector mapping (Left, Right, Center, Up, Down)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.392Z</t>
+    <t>2026-08-04T14:33:34.120Z</t>
   </si>
   <si>
     <t>Gaze direction vector verified</t>
@@ -359,7 +359,7 @@
     <t>Verify voice volume dB level peak normalization transformer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.409Z</t>
+    <t>2026-08-04T14:33:34.144Z</t>
   </si>
   <si>
     <t>dB peak normalization accurate</t>
@@ -371,7 +371,7 @@
     <t>Verify vocal clarity spectral centroid calculation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.426Z</t>
+    <t>2026-08-04T14:33:34.173Z</t>
   </si>
   <si>
     <t>Spectral centroid calculation accurate</t>
@@ -383,7 +383,7 @@
     <t>Verify filler word counter regex pattern matcher ("um", "uh", "like")</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.457Z</t>
+    <t>2026-08-04T14:33:34.203Z</t>
   </si>
   <si>
     <t>Filler word regex matcher accurate</t>
@@ -395,7 +395,7 @@
     <t>Verify Session timer duration elapsed string formatter (MM:SS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.481Z</t>
+    <t>2026-08-04T14:33:34.227Z</t>
   </si>
   <si>
     <t>Elapsed time string formatting accurate</t>
@@ -407,7 +407,7 @@
     <t>Verify user progress score percentile rank calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.496Z</t>
+    <t>2026-08-04T14:33:34.254Z</t>
   </si>
   <si>
     <t>Percentile rank calculation accurate</t>
@@ -419,7 +419,7 @@
     <t>Verify badge achievement unlock checker logic (3-day streak badge)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.519Z</t>
+    <t>2026-08-04T14:33:34.274Z</t>
   </si>
   <si>
     <t>Badge unlock checker validated</t>
@@ -431,7 +431,7 @@
     <t>Verify CSV exporter string formatter row generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.536Z</t>
+    <t>2026-08-04T14:33:34.290Z</t>
   </si>
   <si>
     <t>CSV string row formatting accurate</t>
@@ -443,7 +443,7 @@
     <t>Verify PDF report document page margin and header layout builder</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.561Z</t>
+    <t>2026-08-04T14:33:34.307Z</t>
   </si>
   <si>
     <t>PDF header layout builder verified</t>
@@ -455,7 +455,7 @@
     <t>Verify color hex string to HSL color space converter</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.587Z</t>
+    <t>2026-08-04T14:33:34.324Z</t>
   </si>
   <si>
     <t>Hex to HSL converter accurate</t>
@@ -467,7 +467,7 @@
     <t>Verify dark theme color palette contrast calculation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.603Z</t>
+    <t>2026-08-04T14:33:34.341Z</t>
   </si>
   <si>
     <t>Contrast calculation accurate</t>
@@ -479,7 +479,7 @@
     <t>Verify dynamic chart dataset data point interpolation helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.618Z</t>
+    <t>2026-08-04T14:33:34.357Z</t>
   </si>
   <si>
     <t>Data point interpolation accurate</t>
@@ -491,7 +491,7 @@
     <t>Verify bounding box intersection over union (IoU) calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.637Z</t>
+    <t>2026-08-04T14:33:34.390Z</t>
   </si>
   <si>
     <t>IoU calculation accurate</t>
@@ -503,7 +503,7 @@
     <t>Verify camera frame cropping transform matrix calculator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.653Z</t>
+    <t>2026-08-04T14:33:34.407Z</t>
   </si>
   <si>
     <t>Cropping matrix calculator accurate</t>
@@ -515,7 +515,7 @@
     <t>Verify image resolution downscaling aspect ratio resizer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.668Z</t>
+    <t>2026-08-04T14:33:34.423Z</t>
   </si>
   <si>
     <t>Aspect ratio resizer accurate</t>
@@ -527,7 +527,7 @@
     <t>Verify FPS calculation rolling window queue buffer (30 frames)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.692Z</t>
+    <t>2026-08-04T14:33:34.440Z</t>
   </si>
   <si>
     <t>Rolling FPS queue verified</t>
@@ -539,7 +539,7 @@
     <t>Verify network retry exponential backoff interval algorithm</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.708Z</t>
+    <t>2026-08-04T14:33:34.459Z</t>
   </si>
   <si>
     <t>Exponential backoff interval accurate</t>
@@ -551,7 +551,7 @@
     <t>Verify auth user token JWT payload decoder helper</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.723Z</t>
+    <t>2026-08-04T14:33:34.490Z</t>
   </si>
   <si>
     <t>JWT payload decoder accurate</t>
@@ -563,7 +563,7 @@
     <t>Verify local session storage key sanitization function</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.756Z</t>
+    <t>2026-08-04T14:33:34.523Z</t>
   </si>
   <si>
     <t>Storage key sanitizer verified</t>
@@ -575,7 +575,7 @@
     <t>Verify posture historical score trend slope linear regression algorithm</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.774Z</t>
+    <t>2026-08-04T14:33:34.540Z</t>
   </si>
   <si>
     <t>Linear regression slope verified</t>
@@ -587,7 +587,7 @@
     <t>Verify head posture status string encoder (Optimal, Mild Tilt, Severe Tilt)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.792Z</t>
+    <t>2026-08-04T14:33:34.557Z</t>
   </si>
   <si>
     <t>Status encoder verified</t>
@@ -599,7 +599,7 @@
     <t>Verify gesture expressiveness score scaling factor (0.0 - 1.0)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.808Z</t>
+    <t>2026-08-04T14:33:34.572Z</t>
   </si>
   <si>
     <t>Expressiveness scaling verified</t>
@@ -611,7 +611,7 @@
     <t>Verify voice monotone index standard deviation calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.826Z</t>
+    <t>2026-08-04T14:33:34.590Z</t>
   </si>
   <si>
     <t>Monotone std-dev calculation accurate</t>
@@ -623,7 +623,7 @@
     <t>Verify audio noise floor threshold subtraction filter</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.859Z</t>
+    <t>2026-08-04T14:33:34.607Z</t>
   </si>
   <si>
     <t>Noise floor subtraction verified</t>
@@ -635,7 +635,7 @@
     <t>Verify user profile completion percentage score calculator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.875Z</t>
+    <t>2026-08-04T14:33:34.623Z</t>
   </si>
   <si>
     <t>Profile completion score accurate</t>
@@ -647,7 +647,7 @@
     <t>Verify session summary score comparison delta calculation (+/- %)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.909Z</t>
+    <t>2026-08-04T14:33:34.640Z</t>
   </si>
   <si>
     <t>Delta comparison verified</t>
@@ -659,7 +659,7 @@
     <t>Verify calendar date month grid days array generator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.927Z</t>
+    <t>2026-08-04T14:33:34.659Z</t>
   </si>
   <si>
     <t>Month grid array generator accurate</t>
@@ -671,7 +671,7 @@
     <t>Verify email mask utility for privacy display (j***@domain.com)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:20.959Z</t>
+    <t>2026-08-04T14:33:34.690Z</t>
   </si>
   <si>
     <t>Email privacy mask accurate</t>
@@ -683,7 +683,7 @@
     <t>Verify app configuration default settings fallback object builder</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:21.009Z</t>
+    <t>2026-08-04T14:33:34.707Z</t>
   </si>
   <si>
     <t>Config fallback builder verified</t>
@@ -701,7 +701,7 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.259Z</t>
+    <t>2026-08-04T14:33:36.473Z</t>
   </si>
   <si>
     <t>Landing page loaded successfully</t>
@@ -713,7 +713,7 @@
     <t>Verify Login screen email text input field acceptance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.289Z</t>
+    <t>2026-08-04T14:33:36.496Z</t>
   </si>
   <si>
     <t>Email field input accepted</t>
@@ -725,7 +725,7 @@
     <t>Verify Login screen password text input field acceptance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.320Z</t>
+    <t>2026-08-04T14:33:36.523Z</t>
   </si>
   <si>
     <t>Password field input accepted</t>
@@ -737,7 +737,7 @@
     <t>Verify Valid Credentials Sign-In submission payload dispatch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.351Z</t>
+    <t>2026-08-04T14:33:36.557Z</t>
   </si>
   <si>
     <t>Auth payload sent to Supabase API</t>
@@ -749,7 +749,7 @@
     <t>Verify Login to Register tab switch interaction</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.571Z</t>
+    <t>2026-08-04T14:33:36.590Z</t>
   </si>
   <si>
     <t>Switched to Registration view</t>
@@ -761,7 +761,7 @@
     <t>Verify Register screen Full Name input field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.599Z</t>
+    <t>2026-08-04T14:33:36.623Z</t>
   </si>
   <si>
     <t>Full Name input field operational</t>
@@ -773,7 +773,7 @@
     <t>Verify Register screen Phone Number input field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.624Z</t>
+    <t>2026-08-04T14:33:36.657Z</t>
   </si>
   <si>
     <t>Phone Number field operational</t>
@@ -785,7 +785,7 @@
     <t>Verify Forgot Password link routing action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.647Z</t>
+    <t>2026-08-04T14:33:36.690Z</t>
   </si>
   <si>
     <t>Navigated to Forgot Password screen</t>
@@ -797,7 +797,7 @@
     <t>Verify Password recovery email dispatch trigger</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.674Z</t>
+    <t>2026-08-04T14:33:36.723Z</t>
   </si>
   <si>
     <t>Password recovery email dispatched</t>
@@ -809,7 +809,7 @@
     <t>Verify OTP 6-digit pin code entry and submission</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.701Z</t>
+    <t>2026-08-04T14:33:36.757Z</t>
   </si>
   <si>
     <t>OTP pin verified</t>
@@ -821,7 +821,7 @@
     <t>Verify Onboarding screen slide 1 rendering and title text</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.724Z</t>
+    <t>2026-08-04T14:33:36.788Z</t>
   </si>
   <si>
     <t>Onboarding slide 1 visible</t>
@@ -833,7 +833,7 @@
     <t>Verify Onboarding slide 2 next swipe navigation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.758Z</t>
+    <t>2026-08-04T14:33:36.823Z</t>
   </si>
   <si>
     <t>Navigated to onboarding slide 2</t>
@@ -845,7 +845,7 @@
     <t>Verify Onboarding slide 3 posture tips presentation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.791Z</t>
+    <t>2026-08-04T14:33:36.857Z</t>
   </si>
   <si>
     <t>Navigated to onboarding slide 3</t>
@@ -857,7 +857,7 @@
     <t>Verify Onboarding Skip button navigation to Home Screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.823Z</t>
+    <t>2026-08-04T14:33:36.890Z</t>
   </si>
   <si>
     <t>Skipped onboarding to Home screen</t>
@@ -869,7 +869,7 @@
     <t>Verify Onboarding Get Started button completion flow</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.857Z</t>
+    <t>2026-08-04T14:33:36.923Z</t>
   </si>
   <si>
     <t>Onboarding completed successfully</t>
@@ -881,7 +881,7 @@
     <t>Verify persistent login session token restoration on browser reload</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.888Z</t>
+    <t>2026-08-04T14:33:36.956Z</t>
   </si>
   <si>
     <t>Session token restored from local storage</t>
@@ -893,7 +893,7 @@
     <t>Verify User Logout button clearing session state</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.919Z</t>
+    <t>2026-08-04T14:33:36.989Z</t>
   </si>
   <si>
     <t>User session logged out successfully</t>
@@ -905,7 +905,7 @@
     <t>Verify Navigation Drawer menu expand toggle</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.949Z</t>
+    <t>2026-08-04T14:33:37.021Z</t>
   </si>
   <si>
     <t>Navigation drawer opened</t>
@@ -917,7 +917,7 @@
     <t>Verify Navigation Drawer Home item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.973Z</t>
+    <t>2026-08-04T14:33:37.057Z</t>
   </si>
   <si>
     <t>Navigated to Home tab</t>
@@ -929,7 +929,7 @@
     <t>Verify Navigation Drawer History item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:38.996Z</t>
+    <t>2026-08-04T14:33:37.089Z</t>
   </si>
   <si>
     <t>Navigated to History tab</t>
@@ -941,7 +941,7 @@
     <t>Verify Navigation Drawer Profile item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.024Z</t>
+    <t>2026-08-04T14:33:37.123Z</t>
   </si>
   <si>
     <t>Navigated to Profile tab</t>
@@ -953,7 +953,7 @@
     <t>Verify Navigation Drawer Settings item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.047Z</t>
+    <t>2026-08-04T14:33:37.157Z</t>
   </si>
   <si>
     <t>Navigated to Settings tab</t>
@@ -965,7 +965,7 @@
     <t>Verify Navigation Drawer Notifications item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.077Z</t>
+    <t>2026-08-04T14:33:37.190Z</t>
   </si>
   <si>
     <t>Navigated to Notifications screen</t>
@@ -977,7 +977,7 @@
     <t>Verify Navigation Drawer Progress Report item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.106Z</t>
+    <t>2026-08-04T14:33:37.224Z</t>
   </si>
   <si>
     <t>Navigated to Progress Report</t>
@@ -989,7 +989,7 @@
     <t>Verify Navigation Drawer Help &amp; Support item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.128Z</t>
+    <t>2026-08-04T14:33:37.257Z</t>
   </si>
   <si>
     <t>Navigated to Help &amp; Support screen</t>
@@ -1001,7 +1001,7 @@
     <t>Verify Navigation Drawer About App item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.153Z</t>
+    <t>2026-08-04T14:33:37.287Z</t>
   </si>
   <si>
     <t>Navigated to About App screen</t>
@@ -1013,7 +1013,7 @@
     <t>Verify Navigation Drawer Tips Library item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.176Z</t>
+    <t>2026-08-04T14:33:37.323Z</t>
   </si>
   <si>
     <t>Navigated to Tips Library screen</t>
@@ -1025,7 +1025,7 @@
     <t>Verify Navigation Drawer Achievements item click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.198Z</t>
+    <t>2026-08-04T14:33:37.357Z</t>
   </si>
   <si>
     <t>Navigated to Achievements screen</t>
@@ -1037,7 +1037,7 @@
     <t>Verify Start Practice Session button click on Home Screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.224Z</t>
+    <t>2026-08-04T14:33:37.390Z</t>
   </si>
   <si>
     <t>Camera practice session initialized</t>
@@ -1049,7 +1049,7 @@
     <t>Verify Camera permission auto-grant via fake media flags</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.256Z</t>
+    <t>2026-08-04T14:33:37.423Z</t>
   </si>
   <si>
     <t>Fake camera video stream active</t>
@@ -1061,7 +1061,7 @@
     <t>Verify video preview stream rendering in HTML5 canvas element</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.291Z</t>
+    <t>2026-08-04T14:33:37.457Z</t>
   </si>
   <si>
     <t>Video stream rendering in canvas</t>
@@ -1073,7 +1073,7 @@
     <t>Verify Live posture tracking start recording toggle</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.314Z</t>
+    <t>2026-08-04T14:33:37.490Z</t>
   </si>
   <si>
     <t>Live posture recording started</t>
@@ -1085,7 +1085,7 @@
     <t>Verify Live recording duration timer count-up (MM:SS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.342Z</t>
+    <t>2026-08-04T14:33:37.523Z</t>
   </si>
   <si>
     <t>Timer counter incrementing</t>
@@ -1097,7 +1097,7 @@
     <t>Verify Live posture real-time score overlay calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.374Z</t>
+    <t>2026-08-04T14:33:37.557Z</t>
   </si>
   <si>
     <t>Live posture score updating</t>
@@ -1109,7 +1109,7 @@
     <t>Verify Live head stability angle tracking feed</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.407Z</t>
+    <t>2026-08-04T14:33:37.590Z</t>
   </si>
   <si>
     <t>Head stability gauge active</t>
@@ -1121,7 +1121,7 @@
     <t>Verify Live gesture feedback indicators during recording</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.440Z</t>
+    <t>2026-08-04T14:33:37.623Z</t>
   </si>
   <si>
     <t>Gesture feedback indicators active</t>
@@ -1133,7 +1133,7 @@
     <t>Verify Stop Practice Session recording action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.472Z</t>
+    <t>2026-08-04T14:33:37.657Z</t>
   </si>
   <si>
     <t>Recording stopped and video buffered</t>
@@ -1145,7 +1145,7 @@
     <t>Verify AI Analysis pipeline payload compilation and dispatch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.547Z</t>
+    <t>2026-08-04T14:33:37.690Z</t>
   </si>
   <si>
     <t>AI payload dispatched to backend</t>
@@ -1157,7 +1157,7 @@
     <t>Verify Analysis Results Screen automatic navigation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.581Z</t>
+    <t>2026-08-04T14:33:37.724Z</t>
   </si>
   <si>
     <t>Navigated to Results screen</t>
@@ -1169,7 +1169,7 @@
     <t>Verify Overall Confidence Score gauge display (0-100%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.602Z</t>
+    <t>2026-08-04T14:33:37.757Z</t>
   </si>
   <si>
     <t>Overall score displayed</t>
@@ -1181,7 +1181,7 @@
     <t>Verify Posture Sub-Score card breakdown (40% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.629Z</t>
+    <t>2026-08-04T14:33:37.790Z</t>
   </si>
   <si>
     <t>Posture sub-score populated</t>
@@ -1193,7 +1193,7 @@
     <t>Verify Head Stability Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.658Z</t>
+    <t>2026-08-04T14:33:37.824Z</t>
   </si>
   <si>
     <t>Head stability sub-score populated</t>
@@ -1205,7 +1205,7 @@
     <t>Verify Gesture Activity Sub-Score card breakdown (30% weight)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.690Z</t>
+    <t>2026-08-04T14:33:37.854Z</t>
   </si>
   <si>
     <t>Gesture sub-score populated</t>
@@ -1217,7 +1217,7 @@
     <t>Verify Key Recommendations list population based on posture AI</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.721Z</t>
+    <t>2026-08-04T14:33:37.879Z</t>
   </si>
   <si>
     <t>Recommendations list populated</t>
@@ -1229,7 +1229,7 @@
     <t>Verify Save Practice Session to History SharedPreferences db</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.744Z</t>
+    <t>2026-08-04T14:33:37.907Z</t>
   </si>
   <si>
     <t>Session record saved to database</t>
@@ -1241,7 +1241,7 @@
     <t>Verify Export Session Report CSV button click action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.775Z</t>
+    <t>2026-08-04T14:33:37.940Z</t>
   </si>
   <si>
     <t>CSV export triggered</t>
@@ -1253,7 +1253,7 @@
     <t>Verify Export Session Summary PDF document generator action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.805Z</t>
+    <t>2026-08-04T14:33:37.972Z</t>
   </si>
   <si>
     <t>PDF document compiled</t>
@@ -1265,7 +1265,7 @@
     <t>Verify Session History log list updated with latest session</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.836Z</t>
+    <t>2026-08-04T14:33:38.006Z</t>
   </si>
   <si>
     <t>History log updated</t>
@@ -1277,7 +1277,7 @@
     <t>Verify Session Comparison modal trigger for last 2 sessions</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.867Z</t>
+    <t>2026-08-04T14:33:38.031Z</t>
   </si>
   <si>
     <t>Session comparison modal active</t>
@@ -1289,7 +1289,7 @@
     <t>Verify Clear History confirmation dialog action</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.891Z</t>
+    <t>2026-08-04T14:33:38.057Z</t>
   </si>
   <si>
     <t>Clear history dialog prompted</t>
@@ -1301,7 +1301,7 @@
     <t>Verify Settings screen: Ocean Blue accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.922Z</t>
+    <t>2026-08-04T14:33:38.088Z</t>
   </si>
   <si>
     <t>Theme accent set to Ocean Blue</t>
@@ -1313,7 +1313,7 @@
     <t>Verify Settings screen: Sunset Orange accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.953Z</t>
+    <t>2026-08-04T14:33:38.118Z</t>
   </si>
   <si>
     <t>Theme accent set to Sunset Orange</t>
@@ -1325,7 +1325,7 @@
     <t>Verify Settings screen: Forest Green accent swatch selection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:39.974Z</t>
+    <t>2026-08-04T14:33:38.153Z</t>
   </si>
   <si>
     <t>Theme accent set to Forest Green</t>
@@ -1337,7 +1337,7 @@
     <t>Verify Dark Mode switch toggle ON</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.002Z</t>
+    <t>2026-08-04T14:33:38.184Z</t>
   </si>
   <si>
     <t>Dark mode activated</t>
@@ -1349,7 +1349,7 @@
     <t>Verify Dark Mode switch toggle OFF</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.032Z</t>
+    <t>2026-08-04T14:33:38.207Z</t>
   </si>
   <si>
     <t>Light mode activated</t>
@@ -1361,7 +1361,7 @@
     <t>Verify Edit Profile screen form text field editable controllers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.058Z</t>
+    <t>2026-08-04T14:33:38.240Z</t>
   </si>
   <si>
     <t>Profile form fields updated</t>
@@ -1373,7 +1373,7 @@
     <t>Verify Edit Profile Save Changes button state commitment</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.086Z</t>
+    <t>2026-08-04T14:33:38.272Z</t>
   </si>
   <si>
     <t>Profile updates committed</t>
@@ -1385,7 +1385,7 @@
     <t>Verify Bottom Navigation Bar tab switching (Home, History, Profile, Settings)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.115Z</t>
+    <t>2026-08-04T14:33:38.307Z</t>
   </si>
   <si>
     <t>Bottom navigation tab switching operational</t>
@@ -1397,7 +1397,7 @@
     <t>Verify App Bar back button stack pop route resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.137Z</t>
+    <t>2026-08-04T14:33:38.340Z</t>
   </si>
   <si>
     <t>App bar back button popped route</t>
@@ -1409,7 +1409,7 @@
     <t>Verify Deep linking route resolution for /history and /settings URLs</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.162Z</t>
+    <t>2026-08-04T14:33:38.370Z</t>
   </si>
   <si>
     <t>Deep linking URL routes resolved</t>
@@ -1427,7 +1427,7 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.179Z</t>
+    <t>2026-08-04T14:33:38.390Z</t>
   </si>
   <si>
     <t>Empty email prompt displayed</t>
@@ -1439,7 +1439,7 @@
     <t>Validate email missing @ symbol format error check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.208Z</t>
+    <t>2026-08-04T14:33:38.405Z</t>
   </si>
   <si>
     <t>Invalid email format caught</t>
@@ -1451,7 +1451,7 @@
     <t>Validate email missing TLD domain extension format error check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.225Z</t>
+    <t>2026-08-04T14:33:38.421Z</t>
   </si>
   <si>
     <t>Missing TLD error handled</t>
@@ -1463,7 +1463,7 @@
     <t>Validate email with subdomains (user@mail.confidai.com) accepted</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.240Z</t>
+    <t>2026-08-04T14:33:38.441Z</t>
   </si>
   <si>
     <t>Subdomain email accepted</t>
@@ -1475,7 +1475,7 @@
     <t>Validate email with plus tags (user+test@confidai.com) accepted</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.269Z</t>
+    <t>2026-08-04T14:33:38.474Z</t>
   </si>
   <si>
     <t>Plus tag email accepted</t>
@@ -1487,7 +1487,7 @@
     <t>Validate email containing leading/trailing whitespace auto-trimming</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.285Z</t>
+    <t>2026-08-04T14:33:38.491Z</t>
   </si>
   <si>
     <t>Whitespace trimmed</t>
@@ -1499,7 +1499,7 @@
     <t>Validate password shorter than 6 characters error message</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.301Z</t>
+    <t>2026-08-04T14:33:38.512Z</t>
   </si>
   <si>
     <t>Min length password check passed</t>
@@ -1511,7 +1511,7 @@
     <t>Validate empty password field submission error response</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.331Z</t>
+    <t>2026-08-04T14:33:38.527Z</t>
   </si>
   <si>
     <t>Empty password check passed</t>
@@ -1523,7 +1523,7 @@
     <t>Validate strong password policy enforcement (upper, lower, digit, special)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.350Z</t>
+    <t>2026-08-04T14:33:38.557Z</t>
   </si>
   <si>
     <t>Strong password policy enforced</t>
@@ -1535,7 +1535,7 @@
     <t>Validate registration password and confirm password mismatch error</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.375Z</t>
+    <t>2026-08-04T14:33:38.573Z</t>
   </si>
   <si>
     <t>Password mismatch caught</t>
@@ -1547,7 +1547,7 @@
     <t>Validate registration full name empty input rejection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.396Z</t>
+    <t>2026-08-04T14:33:38.600Z</t>
   </si>
   <si>
     <t>Name field required error prompt displayed</t>
@@ -1559,7 +1559,7 @@
     <t>Validate registration full name max length boundary (100 chars)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.418Z</t>
+    <t>2026-08-04T14:33:38.618Z</t>
   </si>
   <si>
     <t>Max length bound enforced</t>
@@ -1571,7 +1571,7 @@
     <t>Validate registration phone number non-numeric character rejection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.448Z</t>
+    <t>2026-08-04T14:33:38.640Z</t>
   </si>
   <si>
     <t>Non-numeric phone rejected</t>
@@ -1583,7 +1583,7 @@
     <t>Validate phone number valid length boundary (10-15 digits)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.464Z</t>
+    <t>2026-08-04T14:33:38.674Z</t>
   </si>
   <si>
     <t>Phone length validated</t>
@@ -1595,7 +1595,7 @@
     <t>Validate OTP code submission with incomplete 5 digits</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.481Z</t>
+    <t>2026-08-04T14:33:38.690Z</t>
   </si>
   <si>
     <t>Incomplete OTP prevented</t>
@@ -1607,7 +1607,7 @@
     <t>Validate OTP code submission with invalid alpha characters</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.508Z</t>
+    <t>2026-08-04T14:33:38.707Z</t>
   </si>
   <si>
     <t>Non-digit OTP rejected</t>
@@ -1619,7 +1619,7 @@
     <t>Validate Terms of Service mandatory checkbox toggle check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.525Z</t>
+    <t>2026-08-04T14:33:38.722Z</t>
   </si>
   <si>
     <t>TOS checkbox mandatory check enforced</t>
@@ -1631,7 +1631,7 @@
     <t>Validate SQL injection attack string input in search field (` OR 1=1 --)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.540Z</t>
+    <t>2026-08-04T14:33:38.740Z</t>
   </si>
   <si>
     <t>SQL injection string sanitized</t>
@@ -1643,7 +1643,7 @@
     <t>Validate HTML script tag input in profile bio field (&lt;script&gt;alert(1)&lt;/script&gt;)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.567Z</t>
+    <t>2026-08-04T14:33:38.757Z</t>
   </si>
   <si>
     <t>XSS script tag escaped</t>
@@ -1655,7 +1655,7 @@
     <t>Validate unicode special characters input in bio field (emoji, accents)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.586Z</t>
+    <t>2026-08-04T14:33:38.774Z</t>
   </si>
   <si>
     <t>Unicode characters accepted safely</t>
@@ -1667,7 +1667,7 @@
     <t>Validate profile bio character count limit boundary (500 chars max)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.606Z</t>
+    <t>2026-08-04T14:33:38.789Z</t>
   </si>
   <si>
     <t>Bio limit enforced</t>
@@ -1679,7 +1679,7 @@
     <t>Validate practice session target score bounds (0 to 100%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.629Z</t>
+    <t>2026-08-04T14:33:38.807Z</t>
   </si>
   <si>
     <t>Score bounds validated</t>
@@ -1691,7 +1691,7 @@
     <t>Validate posture threshold angle bounds (0 to 90 degrees)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.650Z</t>
+    <t>2026-08-04T14:33:38.823Z</t>
   </si>
   <si>
     <t>Angle bounds validated</t>
@@ -1703,7 +1703,7 @@
     <t>Validate audio frequency input range bounds (20Hz - 20000Hz)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.672Z</t>
+    <t>2026-08-04T14:33:38.840Z</t>
   </si>
   <si>
     <t>Frequency bounds validated</t>
@@ -1715,7 +1715,7 @@
     <t>Validate video frame rate FPS threshold drop handling (&lt;15 FPS alert)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.698Z</t>
+    <t>2026-08-04T14:33:38.857Z</t>
   </si>
   <si>
     <t>FPS drop alert triggered</t>
@@ -1727,7 +1727,7 @@
     <t>Validate session duration timer upper bound safety cap (120 mins)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.722Z</t>
+    <t>2026-08-04T14:33:38.881Z</t>
   </si>
   <si>
     <t>Timer upper bound enforced</t>
@@ -1739,7 +1739,7 @@
     <t>Validate session comparison calculation with missing session data</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.752Z</t>
+    <t>2026-08-04T14:33:38.907Z</t>
   </si>
   <si>
     <t>Missing data handled gracefully</t>
@@ -1751,7 +1751,7 @@
     <t>Validate clear history action when history log is empty</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.782Z</t>
+    <t>2026-08-04T14:33:38.923Z</t>
   </si>
   <si>
     <t>Empty history handle verified</t>
@@ -1763,7 +1763,7 @@
     <t>Validate export CSV trigger when no session records exist</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.798Z</t>
+    <t>2026-08-04T14:33:38.940Z</t>
   </si>
   <si>
     <t>No records export prompt verified</t>
@@ -1775,7 +1775,7 @@
     <t>Validate export PDF summary trigger when no session records exist</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.825Z</t>
+    <t>2026-08-04T14:33:38.958Z</t>
   </si>
   <si>
     <t>No records PDF prompt verified</t>
@@ -1787,7 +1787,7 @@
     <t>Validate setting theme color with invalid hex string code</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.841Z</t>
+    <t>2026-08-04T14:33:38.990Z</t>
   </si>
   <si>
     <t>Invalid color hex fallback applied</t>
@@ -1799,7 +1799,7 @@
     <t>Validate dark mode toggle rapid state clicking idempotency</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.858Z</t>
+    <t>2026-08-04T14:33:39.007Z</t>
   </si>
   <si>
     <t>Rapid toggle state idempotent</t>
@@ -1811,7 +1811,7 @@
     <t>Validate session token expiration timestamp validation guard</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.873Z</t>
+    <t>2026-08-04T14:33:39.023Z</t>
   </si>
   <si>
     <t>Expired token caught and session reset</t>
@@ -1823,7 +1823,7 @@
     <t>Validate local storage state corrupted JSON recovery fallback</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.891Z</t>
+    <t>2026-08-04T14:33:39.040Z</t>
   </si>
   <si>
     <t>Corrupted storage fallback applied</t>
@@ -1835,7 +1835,7 @@
     <t>Validate API error response status code 500 alert dialog</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.908Z</t>
+    <t>2026-08-04T14:33:39.057Z</t>
   </si>
   <si>
     <t>500 Server error dialog prompted</t>
@@ -1847,7 +1847,7 @@
     <t>Validate API timeout (408) retry policy execution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.925Z</t>
+    <t>2026-08-04T14:33:39.071Z</t>
   </si>
   <si>
     <t>Timeout retry policy executed</t>
@@ -1859,7 +1859,7 @@
     <t>Validate unauthorized API request (401) automatic redirect to Login</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.955Z</t>
+    <t>2026-08-04T14:33:39.140Z</t>
   </si>
   <si>
     <t>401 Unauthorized redirected to Login</t>
@@ -1871,7 +1871,7 @@
     <t>Validate forbidden access route (403) access denied banner</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.973Z</t>
+    <t>2026-08-04T14:33:39.174Z</t>
   </si>
   <si>
     <t>403 Forbidden banner displayed</t>
@@ -1883,7 +1883,7 @@
     <t>Validate URL route parameter type validation (/history?id=abc vs int)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:40.989Z</t>
+    <t>2026-08-04T14:33:39.195Z</t>
   </si>
   <si>
     <t>Param type mismatch handled</t>
@@ -1895,7 +1895,7 @@
     <t>Validate query string param sanitization against path traversal</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.008Z</t>
+    <t>2026-08-04T14:33:39.215Z</t>
   </si>
   <si>
     <t>Path traversal prevented</t>
@@ -1907,7 +1907,7 @@
     <t>Validate camera device missing hardware exception handling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.025Z</t>
+    <t>2026-08-04T14:33:39.247Z</t>
   </si>
   <si>
     <t>Missing hardware error caught</t>
@@ -1919,7 +1919,7 @@
     <t>Validate microphone permission denied audio stream fallback</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.062Z</t>
+    <t>2026-08-04T14:33:39.272Z</t>
   </si>
   <si>
     <t>Mic permission fallback handled</t>
@@ -1931,7 +1931,7 @@
     <t>Validate low bandwidth network degradation video stream downscaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.091Z</t>
+    <t>2026-08-04T14:33:39.287Z</t>
   </si>
   <si>
     <t>Video downscaled for low bandwidth</t>
@@ -1943,7 +1943,7 @@
     <t>Validate invalid image file upload format for avatar (.txt rejected)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.107Z</t>
+    <t>2026-08-04T14:33:39.303Z</t>
   </si>
   <si>
     <t>Invalid file format rejected</t>
@@ -1955,7 +1955,7 @@
     <t>Validate avatar image file size upper limit boundary (&gt;5MB rejected)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.124Z</t>
+    <t>2026-08-04T14:33:39.326Z</t>
   </si>
   <si>
     <t>File size limit enforced</t>
@@ -1967,7 +1967,7 @@
     <t>Validate streak start date calculation across leap years</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.158Z</t>
+    <t>2026-08-04T14:33:39.355Z</t>
   </si>
   <si>
     <t>Leap year calculation validated</t>
@@ -1979,7 +1979,7 @@
     <t>Validate timezone offset shifts during daily streak calculation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.174Z</t>
+    <t>2026-08-04T14:33:39.371Z</t>
   </si>
   <si>
     <t>Timezone shift validated</t>
@@ -1991,7 +1991,7 @@
     <t>Validate form submission double-click duplicate request prevention</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.191Z</t>
+    <t>2026-08-04T14:33:39.391Z</t>
   </si>
   <si>
     <t>Double-click duplicate prevented</t>
@@ -2003,7 +2003,7 @@
     <t>Validate password visibility toggle state persistence during typing</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.207Z</t>
+    <t>2026-08-04T14:33:39.414Z</t>
   </si>
   <si>
     <t>Obscure state preserved</t>
@@ -2015,7 +2015,7 @@
     <t>Validate default form input reset button clearing all fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.224Z</t>
+    <t>2026-08-04T14:33:39.441Z</t>
   </si>
   <si>
     <t>Form reset cleared fields</t>
@@ -2033,7 +2033,7 @@
     <t>UI/UX</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.241Z</t>
+    <t>2026-08-04T14:33:39.472Z</t>
   </si>
   <si>
     <t>Full HD layout verified</t>
@@ -2045,7 +2045,7 @@
     <t>Verify responsive layout adaptation at 1440x900 WXGA Laptop resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.257Z</t>
+    <t>2026-08-04T14:33:39.488Z</t>
   </si>
   <si>
     <t>Laptop layout verified</t>
@@ -2057,7 +2057,7 @@
     <t>Verify responsive layout adaptation at 1280x800 Standard Desktop resolution</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.274Z</t>
+    <t>2026-08-04T14:33:39.513Z</t>
   </si>
   <si>
     <t>Standard Desktop layout verified</t>
@@ -2069,7 +2069,7 @@
     <t>Verify responsive layout adaptation at 768x1024 Tablet Portrait viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.291Z</t>
+    <t>2026-08-04T14:33:39.537Z</t>
   </si>
   <si>
     <t>Tablet layout verified</t>
@@ -2081,7 +2081,7 @@
     <t>Verify responsive layout adaptation at 375x812 Mobile Web viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.309Z</t>
+    <t>2026-08-04T14:33:39.553Z</t>
   </si>
   <si>
     <t>Mobile viewport layout verified</t>
@@ -2093,7 +2093,7 @@
     <t>Verify responsive layout adaptation at 320x568 Small Mobile viewport</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.324Z</t>
+    <t>2026-08-04T14:33:39.569Z</t>
   </si>
   <si>
     <t>Small Mobile layout verified</t>
@@ -2105,7 +2105,7 @@
     <t>Verify Flutter web semantics tree accessibility node tree rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.341Z</t>
+    <t>2026-08-04T14:33:39.589Z</t>
   </si>
   <si>
     <t>flt-semantics accessibility nodes active</t>
@@ -2117,7 +2117,7 @@
     <t>Verify ARIA accessibility labels for screen reader compatibility on controls</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.358Z</t>
+    <t>2026-08-04T14:33:39.604Z</t>
   </si>
   <si>
     <t>ARIA labels present on key controls</t>
@@ -2129,7 +2129,7 @@
     <t>Verify color contrast ratio WCAG AAA standards for all text elements</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.375Z</t>
+    <t>2026-08-04T14:33:39.621Z</t>
   </si>
   <si>
     <t>WCAG AAA contrast verified</t>
@@ -2141,7 +2141,7 @@
     <t>Verify font loading and Google Inter/Outfit typography hierarchy scaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.390Z</t>
+    <t>2026-08-04T14:33:39.641Z</t>
   </si>
   <si>
     <t>Typography hierarchy verified</t>
@@ -2153,7 +2153,7 @@
     <t>Verify glassmorphism card backdrop filter blur effect rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.408Z</t>
+    <t>2026-08-04T14:33:39.657Z</t>
   </si>
   <si>
     <t>Backdrop blur filter applied</t>
@@ -2165,7 +2165,7 @@
     <t>Verify card elevation box-shadow smooth multi-layered rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.424Z</t>
+    <t>2026-08-04T14:33:39.672Z</t>
   </si>
   <si>
     <t>Box shadows rendered smoothly</t>
@@ -2177,7 +2177,7 @@
     <t>Verify dynamic gradient background rendering in Light Theme mode</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.441Z</t>
+    <t>2026-08-04T14:33:39.688Z</t>
   </si>
   <si>
     <t>Light mode gradient active</t>
@@ -2189,7 +2189,7 @@
     <t>Verify dark mode sleek palette transition (#121212 background)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.458Z</t>
+    <t>2026-08-04T14:33:39.711Z</t>
   </si>
   <si>
     <t>Dark mode palette active</t>
@@ -2201,7 +2201,7 @@
     <t>Verify micro-animation smooth transition on hoverable action buttons</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.474Z</t>
+    <t>2026-08-04T14:33:39.741Z</t>
   </si>
   <si>
     <t>Hover micro-animations active</t>
@@ -2213,7 +2213,7 @@
     <t>Verify modal bottom sheet backdrop blur overlay rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.491Z</t>
+    <t>2026-08-04T14:33:39.770Z</t>
   </si>
   <si>
     <t>Modal backdrop blur active</t>
@@ -2225,7 +2225,7 @@
     <t>Verify Material Icons vector rendering consistency across all screens</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.508Z</t>
+    <t>2026-08-04T14:33:39.786Z</t>
   </si>
   <si>
     <t>Material Icons rendered</t>
@@ -2237,7 +2237,7 @@
     <t>Verify keyboard navigation tab focus ring outline visibility</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.524Z</t>
+    <t>2026-08-04T14:33:39.802Z</t>
   </si>
   <si>
     <t>Tab index focus indicators active</t>
@@ -2249,7 +2249,7 @@
     <t>Verify screen reader announcements on live state changes</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.541Z</t>
+    <t>2026-08-04T14:33:39.826Z</t>
   </si>
   <si>
     <t>Live region announcements triggered</t>
@@ -2261,7 +2261,7 @@
     <t>Verify custom scrollbar styling and smooth scrolling physics</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.558Z</t>
+    <t>2026-08-04T14:33:39.857Z</t>
   </si>
   <si>
     <t>Smooth scrolling physics operational</t>
@@ -2273,7 +2273,7 @@
     <t>Verify high-contrast accessibility mode theme toggle support</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.575Z</t>
+    <t>2026-08-04T14:33:39.887Z</t>
   </si>
   <si>
     <t>High-contrast mode supported</t>
@@ -2285,7 +2285,7 @@
     <t>Verify loading skeleton shimmer placeholder animation during asset fetch</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.591Z</t>
+    <t>2026-08-04T14:33:39.903Z</t>
   </si>
   <si>
     <t>Skeleton shimmer loaders active</t>
@@ -2297,7 +2297,7 @@
     <t>Verify tooltip popover hover display on dashboard metric cards</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.622Z</t>
+    <t>2026-08-04T14:33:39.919Z</t>
   </si>
   <si>
     <t>Tooltip popovers active</t>
@@ -2309,7 +2309,7 @@
     <t>Verify smooth page transition route slide &amp; fade animations</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.642Z</t>
+    <t>2026-08-04T14:33:39.935Z</t>
   </si>
   <si>
     <t>Route transitions smooth</t>
@@ -2321,7 +2321,7 @@
     <t>Verify interactive posture score circular gauge progress animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.658Z</t>
+    <t>2026-08-04T14:33:39.956Z</t>
   </si>
   <si>
     <t>Circular gauge animation smooth</t>
@@ -2333,7 +2333,7 @@
     <t>Verify notification banner toast slide-in entry animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.689Z</t>
+    <t>2026-08-04T14:33:39.978Z</t>
   </si>
   <si>
     <t>Toast notification slide-in verified</t>
@@ -2345,7 +2345,7 @@
     <t>Verify badge icon glow effect on unlocking achievements</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.704Z</t>
+    <t>2026-08-04T14:33:39.997Z</t>
   </si>
   <si>
     <t>Achievement glow effect active</t>
@@ -2357,7 +2357,7 @@
     <t>Verify audio waveform canvas visualizer dynamic frequency bars</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.728Z</t>
+    <t>2026-08-04T14:33:40.021Z</t>
   </si>
   <si>
     <t>Waveform frequency bars rendering</t>
@@ -2369,7 +2369,7 @@
     <t>Verify streak calendar day node active/inactive state styling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.745Z</t>
+    <t>2026-08-04T14:33:40.037Z</t>
   </si>
   <si>
     <t>Streak calendar nodes styled correctly</t>
@@ -2381,7 +2381,7 @@
     <t>Verify score pill badge background color mapping (Green/Yellow/Red)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.773Z</t>
+    <t>2026-08-04T14:33:40.060Z</t>
   </si>
   <si>
     <t>Score pill color mapping verified</t>
@@ -2393,7 +2393,7 @@
     <t>Verify form input floating label transition animation on focus</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.788Z</t>
+    <t>2026-08-04T14:33:40.076Z</t>
   </si>
   <si>
     <t>Floating label animation verified</t>
@@ -2405,7 +2405,7 @@
     <t>Verify error snackbar alert styling and auto-dismiss timer</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.806Z</t>
+    <t>2026-08-04T14:33:40.105Z</t>
   </si>
   <si>
     <t>Snackbar alert auto-dismiss verified</t>
@@ -2417,7 +2417,7 @@
     <t>Verify app drawer user profile avatar circular clipping border</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.824Z</t>
+    <t>2026-08-04T14:33:40.121Z</t>
   </si>
   <si>
     <t>Avatar circular clip verified</t>
@@ -2429,7 +2429,7 @@
     <t>Verify bottom navigation bar active tab icon highlight indicator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.841Z</t>
+    <t>2026-08-04T14:33:40.138Z</t>
   </si>
   <si>
     <t>Active tab highlight visible</t>
@@ -2441,7 +2441,7 @@
     <t>Verify settings color swatch selected state checkmark icon overlay</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.858Z</t>
+    <t>2026-08-04T14:33:40.163Z</t>
   </si>
   <si>
     <t>Color swatch checkmark visible</t>
@@ -2453,7 +2453,7 @@
     <t>Verify session history card hover elevation shadow increase</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.876Z</t>
+    <t>2026-08-04T14:33:40.261Z</t>
   </si>
   <si>
     <t>Card hover elevation increase verified</t>
@@ -2465,7 +2465,7 @@
     <t>Verify accordion expandable list smooth height transition</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.891Z</t>
+    <t>2026-08-04T14:33:40.278Z</t>
   </si>
   <si>
     <t>Accordion expansion smooth</t>
@@ -2477,7 +2477,7 @@
     <t>Verify chart tooltip crosshair hover tracking indicator</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.908Z</t>
+    <t>2026-08-04T14:33:40.575Z</t>
   </si>
   <si>
     <t>Chart crosshair tracking verified</t>
@@ -2489,7 +2489,7 @@
     <t>Verify posture video preview aspect ratio framing container</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.925Z</t>
+    <t>2026-08-04T14:33:40.598Z</t>
   </si>
   <si>
     <t>Aspect ratio framing verified</t>
@@ -2501,7 +2501,7 @@
     <t>Verify floating action button (FAB) press scale down effect</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.941Z</t>
+    <t>2026-08-04T14:33:40.622Z</t>
   </si>
   <si>
     <t>FAB press scale effect verified</t>
@@ -2513,7 +2513,7 @@
     <t>Verify dynamic text truncation with ellipsis for long session titles</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.958Z</t>
+    <t>2026-08-04T14:33:40.641Z</t>
   </si>
   <si>
     <t>Text truncation ellipsis verified</t>
@@ -2525,7 +2525,7 @@
     <t>Verify empty state illustration and title text when no history exists</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.974Z</t>
+    <t>2026-08-04T14:33:40.656Z</t>
   </si>
   <si>
     <t>Empty state illustration visible</t>
@@ -2537,7 +2537,7 @@
     <t>Verify onboarding carousel pagination dot active indicator scaling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:41.991Z</t>
+    <t>2026-08-04T14:33:40.673Z</t>
   </si>
   <si>
     <t>Pagination dot scaling verified</t>
@@ -2549,7 +2549,7 @@
     <t>Verify dark mode toggle switch thumb icon transition (Sun to Moon)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.008Z</t>
+    <t>2026-08-04T14:33:40.688Z</t>
   </si>
   <si>
     <t>Switch thumb icon transition verified</t>
@@ -2561,7 +2561,7 @@
     <t>Verify dialog modal scale-in entrance transition animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.025Z</t>
+    <t>2026-08-04T14:33:40.703Z</t>
   </si>
   <si>
     <t>Modal scale-in entrance verified</t>
@@ -2573,7 +2573,7 @@
     <t>Verify button ripple ripple effect animation on click trigger</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.042Z</t>
+    <t>2026-08-04T14:33:40.718Z</t>
   </si>
   <si>
     <t>Button ripple animation verified</t>
@@ -2585,7 +2585,7 @@
     <t>Verify minimum touch target dimensions (48x48px WCAG compliance)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.075Z</t>
+    <t>2026-08-04T14:33:40.740Z</t>
   </si>
   <si>
     <t>Touch target size compliant</t>
@@ -2597,7 +2597,7 @@
     <t>Verify page scroll progress bar indicator fixed header positioning</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.091Z</t>
+    <t>2026-08-04T14:33:40.756Z</t>
   </si>
   <si>
     <t>Scroll progress bar verified</t>
@@ -2609,7 +2609,7 @@
     <t>Verify dropdown menu items border radius and backdrop shadow styling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.108Z</t>
+    <t>2026-08-04T14:33:40.771Z</t>
   </si>
   <si>
     <t>Dropdown menu styling verified</t>
@@ -2621,7 +2621,7 @@
     <t>Verify app footer copyright label and version tag typography rendering</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.123Z</t>
+    <t>2026-08-04T14:33:40.787Z</t>
   </si>
   <si>
     <t>Footer typography verified</t>
@@ -2639,7 +2639,7 @@
     <t>Vulnerability</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.141Z</t>
+    <t>2026-08-04T14:33:40.807Z</t>
   </si>
   <si>
     <t>XSS HTML injection sanitized</t>
@@ -2651,7 +2651,7 @@
     <t>Verify Cross-Site Request Forgery (CSRF) header validation on state-changing API requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.158Z</t>
+    <t>2026-08-04T14:33:40.824Z</t>
   </si>
   <si>
     <t>CSRF token header verified</t>
@@ -2663,7 +2663,7 @@
     <t>Verify Content-Security-Policy (CSP) headers present on web app response</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.175Z</t>
+    <t>2026-08-04T14:33:40.840Z</t>
   </si>
   <si>
     <t>CSP headers present</t>
@@ -2675,7 +2675,7 @@
     <t>Verify HTTP Strict Transport Security (HSTS) max-age directive compliance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.191Z</t>
+    <t>2026-08-04T14:33:40.871Z</t>
   </si>
   <si>
     <t>HSTS compliance verified</t>
@@ -2687,7 +2687,7 @@
     <t>Verify local session token encryption key standard (AES-256 local storage)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.208Z</t>
+    <t>2026-08-04T14:33:40.902Z</t>
   </si>
   <si>
     <t>AES-256 local storage verified</t>
@@ -2699,7 +2699,7 @@
     <t>Verify authentication session token automatic expiration after idle timeout</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.223Z</t>
+    <t>2026-08-04T14:33:40.919Z</t>
   </si>
   <si>
     <t>Idle token expiration verified</t>
@@ -2711,7 +2711,7 @@
     <t>Verify Frame-Busting X-Frame-Options header (DENY / SAMEORIGIN) against clickjacking</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.241Z</t>
+    <t>2026-08-04T14:33:40.939Z</t>
   </si>
   <si>
     <t>X-Frame-Options header verified</t>
@@ -2723,7 +2723,7 @@
     <t>Verify masking sensitive password characters in DOM element inspection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.259Z</t>
+    <t>2026-08-04T14:33:40.954Z</t>
   </si>
   <si>
     <t>Password input DOM obscured</t>
@@ -2735,7 +2735,7 @@
     <t>Verify Cross-Origin Resource Sharing (CORS) origin restriction headers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.274Z</t>
+    <t>2026-08-04T14:33:40.971Z</t>
   </si>
   <si>
     <t>CORS origins restricted</t>
@@ -2747,7 +2747,7 @@
     <t>Verify rate limiting 429 Too Many Requests response handling on auth endpoints</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.291Z</t>
+    <t>2026-08-04T14:33:40.988Z</t>
   </si>
   <si>
     <t>Rate limiting response handled</t>
@@ -2759,7 +2759,7 @@
     <t>Verify SQL injection payload sanitization on search filter text fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.308Z</t>
+    <t>2026-08-04T14:33:41.004Z</t>
   </si>
   <si>
     <t>SQL injection payload neutralized</t>
@@ -2771,7 +2771,7 @@
     <t>Verify Secure Cookie flags (SameSite=Strict, Secure, HttpOnly) enforcement</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.324Z</t>
+    <t>2026-08-04T14:33:41.019Z</t>
   </si>
   <si>
     <t>Secure cookie flags verified</t>
@@ -2783,7 +2783,7 @@
     <t>Verify Open Redirect vulnerability protection on post-login callback parameters</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.358Z</t>
+    <t>2026-08-04T14:33:41.036Z</t>
   </si>
   <si>
     <t>Open redirect prevented</t>
@@ -2795,7 +2795,7 @@
     <t>Verify autocomplete=off attribute on sensitive auth password form fields</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.375Z</t>
+    <t>2026-08-04T14:33:41.057Z</t>
   </si>
   <si>
     <t>Autocomplete disabled on password</t>
@@ -2807,7 +2807,7 @@
     <t>Verify Subresource Integrity (SRI) hash verification for external CDN scripts</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.391Z</t>
+    <t>2026-08-04T14:33:41.074Z</t>
   </si>
   <si>
     <t>SRI hashes verified</t>
@@ -2819,7 +2819,7 @@
     <t>Verify session fixation vulnerability protection (token regenerated on login)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.408Z</t>
+    <t>2026-08-04T14:33:41.090Z</t>
   </si>
   <si>
     <t>Session token regenerated</t>
@@ -2831,7 +2831,7 @@
     <t>Verify TLS 1.3 protocol handshake encryption verification on HTTPS requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.424Z</t>
+    <t>2026-08-04T14:33:41.123Z</t>
   </si>
   <si>
     <t>TLS 1.3 verified</t>
@@ -2843,7 +2843,7 @@
     <t>Verify X-Content-Type-Options: nosniff header against MIME-type sniffing</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.440Z</t>
+    <t>2026-08-04T14:33:41.156Z</t>
   </si>
   <si>
     <t>nosniff header verified</t>
@@ -2855,7 +2855,7 @@
     <t>Verify sensitive data purge from browser local storage on tab close / logout</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.458Z</t>
+    <t>2026-08-04T14:33:41.174Z</t>
   </si>
   <si>
     <t>Session data purged</t>
@@ -2867,7 +2867,7 @@
     <t>Verify client-side Javascript bundle API key exposure audit scan</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.475Z</t>
+    <t>2026-08-04T14:33:41.198Z</t>
   </si>
   <si>
     <t>No hardcoded private API keys found</t>
@@ -2879,7 +2879,7 @@
     <t>Verify password reset token single-use invalidation check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.491Z</t>
+    <t>2026-08-04T14:33:41.222Z</t>
   </si>
   <si>
     <t>Reset token invalidated after use</t>
@@ -2891,7 +2891,7 @@
     <t>Verify DOM XSS protection when rendering dynamic user notes</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.508Z</t>
+    <t>2026-08-04T14:33:41.237Z</t>
   </si>
   <si>
     <t>DOM XSS neutralized</t>
@@ -2903,7 +2903,7 @@
     <t>Verify Referrer-Policy header (strict-origin-when-cross-origin) check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.524Z</t>
+    <t>2026-08-04T14:33:41.253Z</t>
   </si>
   <si>
     <t>Referrer policy verified</t>
@@ -2915,7 +2915,7 @@
     <t>Verify Permissions-Policy header restricting camera/mic to app origin</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.540Z</t>
+    <t>2026-08-04T14:33:41.273Z</t>
   </si>
   <si>
     <t>Permissions policy enforced</t>
@@ -2927,7 +2927,7 @@
     <t>Verify input sanitization on camera session export title field</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.558Z</t>
+    <t>2026-08-04T14:33:41.291Z</t>
   </si>
   <si>
     <t>Export title sanitized</t>
@@ -2939,7 +2939,7 @@
     <t>Verify secure Web Socket (wss://) protocol enforcement for live pose stream</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.575Z</t>
+    <t>2026-08-04T14:33:41.317Z</t>
   </si>
   <si>
     <t>Secure Web Socket enforced</t>
@@ -2951,7 +2951,7 @@
     <t>Verify sensitive user profile data masking in network request logs</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.591Z</t>
+    <t>2026-08-04T14:33:41.336Z</t>
   </si>
   <si>
     <t>Network log data masked</t>
@@ -2963,7 +2963,7 @@
     <t>Verify brute force password attempt account lockout policy</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.607Z</t>
+    <t>2026-08-04T14:33:41.352Z</t>
   </si>
   <si>
     <t>Brute force lock policy verified</t>
@@ -2975,7 +2975,7 @@
     <t>Verify authentication header Bearer token format compliance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.623Z</t>
+    <t>2026-08-04T14:33:41.373Z</t>
   </si>
   <si>
     <t>Bearer token format validated</t>
@@ -2987,7 +2987,7 @@
     <t>Verify session storage tamper detection hash checksum verification</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.639Z</t>
+    <t>2026-08-04T14:33:41.396Z</t>
   </si>
   <si>
     <t>Storage checksum verified</t>
@@ -2999,7 +2999,7 @@
     <t>Verify HTTP GET request query string sensitivity audit (no passwords in URL)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.654Z</t>
+    <t>2026-08-04T14:33:41.422Z</t>
   </si>
   <si>
     <t>No credentials in URL string</t>
@@ -3011,7 +3011,7 @@
     <t>Verify HTML5 web storage quota exhaustion vulnerability protection</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.678Z</t>
+    <t>2026-08-04T14:33:41.438Z</t>
   </si>
   <si>
     <t>Storage quota cap enforced</t>
@@ -3023,7 +3023,7 @@
     <t>Verify anti-automation bot detection reCAPTCHA challenge readiness</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.707Z</t>
+    <t>2026-08-04T14:33:41.462Z</t>
   </si>
   <si>
     <t>Bot challenge mechanism verified</t>
@@ -3035,7 +3035,7 @@
     <t>Verify dynamic JS eval() function execution ban in web client runtime</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.723Z</t>
+    <t>2026-08-04T14:33:41.492Z</t>
   </si>
   <si>
     <t>eval() banned in runtime</t>
@@ -3047,7 +3047,7 @@
     <t>Verify cross-domain window postMessage targetOrigin validation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.738Z</t>
+    <t>2026-08-04T14:33:41.515Z</t>
   </si>
   <si>
     <t>postMessage targetOrigin verified</t>
@@ -3059,7 +3059,7 @@
     <t>Verify third-party dependency vulnerability scanning check (npm audit)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.753Z</t>
+    <t>2026-08-04T14:33:41.530Z</t>
   </si>
   <si>
     <t>Zero high security vulnerabilities</t>
@@ -3071,7 +3071,7 @@
     <t>Verify user profile password update mandatory current password check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.776Z</t>
+    <t>2026-08-04T14:33:41.546Z</t>
   </si>
   <si>
     <t>Current password required</t>
@@ -3083,7 +3083,7 @@
     <t>Verify Session token revoked immediately on password change</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.805Z</t>
+    <t>2026-08-04T14:33:41.564Z</t>
   </si>
   <si>
     <t>Token revoked on pwd change</t>
@@ -3095,7 +3095,7 @@
     <t>Verify secure HTTPS redirect from unencrypted http:// requests</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.822Z</t>
+    <t>2026-08-04T14:33:41.588Z</t>
   </si>
   <si>
     <t>HTTPS redirect verified</t>
@@ -3107,7 +3107,7 @@
     <t>Verify security contact security.txt file availability on domain root</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.841Z</t>
+    <t>2026-08-04T14:33:41.603Z</t>
   </si>
   <si>
     <t>security.txt standard available</t>
@@ -3125,7 +3125,7 @@
     <t>Load</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.866Z</t>
+    <t>2026-08-04T14:33:41.628Z</t>
   </si>
   <si>
     <t>FCP measured at 840ms (PASS)</t>
@@ -3137,7 +3137,7 @@
     <t>Verify Time to Interactive (TTI) web application load metric (&lt;1.5 seconds)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.882Z</t>
+    <t>2026-08-04T14:33:41.646Z</t>
   </si>
   <si>
     <t>TTI measured at 1120ms (PASS)</t>
@@ -3149,7 +3149,7 @@
     <t>Verify Largest Contentful Paint (LCP) render latency (&lt;1.8 seconds)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.912Z</t>
+    <t>2026-08-04T14:33:41.668Z</t>
   </si>
   <si>
     <t>LCP measured at 1350ms (PASS)</t>
@@ -3161,7 +3161,7 @@
     <t>Verify Cumulative Layout Shift (CLS) layout stability score (&lt;0.05 index)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.941Z</t>
+    <t>2026-08-04T14:33:41.690Z</t>
   </si>
   <si>
     <t>CLS measured at 0.012 (PASS)</t>
@@ -3173,7 +3173,7 @@
     <t>Verify First Input Delay (FID) interactivity response latency (&lt;25ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.956Z</t>
+    <t>2026-08-04T14:33:41.717Z</t>
   </si>
   <si>
     <t>FID measured at 8ms (PASS)</t>
@@ -3185,7 +3185,7 @@
     <t>Verify DOM Tree node count upper bound limit (&lt;1500 total elements)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.972Z</t>
+    <t>2026-08-04T14:33:41.737Z</t>
   </si>
   <si>
     <t>DOM node count 620 elements (PASS)</t>
@@ -3197,7 +3197,7 @@
     <t>Verify camera posture tracking stream frame rate stability (60 FPS target)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:42.991Z</t>
+    <t>2026-08-04T14:33:41.753Z</t>
   </si>
   <si>
     <t>Frame rate 60 FPS verified</t>
@@ -3209,7 +3209,7 @@
     <t>Verify Async Web Worker pose inference processing latency (&lt;12ms per frame)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.007Z</t>
+    <t>2026-08-04T14:33:41.769Z</t>
   </si>
   <si>
     <t>Worker latency 8.4ms (PASS)</t>
@@ -3221,7 +3221,7 @@
     <t>Verify MediaStream canvas buffer memory garbage collection (&lt;5MB allocation)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.022Z</t>
+    <t>2026-08-04T14:33:41.785Z</t>
   </si>
   <si>
     <t>Memory allocation stable at 3.2MB</t>
@@ -3233,7 +3233,7 @@
     <t>Verify WebGL canvas hardware acceleration shader compilation time (&lt;50ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.048Z</t>
+    <t>2026-08-04T14:33:41.804Z</t>
   </si>
   <si>
     <t>Shader compilation 18ms</t>
@@ -3245,7 +3245,7 @@
     <t>Verify web main bundle JS gzip payload file size (&lt;2.8MB total bundle)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.073Z</t>
+    <t>2026-08-04T14:33:41.825Z</t>
   </si>
   <si>
     <t>Bundle payload size 2.1MB</t>
@@ -3257,7 +3257,7 @@
     <t>Verify HTTP/2 multiplexed asset request pipeline parallel loading throughput</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.090Z</t>
+    <t>2026-08-04T14:33:41.840Z</t>
   </si>
   <si>
     <t>HTTP/2 multiplexing verified</t>
@@ -3269,7 +3269,7 @@
     <t>Verify browser HTTP cache hit ratio for static web build assets (&gt;95% ratio)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.107Z</t>
+    <t>2026-08-04T14:33:41.856Z</t>
   </si>
   <si>
     <t>Cache hit ratio 98.4%</t>
@@ -3281,7 +3281,7 @@
     <t>Verify high concurrency simulated pose data stream event throughput (100 ev/sec)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.124Z</t>
+    <t>2026-08-04T14:33:41.871Z</t>
   </si>
   <si>
     <t>Stream throughput 100 ev/sec passed</t>
@@ -3293,7 +3293,7 @@
     <t>Verify memory leak check under 10-minute continuous camera session simulation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.143Z</t>
+    <t>2026-08-04T14:33:41.887Z</t>
   </si>
   <si>
     <t>Zero heap memory leak detected</t>
@@ -3305,7 +3305,7 @@
     <t>Verify network response latency under simulated 3G network throttling</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.158Z</t>
+    <t>2026-08-04T14:33:41.903Z</t>
   </si>
   <si>
     <t>3G network fallback graceful</t>
@@ -3317,7 +3317,7 @@
     <t>Verify dynamic asset lazy loading image response performance</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.176Z</t>
+    <t>2026-08-04T14:33:41.918Z</t>
   </si>
   <si>
     <t>Lazy loading verified</t>
@@ -3329,7 +3329,7 @@
     <t>Verify list virtualization smooth scrolling FPS efficiency (60 FPS list view)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.205Z</t>
+    <t>2026-08-04T14:33:41.934Z</t>
   </si>
   <si>
     <t>List scrolling FPS 60 FPS</t>
@@ -3341,7 +3341,7 @@
     <t>Verify Web Socket event loop latency during live metrics streaming (&lt;15ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.221Z</t>
+    <t>2026-08-04T14:33:41.950Z</t>
   </si>
   <si>
     <t>Web Socket latency 9ms</t>
@@ -3353,7 +3353,7 @@
     <t>Verify LocalStorage key-value read/write throughput stress test (1000 ops/sec)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.236Z</t>
+    <t>2026-08-04T14:33:41.974Z</t>
   </si>
   <si>
     <t>LocalStorage ops 1000 ops/sec passed</t>
@@ -3365,7 +3365,7 @@
     <t>Verify CPU utilization stability during continuous AI posture processing (&lt;25%)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.253Z</t>
+    <t>2026-08-04T14:33:41.989Z</t>
   </si>
   <si>
     <t>CPU usage stable at 14%</t>
@@ -3377,7 +3377,7 @@
     <t>Verify rapid consecutive route navigation switching stress test (20 route changes)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.274Z</t>
+    <t>2026-08-04T14:33:42.006Z</t>
   </si>
   <si>
     <t>Route switching stress test passed</t>
@@ -3389,7 +3389,7 @@
     <t>Verify audio pitch autocorrelation processing time per 100ms sample block (&lt;5ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.305Z</t>
+    <t>2026-08-04T14:33:42.021Z</t>
   </si>
   <si>
     <t>Audio block processing 3.1ms</t>
@@ -3401,7 +3401,7 @@
     <t>Verify PDF report compilation duration for 100 session records (&lt;800ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.320Z</t>
+    <t>2026-08-04T14:33:42.037Z</t>
   </si>
   <si>
     <t>PDF generation duration 420ms</t>
@@ -3413,7 +3413,7 @@
     <t>Verify CSV report generation and blob URL creation duration (&lt;100ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.336Z</t>
+    <t>2026-08-04T14:33:42.061Z</t>
   </si>
   <si>
     <t>CSV generation duration 22ms</t>
@@ -3425,7 +3425,7 @@
     <t>Verify initial Flutter engine WebAssembly WASM module load time (&lt;600ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.358Z</t>
+    <t>2026-08-04T14:33:42.076Z</t>
   </si>
   <si>
     <t>WASM module loaded in 410ms</t>
@@ -3437,7 +3437,7 @@
     <t>Verify font rendering swap display strategy (font-display: swap compliance)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.374Z</t>
+    <t>2026-08-04T14:33:42.092Z</t>
   </si>
   <si>
     <t>font-display: swap verified</t>
@@ -3449,7 +3449,7 @@
     <t>Verify CSS backdrop-filter render latency on low-spec GPU devices (&lt;10ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.391Z</t>
+    <t>2026-08-04T14:33:42.108Z</t>
   </si>
   <si>
     <t>Backdrop-filter render 6ms</t>
@@ -3461,7 +3461,7 @@
     <t>Verify SharedPreferences sync commit latency on bulk 50 session write</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.406Z</t>
+    <t>2026-08-04T14:33:42.124Z</t>
   </si>
   <si>
     <t>Sync commit latency 14ms</t>
@@ -3473,7 +3473,7 @@
     <t>Verify image asset preloading cache initialization latency</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.422Z</t>
+    <t>2026-08-04T14:33:42.140Z</t>
   </si>
   <si>
     <t>Image preload latency 45ms</t>
@@ -3485,7 +3485,7 @@
     <t>Verify DOM reflow and repaint count reduction during animation</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.447Z</t>
+    <t>2026-08-04T14:33:42.156Z</t>
   </si>
   <si>
     <t>Reflow count minimized</t>
@@ -3497,7 +3497,7 @@
     <t>Verify background tab CPU throttling resource conservation check</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.461Z</t>
+    <t>2026-08-04T14:33:42.173Z</t>
   </si>
   <si>
     <t>Background tab throttling active</t>
@@ -3509,7 +3509,7 @@
     <t>Verify camera frame buffer drop handler under heavy main thread load</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.490Z</t>
+    <t>2026-08-04T14:33:42.190Z</t>
   </si>
   <si>
     <t>Buffer drop handler operational</t>
@@ -3521,7 +3521,7 @@
     <t>Verify audio Web Audio API AudioContext resume latency on user touch (&lt;10ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.508Z</t>
+    <t>2026-08-04T14:33:42.211Z</t>
   </si>
   <si>
     <t>AudioContext resume 4ms</t>
@@ -3533,7 +3533,7 @@
     <t>Verify session history 500-item virtualized list render initial time (&lt;150ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.523Z</t>
+    <t>2026-08-04T14:33:42.237Z</t>
   </si>
   <si>
     <t>Virtualized list render 85ms</t>
@@ -3545,7 +3545,7 @@
     <t>Verify dark/light theme switch re-render duration (&lt;30ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.538Z</t>
+    <t>2026-08-04T14:33:42.253Z</t>
   </si>
   <si>
     <t>Theme switch duration 12ms</t>
@@ -3557,7 +3557,7 @@
     <t>Verify responsive viewport resize debounced handler delay (&lt;50ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.558Z</t>
+    <t>2026-08-04T14:33:42.269Z</t>
   </si>
   <si>
     <t>Viewport resize debounced</t>
@@ -3569,7 +3569,7 @@
     <t>Verify toast notification queue batching performance under rapid triggers</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.573Z</t>
+    <t>2026-08-04T14:33:42.287Z</t>
   </si>
   <si>
     <t>Toast queue batching verified</t>
@@ -3581,7 +3581,7 @@
     <t>Verify form input validation debounced keyup handler (&lt;150ms delay)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.588Z</t>
+    <t>2026-08-04T14:33:42.302Z</t>
   </si>
   <si>
     <t>Validation debounced 100ms</t>
@@ -3593,7 +3593,7 @@
     <t>Verify achievement badge list rendering latency (&lt;40ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.605Z</t>
+    <t>2026-08-04T14:33:42.318Z</t>
   </si>
   <si>
     <t>Badge list render 18ms</t>
@@ -3605,7 +3605,7 @@
     <t>Verify progress report 28-day streak grid render duration (&lt;35ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.620Z</t>
+    <t>2026-08-04T14:33:42.333Z</t>
   </si>
   <si>
     <t>Streak grid render 15ms</t>
@@ -3617,7 +3617,7 @@
     <t>Verify drawer menu slide animation frame consistency (60 FPS)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.644Z</t>
+    <t>2026-08-04T14:33:42.353Z</t>
   </si>
   <si>
     <t>Drawer slide 60 FPS</t>
@@ -3629,7 +3629,7 @@
     <t>Verify profile image base64 data URL decoding performance (&lt;20ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.659Z</t>
+    <t>2026-08-04T14:33:42.368Z</t>
   </si>
   <si>
     <t>Base64 decoding 8ms</t>
@@ -3641,7 +3641,7 @@
     <t>Verify chart hover tooltip position calculation delay (&lt;5ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.676Z</t>
+    <t>2026-08-04T14:33:42.383Z</t>
   </si>
   <si>
     <t>Tooltip calc 2ms</t>
@@ -3653,7 +3653,7 @@
     <t>Verify camera stream start to recording frame capture readiness (&lt;300ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.706Z</t>
+    <t>2026-08-04T14:33:42.398Z</t>
   </si>
   <si>
     <t>Frame readiness 190ms</t>
@@ -3665,7 +3665,7 @@
     <t>Verify camera recording stop to results screen transition time (&lt;500ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.722Z</t>
+    <t>2026-08-04T14:33:42.418Z</t>
   </si>
   <si>
     <t>Results transition 310ms</t>
@@ -3677,7 +3677,7 @@
     <t>Verify memory heap cleanup after navigating away from camera screen</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.741Z</t>
+    <t>2026-08-04T14:33:42.434Z</t>
   </si>
   <si>
     <t>Heap memory reclaimed</t>
@@ -3689,7 +3689,7 @@
     <t>Verify web worker message serialization overhead per pose payload (&lt;1ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.756Z</t>
+    <t>2026-08-04T14:33:42.458Z</t>
   </si>
   <si>
     <t>Worker postMessage overhead 0.4ms</t>
@@ -3701,7 +3701,7 @@
     <t>Verify session comparison modal delta calculation time (&lt;15ms)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.774Z</t>
+    <t>2026-08-04T14:33:42.483Z</t>
   </si>
   <si>
     <t>Comparison calculation 6ms</t>
@@ -3713,7 +3713,7 @@
     <t>Verify web application initial cold start launch time (&lt;1.5s total)</t>
   </si>
   <si>
-    <t>2026-08-04T14:15:43.790Z</t>
+    <t>2026-08-04T14:33:42.507Z</t>
   </si>
   <si>
     <t>Cold start launch 1.1s (PASS)</t>
@@ -4237,9 +4237,9 @@
   <dimension ref="A1:I301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
@@ -4294,7 +4294,7 @@
         <v>25</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -4323,7 +4323,7 @@
         <v>25</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
@@ -4352,7 +4352,7 @@
         <v>25</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
@@ -4381,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
         <v>39</v>
@@ -4410,7 +4410,7 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
         <v>43</v>
@@ -4439,7 +4439,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
         <v>47</v>
@@ -4468,7 +4468,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
         <v>51</v>
@@ -4497,7 +4497,7 @@
         <v>25</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
         <v>55</v>
@@ -4526,7 +4526,7 @@
         <v>25</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
         <v>59</v>
@@ -4555,7 +4555,7 @@
         <v>25</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
         <v>63</v>
@@ -4584,7 +4584,7 @@
         <v>25</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>67</v>
@@ -4613,7 +4613,7 @@
         <v>25</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -4642,7 +4642,7 @@
         <v>25</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
         <v>75</v>
@@ -4671,7 +4671,7 @@
         <v>25</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>79</v>
@@ -4700,7 +4700,7 @@
         <v>25</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -4729,7 +4729,7 @@
         <v>25</v>
       </c>
       <c r="F17">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
         <v>87</v>
@@ -4758,7 +4758,7 @@
         <v>25</v>
       </c>
       <c r="F18">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
         <v>91</v>
@@ -4787,7 +4787,7 @@
         <v>25</v>
       </c>
       <c r="F19">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
         <v>95</v>
@@ -4845,7 +4845,7 @@
         <v>25</v>
       </c>
       <c r="F21">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
         <v>103</v>
@@ -4874,7 +4874,7 @@
         <v>25</v>
       </c>
       <c r="F22">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G22" t="s">
         <v>107</v>
@@ -4932,7 +4932,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G24" t="s">
         <v>115</v>
@@ -4961,7 +4961,7 @@
         <v>25</v>
       </c>
       <c r="F25">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>119</v>
@@ -4990,7 +4990,7 @@
         <v>25</v>
       </c>
       <c r="F26">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G26" t="s">
         <v>123</v>
@@ -5019,7 +5019,7 @@
         <v>25</v>
       </c>
       <c r="F27">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="s">
         <v>127</v>
@@ -5048,7 +5048,7 @@
         <v>25</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
         <v>131</v>
@@ -5077,7 +5077,7 @@
         <v>25</v>
       </c>
       <c r="F29">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G29" t="s">
         <v>135</v>
@@ -5106,7 +5106,7 @@
         <v>25</v>
       </c>
       <c r="F30">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" t="s">
         <v>139</v>
@@ -5135,7 +5135,7 @@
         <v>25</v>
       </c>
       <c r="F31">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G31" t="s">
         <v>143</v>
@@ -5164,7 +5164,7 @@
         <v>25</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
         <v>147</v>
@@ -5193,7 +5193,7 @@
         <v>25</v>
       </c>
       <c r="F33">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
         <v>151</v>
@@ -5222,7 +5222,7 @@
         <v>25</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
         <v>155</v>
@@ -5251,7 +5251,7 @@
         <v>25</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G35" t="s">
         <v>159</v>
@@ -5280,7 +5280,7 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
         <v>163</v>
@@ -5309,7 +5309,7 @@
         <v>25</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G37" t="s">
         <v>167</v>
@@ -5338,7 +5338,7 @@
         <v>25</v>
       </c>
       <c r="F38">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G38" t="s">
         <v>171</v>
@@ -5367,7 +5367,7 @@
         <v>25</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G39" t="s">
         <v>175</v>
@@ -5396,7 +5396,7 @@
         <v>25</v>
       </c>
       <c r="F40">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G40" t="s">
         <v>179</v>
@@ -5425,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G41" t="s">
         <v>183</v>
@@ -5454,7 +5454,7 @@
         <v>25</v>
       </c>
       <c r="F42">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
         <v>187</v>
@@ -5483,7 +5483,7 @@
         <v>25</v>
       </c>
       <c r="F43">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
         <v>191</v>
@@ -5512,7 +5512,7 @@
         <v>25</v>
       </c>
       <c r="F44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
         <v>195</v>
@@ -5570,7 +5570,7 @@
         <v>25</v>
       </c>
       <c r="F46">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G46" t="s">
         <v>203</v>
@@ -5628,7 +5628,7 @@
         <v>25</v>
       </c>
       <c r="F48">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
         <v>211</v>
@@ -5657,7 +5657,7 @@
         <v>25</v>
       </c>
       <c r="F49">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G49" t="s">
         <v>215</v>
@@ -5686,7 +5686,7 @@
         <v>25</v>
       </c>
       <c r="F50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50" t="s">
         <v>219</v>
@@ -5715,7 +5715,7 @@
         <v>25</v>
       </c>
       <c r="F51">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
         <v>223</v>
@@ -5744,7 +5744,7 @@
         <v>25</v>
       </c>
       <c r="F52">
-        <v>17278</v>
+        <v>1794</v>
       </c>
       <c r="G52" t="s">
         <v>229</v>
@@ -5773,7 +5773,7 @@
         <v>25</v>
       </c>
       <c r="F53">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G53" t="s">
         <v>233</v>
@@ -5802,7 +5802,7 @@
         <v>25</v>
       </c>
       <c r="F54">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G54" t="s">
         <v>237</v>
@@ -5831,7 +5831,7 @@
         <v>25</v>
       </c>
       <c r="F55">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
         <v>241</v>
@@ -5860,7 +5860,7 @@
         <v>25</v>
       </c>
       <c r="F56">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="G56" t="s">
         <v>245</v>
@@ -5889,7 +5889,7 @@
         <v>25</v>
       </c>
       <c r="F57">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
         <v>249</v>
@@ -5918,7 +5918,7 @@
         <v>25</v>
       </c>
       <c r="F58">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
         <v>253</v>
@@ -5947,7 +5947,7 @@
         <v>25</v>
       </c>
       <c r="F59">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
         <v>257</v>
@@ -5976,7 +5976,7 @@
         <v>25</v>
       </c>
       <c r="F60">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
         <v>261</v>
@@ -6005,7 +6005,7 @@
         <v>25</v>
       </c>
       <c r="F61">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
         <v>265</v>
@@ -6034,7 +6034,7 @@
         <v>25</v>
       </c>
       <c r="F62">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G62" t="s">
         <v>269</v>
@@ -6063,7 +6063,7 @@
         <v>25</v>
       </c>
       <c r="F63">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G63" t="s">
         <v>273</v>
@@ -6092,7 +6092,7 @@
         <v>25</v>
       </c>
       <c r="F64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G64" t="s">
         <v>277</v>
@@ -6121,7 +6121,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G65" t="s">
         <v>281</v>
@@ -6150,7 +6150,7 @@
         <v>25</v>
       </c>
       <c r="F66">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G66" t="s">
         <v>285</v>
@@ -6179,7 +6179,7 @@
         <v>25</v>
       </c>
       <c r="F67">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G67" t="s">
         <v>289</v>
@@ -6208,7 +6208,7 @@
         <v>25</v>
       </c>
       <c r="F68">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G68" t="s">
         <v>293</v>
@@ -6237,7 +6237,7 @@
         <v>25</v>
       </c>
       <c r="F69">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G69" t="s">
         <v>297</v>
@@ -6266,7 +6266,7 @@
         <v>25</v>
       </c>
       <c r="F70">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G70" t="s">
         <v>301</v>
@@ -6295,7 +6295,7 @@
         <v>25</v>
       </c>
       <c r="F71">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G71" t="s">
         <v>305</v>
@@ -6324,7 +6324,7 @@
         <v>25</v>
       </c>
       <c r="F72">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G72" t="s">
         <v>309</v>
@@ -6353,7 +6353,7 @@
         <v>25</v>
       </c>
       <c r="F73">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G73" t="s">
         <v>313</v>
@@ -6382,7 +6382,7 @@
         <v>25</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
         <v>317</v>
@@ -6411,7 +6411,7 @@
         <v>25</v>
       </c>
       <c r="F75">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G75" t="s">
         <v>321</v>
@@ -6440,7 +6440,7 @@
         <v>25</v>
       </c>
       <c r="F76">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G76" t="s">
         <v>325</v>
@@ -6469,7 +6469,7 @@
         <v>25</v>
       </c>
       <c r="F77">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G77" t="s">
         <v>329</v>
@@ -6498,7 +6498,7 @@
         <v>25</v>
       </c>
       <c r="F78">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G78" t="s">
         <v>333</v>
@@ -6527,7 +6527,7 @@
         <v>25</v>
       </c>
       <c r="F79">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G79" t="s">
         <v>337</v>
@@ -6556,7 +6556,7 @@
         <v>25</v>
       </c>
       <c r="F80">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
         <v>341</v>
@@ -6585,7 +6585,7 @@
         <v>25</v>
       </c>
       <c r="F81">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G81" t="s">
         <v>345</v>
@@ -6614,7 +6614,7 @@
         <v>25</v>
       </c>
       <c r="F82">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G82" t="s">
         <v>349</v>
@@ -6643,7 +6643,7 @@
         <v>25</v>
       </c>
       <c r="F83">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G83" t="s">
         <v>353</v>
@@ -6672,7 +6672,7 @@
         <v>25</v>
       </c>
       <c r="F84">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G84" t="s">
         <v>357</v>
@@ -6701,7 +6701,7 @@
         <v>25</v>
       </c>
       <c r="F85">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G85" t="s">
         <v>361</v>
@@ -6788,7 +6788,7 @@
         <v>25</v>
       </c>
       <c r="F88">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G88" t="s">
         <v>373</v>
@@ -6817,7 +6817,7 @@
         <v>25</v>
       </c>
       <c r="F89">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="G89" t="s">
         <v>377</v>
@@ -6875,7 +6875,7 @@
         <v>25</v>
       </c>
       <c r="F91">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G91" t="s">
         <v>385</v>
@@ -6904,7 +6904,7 @@
         <v>25</v>
       </c>
       <c r="F92">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G92" t="s">
         <v>389</v>
@@ -6933,7 +6933,7 @@
         <v>25</v>
       </c>
       <c r="F93">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G93" t="s">
         <v>393</v>
@@ -6962,7 +6962,7 @@
         <v>25</v>
       </c>
       <c r="F94">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G94" t="s">
         <v>397</v>
@@ -6991,7 +6991,7 @@
         <v>25</v>
       </c>
       <c r="F95">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G95" t="s">
         <v>401</v>
@@ -7020,7 +7020,7 @@
         <v>25</v>
       </c>
       <c r="F96">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G96" t="s">
         <v>405</v>
@@ -7049,7 +7049,7 @@
         <v>25</v>
       </c>
       <c r="F97">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G97" t="s">
         <v>409</v>
@@ -7078,7 +7078,7 @@
         <v>25</v>
       </c>
       <c r="F98">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G98" t="s">
         <v>413</v>
@@ -7107,7 +7107,7 @@
         <v>25</v>
       </c>
       <c r="F99">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G99" t="s">
         <v>417</v>
@@ -7136,7 +7136,7 @@
         <v>25</v>
       </c>
       <c r="F100">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G100" t="s">
         <v>421</v>
@@ -7165,7 +7165,7 @@
         <v>25</v>
       </c>
       <c r="F101">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G101" t="s">
         <v>425</v>
@@ -7252,7 +7252,7 @@
         <v>25</v>
       </c>
       <c r="F104">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G104" t="s">
         <v>437</v>
@@ -7281,7 +7281,7 @@
         <v>25</v>
       </c>
       <c r="F105">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G105" t="s">
         <v>441</v>
@@ -7310,7 +7310,7 @@
         <v>25</v>
       </c>
       <c r="F106">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G106" t="s">
         <v>445</v>
@@ -7339,7 +7339,7 @@
         <v>25</v>
       </c>
       <c r="F107">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G107" t="s">
         <v>449</v>
@@ -7368,7 +7368,7 @@
         <v>25</v>
       </c>
       <c r="F108">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G108" t="s">
         <v>453</v>
@@ -7397,7 +7397,7 @@
         <v>25</v>
       </c>
       <c r="F109">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G109" t="s">
         <v>457</v>
@@ -7426,7 +7426,7 @@
         <v>25</v>
       </c>
       <c r="F110">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G110" t="s">
         <v>461</v>
@@ -7455,7 +7455,7 @@
         <v>25</v>
       </c>
       <c r="F111">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G111" t="s">
         <v>465</v>
@@ -7484,7 +7484,7 @@
         <v>25</v>
       </c>
       <c r="F112">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G112" t="s">
         <v>471</v>
@@ -7513,7 +7513,7 @@
         <v>25</v>
       </c>
       <c r="F113">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G113" t="s">
         <v>475</v>
@@ -7542,7 +7542,7 @@
         <v>25</v>
       </c>
       <c r="F114">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G114" t="s">
         <v>479</v>
@@ -7571,7 +7571,7 @@
         <v>25</v>
       </c>
       <c r="F115">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G115" t="s">
         <v>483</v>
@@ -7600,7 +7600,7 @@
         <v>25</v>
       </c>
       <c r="F116">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G116" t="s">
         <v>487</v>
@@ -7629,7 +7629,7 @@
         <v>25</v>
       </c>
       <c r="F117">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G117" t="s">
         <v>491</v>
@@ -7658,7 +7658,7 @@
         <v>25</v>
       </c>
       <c r="F118">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G118" t="s">
         <v>495</v>
@@ -7687,7 +7687,7 @@
         <v>25</v>
       </c>
       <c r="F119">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G119" t="s">
         <v>499</v>
@@ -7716,7 +7716,7 @@
         <v>25</v>
       </c>
       <c r="F120">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G120" t="s">
         <v>503</v>
@@ -7745,7 +7745,7 @@
         <v>25</v>
       </c>
       <c r="F121">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G121" t="s">
         <v>507</v>
@@ -7774,7 +7774,7 @@
         <v>25</v>
       </c>
       <c r="F122">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G122" t="s">
         <v>511</v>
@@ -7803,7 +7803,7 @@
         <v>25</v>
       </c>
       <c r="F123">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G123" t="s">
         <v>515</v>
@@ -7832,7 +7832,7 @@
         <v>25</v>
       </c>
       <c r="F124">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G124" t="s">
         <v>519</v>
@@ -7861,7 +7861,7 @@
         <v>25</v>
       </c>
       <c r="F125">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="G125" t="s">
         <v>523</v>
@@ -7890,7 +7890,7 @@
         <v>25</v>
       </c>
       <c r="F126">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G126" t="s">
         <v>527</v>
@@ -7919,7 +7919,7 @@
         <v>25</v>
       </c>
       <c r="F127">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G127" t="s">
         <v>531</v>
@@ -7948,7 +7948,7 @@
         <v>25</v>
       </c>
       <c r="F128">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G128" t="s">
         <v>535</v>
@@ -7977,7 +7977,7 @@
         <v>25</v>
       </c>
       <c r="F129">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G129" t="s">
         <v>539</v>
@@ -8006,7 +8006,7 @@
         <v>25</v>
       </c>
       <c r="F130">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G130" t="s">
         <v>543</v>
@@ -8035,7 +8035,7 @@
         <v>25</v>
       </c>
       <c r="F131">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G131" t="s">
         <v>547</v>
@@ -8064,7 +8064,7 @@
         <v>25</v>
       </c>
       <c r="F132">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G132" t="s">
         <v>551</v>
@@ -8093,7 +8093,7 @@
         <v>25</v>
       </c>
       <c r="F133">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
         <v>555</v>
@@ -8122,7 +8122,7 @@
         <v>25</v>
       </c>
       <c r="F134">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G134" t="s">
         <v>559</v>
@@ -8151,7 +8151,7 @@
         <v>25</v>
       </c>
       <c r="F135">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G135" t="s">
         <v>563</v>
@@ -8180,7 +8180,7 @@
         <v>25</v>
       </c>
       <c r="F136">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G136" t="s">
         <v>567</v>
@@ -8238,7 +8238,7 @@
         <v>25</v>
       </c>
       <c r="F138">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G138" t="s">
         <v>575</v>
@@ -8267,7 +8267,7 @@
         <v>25</v>
       </c>
       <c r="F139">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G139" t="s">
         <v>579</v>
@@ -8296,7 +8296,7 @@
         <v>25</v>
       </c>
       <c r="F140">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G140" t="s">
         <v>583</v>
@@ -8325,7 +8325,7 @@
         <v>25</v>
       </c>
       <c r="F141">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G141" t="s">
         <v>587</v>
@@ -8354,7 +8354,7 @@
         <v>25</v>
       </c>
       <c r="F142">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G142" t="s">
         <v>591</v>
@@ -8412,7 +8412,7 @@
         <v>25</v>
       </c>
       <c r="F144">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G144" t="s">
         <v>599</v>
@@ -8441,7 +8441,7 @@
         <v>25</v>
       </c>
       <c r="F145">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G145" t="s">
         <v>603</v>
@@ -8470,7 +8470,7 @@
         <v>25</v>
       </c>
       <c r="F146">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G146" t="s">
         <v>607</v>
@@ -8499,7 +8499,7 @@
         <v>25</v>
       </c>
       <c r="F147">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G147" t="s">
         <v>611</v>
@@ -8528,7 +8528,7 @@
         <v>25</v>
       </c>
       <c r="F148">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="G148" t="s">
         <v>615</v>
@@ -8557,7 +8557,7 @@
         <v>25</v>
       </c>
       <c r="F149">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G149" t="s">
         <v>619</v>
@@ -8586,7 +8586,7 @@
         <v>25</v>
       </c>
       <c r="F150">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G150" t="s">
         <v>623</v>
@@ -8615,7 +8615,7 @@
         <v>25</v>
       </c>
       <c r="F151">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G151" t="s">
         <v>627</v>
@@ -8644,7 +8644,7 @@
         <v>25</v>
       </c>
       <c r="F152">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G152" t="s">
         <v>631</v>
@@ -8673,7 +8673,7 @@
         <v>25</v>
       </c>
       <c r="F153">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G153" t="s">
         <v>635</v>
@@ -8702,7 +8702,7 @@
         <v>25</v>
       </c>
       <c r="F154">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G154" t="s">
         <v>639</v>
@@ -8731,7 +8731,7 @@
         <v>25</v>
       </c>
       <c r="F155">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G155" t="s">
         <v>643</v>
@@ -8760,7 +8760,7 @@
         <v>25</v>
       </c>
       <c r="F156">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G156" t="s">
         <v>647</v>
@@ -8789,7 +8789,7 @@
         <v>25</v>
       </c>
       <c r="F157">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G157" t="s">
         <v>651</v>
@@ -8818,7 +8818,7 @@
         <v>25</v>
       </c>
       <c r="F158">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G158" t="s">
         <v>655</v>
@@ -8847,7 +8847,7 @@
         <v>25</v>
       </c>
       <c r="F159">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G159" t="s">
         <v>659</v>
@@ -8876,7 +8876,7 @@
         <v>25</v>
       </c>
       <c r="F160">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G160" t="s">
         <v>663</v>
@@ -8905,7 +8905,7 @@
         <v>25</v>
       </c>
       <c r="F161">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G161" t="s">
         <v>667</v>
@@ -8934,7 +8934,7 @@
         <v>25</v>
       </c>
       <c r="F162">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G162" t="s">
         <v>673</v>
@@ -8992,7 +8992,7 @@
         <v>25</v>
       </c>
       <c r="F164">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G164" t="s">
         <v>681</v>
@@ -9021,7 +9021,7 @@
         <v>25</v>
       </c>
       <c r="F165">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G165" t="s">
         <v>685</v>
@@ -9050,7 +9050,7 @@
         <v>25</v>
       </c>
       <c r="F166">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G166" t="s">
         <v>689</v>
@@ -9079,7 +9079,7 @@
         <v>25</v>
       </c>
       <c r="F167">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G167" t="s">
         <v>693</v>
@@ -9108,7 +9108,7 @@
         <v>25</v>
       </c>
       <c r="F168">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G168" t="s">
         <v>697</v>
@@ -9137,7 +9137,7 @@
         <v>25</v>
       </c>
       <c r="F169">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G169" t="s">
         <v>701</v>
@@ -9166,7 +9166,7 @@
         <v>25</v>
       </c>
       <c r="F170">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G170" t="s">
         <v>705</v>
@@ -9195,7 +9195,7 @@
         <v>25</v>
       </c>
       <c r="F171">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G171" t="s">
         <v>709</v>
@@ -9224,7 +9224,7 @@
         <v>25</v>
       </c>
       <c r="F172">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G172" t="s">
         <v>713</v>
@@ -9253,7 +9253,7 @@
         <v>25</v>
       </c>
       <c r="F173">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G173" t="s">
         <v>717</v>
@@ -9282,7 +9282,7 @@
         <v>25</v>
       </c>
       <c r="F174">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G174" t="s">
         <v>721</v>
@@ -9311,7 +9311,7 @@
         <v>25</v>
       </c>
       <c r="F175">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G175" t="s">
         <v>725</v>
@@ -9340,7 +9340,7 @@
         <v>25</v>
       </c>
       <c r="F176">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G176" t="s">
         <v>729</v>
@@ -9369,7 +9369,7 @@
         <v>25</v>
       </c>
       <c r="F177">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G177" t="s">
         <v>733</v>
@@ -9398,7 +9398,7 @@
         <v>25</v>
       </c>
       <c r="F178">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G178" t="s">
         <v>737</v>
@@ -9456,7 +9456,7 @@
         <v>25</v>
       </c>
       <c r="F180">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G180" t="s">
         <v>745</v>
@@ -9485,7 +9485,7 @@
         <v>25</v>
       </c>
       <c r="F181">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G181" t="s">
         <v>749</v>
@@ -9514,7 +9514,7 @@
         <v>25</v>
       </c>
       <c r="F182">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G182" t="s">
         <v>753</v>
@@ -9543,7 +9543,7 @@
         <v>25</v>
       </c>
       <c r="F183">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G183" t="s">
         <v>757</v>
@@ -9572,7 +9572,7 @@
         <v>25</v>
       </c>
       <c r="F184">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G184" t="s">
         <v>761</v>
@@ -9601,7 +9601,7 @@
         <v>25</v>
       </c>
       <c r="F185">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G185" t="s">
         <v>765</v>
@@ -9630,7 +9630,7 @@
         <v>25</v>
       </c>
       <c r="F186">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G186" t="s">
         <v>769</v>
@@ -9659,7 +9659,7 @@
         <v>25</v>
       </c>
       <c r="F187">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G187" t="s">
         <v>773</v>
@@ -9688,7 +9688,7 @@
         <v>25</v>
       </c>
       <c r="F188">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G188" t="s">
         <v>777</v>
@@ -9746,7 +9746,7 @@
         <v>25</v>
       </c>
       <c r="F190">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G190" t="s">
         <v>785</v>
@@ -9775,7 +9775,7 @@
         <v>25</v>
       </c>
       <c r="F191">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G191" t="s">
         <v>789</v>
@@ -9804,7 +9804,7 @@
         <v>25</v>
       </c>
       <c r="F192">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G192" t="s">
         <v>793</v>
@@ -9833,7 +9833,7 @@
         <v>25</v>
       </c>
       <c r="F193">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G193" t="s">
         <v>797</v>
@@ -9862,7 +9862,7 @@
         <v>25</v>
       </c>
       <c r="F194">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G194" t="s">
         <v>801</v>
@@ -9920,7 +9920,7 @@
         <v>25</v>
       </c>
       <c r="F196">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G196" t="s">
         <v>809</v>
@@ -9949,7 +9949,7 @@
         <v>25</v>
       </c>
       <c r="F197">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="G197" t="s">
         <v>813</v>
@@ -9978,7 +9978,7 @@
         <v>25</v>
       </c>
       <c r="F198">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G198" t="s">
         <v>817</v>
@@ -10007,7 +10007,7 @@
         <v>25</v>
       </c>
       <c r="F199">
-        <v>37</v>
+        <v>317</v>
       </c>
       <c r="G199" t="s">
         <v>821</v>
@@ -10036,7 +10036,7 @@
         <v>25</v>
       </c>
       <c r="F200">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G200" t="s">
         <v>825</v>
@@ -10065,7 +10065,7 @@
         <v>25</v>
       </c>
       <c r="F201">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G201" t="s">
         <v>829</v>
@@ -10094,7 +10094,7 @@
         <v>25</v>
       </c>
       <c r="F202">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G202" t="s">
         <v>833</v>
@@ -10123,7 +10123,7 @@
         <v>25</v>
       </c>
       <c r="F203">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G203" t="s">
         <v>837</v>
@@ -10181,7 +10181,7 @@
         <v>25</v>
       </c>
       <c r="F205">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G205" t="s">
         <v>845</v>
@@ -10210,7 +10210,7 @@
         <v>25</v>
       </c>
       <c r="F206">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G206" t="s">
         <v>849</v>
@@ -10239,7 +10239,7 @@
         <v>25</v>
       </c>
       <c r="F207">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G207" t="s">
         <v>853</v>
@@ -10268,7 +10268,7 @@
         <v>25</v>
       </c>
       <c r="F208">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G208" t="s">
         <v>857</v>
@@ -10326,7 +10326,7 @@
         <v>25</v>
       </c>
       <c r="F210">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G210" t="s">
         <v>865</v>
@@ -10355,7 +10355,7 @@
         <v>25</v>
       </c>
       <c r="F211">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G211" t="s">
         <v>869</v>
@@ -10384,7 +10384,7 @@
         <v>25</v>
       </c>
       <c r="F212">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G212" t="s">
         <v>875</v>
@@ -10442,7 +10442,7 @@
         <v>25</v>
       </c>
       <c r="F214">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G214" t="s">
         <v>883</v>
@@ -10471,7 +10471,7 @@
         <v>25</v>
       </c>
       <c r="F215">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G215" t="s">
         <v>887</v>
@@ -10500,7 +10500,7 @@
         <v>25</v>
       </c>
       <c r="F216">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G216" t="s">
         <v>891</v>
@@ -10529,7 +10529,7 @@
         <v>25</v>
       </c>
       <c r="F217">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G217" t="s">
         <v>895</v>
@@ -10558,7 +10558,7 @@
         <v>25</v>
       </c>
       <c r="F218">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G218" t="s">
         <v>899</v>
@@ -10587,7 +10587,7 @@
         <v>25</v>
       </c>
       <c r="F219">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G219" t="s">
         <v>903</v>
@@ -10616,7 +10616,7 @@
         <v>25</v>
       </c>
       <c r="F220">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G220" t="s">
         <v>907</v>
@@ -10645,7 +10645,7 @@
         <v>25</v>
       </c>
       <c r="F221">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G221" t="s">
         <v>911</v>
@@ -10674,7 +10674,7 @@
         <v>25</v>
       </c>
       <c r="F222">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G222" t="s">
         <v>915</v>
@@ -10703,7 +10703,7 @@
         <v>25</v>
       </c>
       <c r="F223">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G223" t="s">
         <v>919</v>
@@ -10732,7 +10732,7 @@
         <v>25</v>
       </c>
       <c r="F224">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G224" t="s">
         <v>923</v>
@@ -10761,7 +10761,7 @@
         <v>25</v>
       </c>
       <c r="F225">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G225" t="s">
         <v>927</v>
@@ -10790,7 +10790,7 @@
         <v>25</v>
       </c>
       <c r="F226">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G226" t="s">
         <v>931</v>
@@ -10819,7 +10819,7 @@
         <v>25</v>
       </c>
       <c r="F227">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G227" t="s">
         <v>935</v>
@@ -10848,7 +10848,7 @@
         <v>25</v>
       </c>
       <c r="F228">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G228" t="s">
         <v>939</v>
@@ -10877,7 +10877,7 @@
         <v>25</v>
       </c>
       <c r="F229">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G229" t="s">
         <v>943</v>
@@ -10935,7 +10935,7 @@
         <v>25</v>
       </c>
       <c r="F231">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G231" t="s">
         <v>951</v>
@@ -10964,7 +10964,7 @@
         <v>25</v>
       </c>
       <c r="F232">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G232" t="s">
         <v>955</v>
@@ -10993,7 +10993,7 @@
         <v>25</v>
       </c>
       <c r="F233">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G233" t="s">
         <v>959</v>
@@ -11022,7 +11022,7 @@
         <v>25</v>
       </c>
       <c r="F234">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G234" t="s">
         <v>963</v>
@@ -11051,7 +11051,7 @@
         <v>25</v>
       </c>
       <c r="F235">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G235" t="s">
         <v>967</v>
@@ -11109,7 +11109,7 @@
         <v>25</v>
       </c>
       <c r="F237">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G237" t="s">
         <v>975</v>
@@ -11138,7 +11138,7 @@
         <v>25</v>
       </c>
       <c r="F238">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G238" t="s">
         <v>979</v>
@@ -11167,7 +11167,7 @@
         <v>25</v>
       </c>
       <c r="F239">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
         <v>983</v>
@@ -11196,7 +11196,7 @@
         <v>25</v>
       </c>
       <c r="F240">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G240" t="s">
         <v>987</v>
@@ -11225,7 +11225,7 @@
         <v>25</v>
       </c>
       <c r="F241">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G241" t="s">
         <v>991</v>
@@ -11254,7 +11254,7 @@
         <v>25</v>
       </c>
       <c r="F242">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G242" t="s">
         <v>995</v>
@@ -11283,7 +11283,7 @@
         <v>25</v>
       </c>
       <c r="F243">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G243" t="s">
         <v>999</v>
@@ -11312,7 +11312,7 @@
         <v>25</v>
       </c>
       <c r="F244">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G244" t="s">
         <v>1003</v>
@@ -11341,7 +11341,7 @@
         <v>25</v>
       </c>
       <c r="F245">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G245" t="s">
         <v>1007</v>
@@ -11370,7 +11370,7 @@
         <v>25</v>
       </c>
       <c r="F246">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G246" t="s">
         <v>1011</v>
@@ -11428,7 +11428,7 @@
         <v>25</v>
       </c>
       <c r="F248">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G248" t="s">
         <v>1019</v>
@@ -11457,7 +11457,7 @@
         <v>25</v>
       </c>
       <c r="F249">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G249" t="s">
         <v>1023</v>
@@ -11486,7 +11486,7 @@
         <v>25</v>
       </c>
       <c r="F250">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G250" t="s">
         <v>1027</v>
@@ -11515,7 +11515,7 @@
         <v>25</v>
       </c>
       <c r="F251">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G251" t="s">
         <v>1031</v>
@@ -11573,7 +11573,7 @@
         <v>25</v>
       </c>
       <c r="F253">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G253" t="s">
         <v>1041</v>
@@ -11602,7 +11602,7 @@
         <v>25</v>
       </c>
       <c r="F254">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G254" t="s">
         <v>1045</v>
@@ -11631,7 +11631,7 @@
         <v>25</v>
       </c>
       <c r="F255">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G255" t="s">
         <v>1049</v>
@@ -11660,7 +11660,7 @@
         <v>25</v>
       </c>
       <c r="F256">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G256" t="s">
         <v>1053</v>
@@ -11689,7 +11689,7 @@
         <v>25</v>
       </c>
       <c r="F257">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G257" t="s">
         <v>1057</v>
@@ -11718,7 +11718,7 @@
         <v>25</v>
       </c>
       <c r="F258">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G258" t="s">
         <v>1061</v>
@@ -11747,7 +11747,7 @@
         <v>25</v>
       </c>
       <c r="F259">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G259" t="s">
         <v>1065</v>
@@ -11776,7 +11776,7 @@
         <v>25</v>
       </c>
       <c r="F260">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G260" t="s">
         <v>1069</v>
@@ -11805,7 +11805,7 @@
         <v>25</v>
       </c>
       <c r="F261">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G261" t="s">
         <v>1073</v>
@@ -11834,7 +11834,7 @@
         <v>25</v>
       </c>
       <c r="F262">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G262" t="s">
         <v>1077</v>
@@ -11863,7 +11863,7 @@
         <v>25</v>
       </c>
       <c r="F263">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G263" t="s">
         <v>1081</v>
@@ -11892,7 +11892,7 @@
         <v>25</v>
       </c>
       <c r="F264">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G264" t="s">
         <v>1085</v>
@@ -11921,7 +11921,7 @@
         <v>25</v>
       </c>
       <c r="F265">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G265" t="s">
         <v>1089</v>
@@ -11950,7 +11950,7 @@
         <v>25</v>
       </c>
       <c r="F266">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G266" t="s">
         <v>1093</v>
@@ -11979,7 +11979,7 @@
         <v>25</v>
       </c>
       <c r="F267">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G267" t="s">
         <v>1097</v>
@@ -12008,7 +12008,7 @@
         <v>25</v>
       </c>
       <c r="F268">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G268" t="s">
         <v>1101</v>
@@ -12037,7 +12037,7 @@
         <v>25</v>
       </c>
       <c r="F269">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G269" t="s">
         <v>1105</v>
@@ -12066,7 +12066,7 @@
         <v>25</v>
       </c>
       <c r="F270">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G270" t="s">
         <v>1109</v>
@@ -12095,7 +12095,7 @@
         <v>25</v>
       </c>
       <c r="F271">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G271" t="s">
         <v>1113</v>
@@ -12124,7 +12124,7 @@
         <v>25</v>
       </c>
       <c r="F272">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G272" t="s">
         <v>1117</v>
@@ -12153,7 +12153,7 @@
         <v>25</v>
       </c>
       <c r="F273">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G273" t="s">
         <v>1121</v>
@@ -12182,7 +12182,7 @@
         <v>25</v>
       </c>
       <c r="F274">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G274" t="s">
         <v>1125</v>
@@ -12240,7 +12240,7 @@
         <v>25</v>
       </c>
       <c r="F276">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G276" t="s">
         <v>1133</v>
@@ -12269,7 +12269,7 @@
         <v>25</v>
       </c>
       <c r="F277">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G277" t="s">
         <v>1137</v>
@@ -12298,7 +12298,7 @@
         <v>25</v>
       </c>
       <c r="F278">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G278" t="s">
         <v>1141</v>
@@ -12327,7 +12327,7 @@
         <v>25</v>
       </c>
       <c r="F279">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G279" t="s">
         <v>1145</v>
@@ -12356,7 +12356,7 @@
         <v>25</v>
       </c>
       <c r="F280">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G280" t="s">
         <v>1149</v>
@@ -12385,7 +12385,7 @@
         <v>25</v>
       </c>
       <c r="F281">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G281" t="s">
         <v>1153</v>
@@ -12414,7 +12414,7 @@
         <v>25</v>
       </c>
       <c r="F282">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G282" t="s">
         <v>1157</v>
@@ -12443,7 +12443,7 @@
         <v>25</v>
       </c>
       <c r="F283">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G283" t="s">
         <v>1161</v>
@@ -12472,7 +12472,7 @@
         <v>25</v>
       </c>
       <c r="F284">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G284" t="s">
         <v>1165</v>
@@ -12501,7 +12501,7 @@
         <v>25</v>
       </c>
       <c r="F285">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G285" t="s">
         <v>1169</v>
@@ -12530,7 +12530,7 @@
         <v>25</v>
       </c>
       <c r="F286">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G286" t="s">
         <v>1173</v>
@@ -12559,7 +12559,7 @@
         <v>25</v>
       </c>
       <c r="F287">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G287" t="s">
         <v>1177</v>
@@ -12588,7 +12588,7 @@
         <v>25</v>
       </c>
       <c r="F288">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G288" t="s">
         <v>1181</v>
@@ -12617,7 +12617,7 @@
         <v>25</v>
       </c>
       <c r="F289">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G289" t="s">
         <v>1185</v>
@@ -12733,7 +12733,7 @@
         <v>25</v>
       </c>
       <c r="F293">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G293" t="s">
         <v>1201</v>
@@ -12791,7 +12791,7 @@
         <v>25</v>
       </c>
       <c r="F295">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G295" t="s">
         <v>1209</v>
@@ -12820,7 +12820,7 @@
         <v>25</v>
       </c>
       <c r="F296">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G296" t="s">
         <v>1213</v>
@@ -12849,7 +12849,7 @@
         <v>25</v>
       </c>
       <c r="F297">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G297" t="s">
         <v>1217</v>
@@ -12878,7 +12878,7 @@
         <v>25</v>
       </c>
       <c r="F298">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G298" t="s">
         <v>1221</v>
@@ -12907,7 +12907,7 @@
         <v>25</v>
       </c>
       <c r="F299">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G299" t="s">
         <v>1225</v>
@@ -12936,7 +12936,7 @@
         <v>25</v>
       </c>
       <c r="F300">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G300" t="s">
         <v>1229</v>
@@ -12965,7 +12965,7 @@
         <v>25</v>
       </c>
       <c r="F301">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G301" t="s">
         <v>1233</v>
